--- a/CodeVS/data/output/barge_schedule_ORDER_9_22.xlsx
+++ b/CodeVS/data/output/barge_schedule_ORDER_9_22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="164">
   <si>
     <t>barge</t>
   </si>
@@ -37,7 +37,10 @@
     <t>tugboat_id_to_customer</t>
   </si>
   <si>
-    <t>Barge ID: B_090, Name: ปอร์เช่ 18, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-06 09:30:00, Water Status: WaterBody.SEA</t>
+    <t>Barge ID: B_048, Name: จากัวร์ 21, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 08:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_090, Name: ปอร์เช่ 18, LOAD: 2850, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-06 09:30:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
     <t>Barge ID: B_092, Name: ปอร์เช่ 20, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-16 10:45:00, Water Status: WaterBody.SEA</t>
@@ -49,7 +52,31 @@
     <t>Barge ID: B_065, Name: จากัวร์ 43, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 07:50:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_053, Name: จากัวร์ 27, LOAD: 950, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:00:00, Water Status: WaterBody.SEA</t>
+    <t>Barge ID: B_010, Name: SP 53, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-06 07:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_038, Name: จากัวร์ 09, LOAD: 3100, Capacity: 3100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 09:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_039, Name: จากัวร์ 10, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 08:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_093, Name: ปอร์เช่ 21, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_080, Name: ปอร์เช่ 03, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-07 08:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_076, Name: จากัวร์ 58, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 08:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_081, Name: ปอร์เช่ 04, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 07:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_099, Name: เอาดี้ 03, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_053, Name: จากัวร์ 27, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:00:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
     <t>Barge ID: B_027, Name: SPI 09, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:20:00, Water Status: WaterBody.SEA</t>
@@ -58,12 +85,6 @@
     <t>Barge ID: B_040, Name: จากัวร์ 11, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:10:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_076, Name: จากัวร์ 58, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 08:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_081, Name: ปอร์เช่ 04, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 07:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
     <t>Barge ID: B_037, Name: จากัวร์ 08, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 07:30:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
@@ -73,27 +94,6 @@
     <t>Barge ID: B_101, Name: เอาดี้ 05, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 09:00:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_099, Name: เอาดี้ 03, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_010, Name: SP 53, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-06 07:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_038, Name: จากัวร์ 09, LOAD: 3100, Capacity: 3100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 09:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_039, Name: จากัวร์ 10, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 08:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_093, Name: ปอร์เช่ 21, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_080, Name: ปอร์เช่ 03, LOAD: 300, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-07 08:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_048, Name: จากัวร์ 21, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 08:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
     <t>Barge ID: B_045, Name: จากัวร์ 17, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:10:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
@@ -103,237 +103,237 @@
     <t>Barge ID: B_047, Name: จากัวร์ 19, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 09:00:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
+    <t>Barge ID: B_095, Name: ปอร์เช่ 24, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_083, Name: ปอร์เช่ 06, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:20:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_025, Name: SPI 05, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 09:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_058, Name: จากัวร์ 34, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 09:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_063, Name: จากัวร์ 41, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_035, Name: จากัวร์ 04, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 08:05:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_056, Name: จากัวร์ 31, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_091, Name: ปอร์เช่ 19, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:20:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_072, Name: จากัวร์ 52, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-31 05:35:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_061, Name: จากัวร์ 37, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 09:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_016, Name: SP 64, LOAD: 2300, Capacity: 2300, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-28 04:55:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_096, Name: ปอร์เช่ 25, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:15:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_079, Name: ปอร์เช่ 02, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-04 09:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_036, Name: จากัวร์ 05, LOAD: 3250, Capacity: 3250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 08:05:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_007, Name: SP 42, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-05 07:20:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_028, Name: SPI 12, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-04 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_094, Name: ปอร์เช่ 23, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-04 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_043, Name: จากัวร์ 15, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-07 07:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_018, Name: SP 75, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_085, Name: ปอร์เช่ 09, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 09:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_097, Name: เอาดี้ 01, LOAD: 1450, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-01 09:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_100, Name: เอาดี้ 04, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_086, Name: ปอร์เช่ 10, LOAD: 3300, Capacity: 3300, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-01 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_009, Name: SP 46, LOAD: 2150, Capacity: 2150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
     <t>Barge ID: B_057, Name: จากัวร์ 32, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:20:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_043, Name: จากัวร์ 15, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-07 07:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_018, Name: SP 75, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:00:00, Water Status: WaterBody.SEA</t>
+    <t>Barge ID: B_068, Name: จากัวร์ 46, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 07:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_041, Name: จากัวร์ 12, LOAD: 3500, Capacity: 3500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_022, Name: SPI 02, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_050, Name: จากัวร์ 24, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 07:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_032, Name: SPI 18, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_012, Name: SP 56, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-04 09:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_064, Name: จากัวร์ 42, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:15:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_019, Name: SP 76, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_033, Name: จากัวร์ 02, LOAD: 3250, Capacity: 3250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_070, Name: จากัวร์ 49, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 07:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_054, Name: จากัวร์ 28, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 08:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_030, Name: SPI 15, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_077, Name: จากัวร์ 60, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_102, Name: เอาดี้ 07, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-15 06:25:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_098, Name: เอาดี้ 02, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-01 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_078, Name: ปอร์เช่ 01, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:15:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
     <t>Barge ID: B_059, Name: จากัวร์ 35, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:00:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_094, Name: ปอร์เช่ 23, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-04 08:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_028, Name: SPI 12, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-04 08:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_079, Name: ปอร์เช่ 02, LOAD: 500, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-04 09:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_091, Name: ปอร์เช่ 19, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:20:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_095, Name: ปอร์เช่ 24, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_083, Name: ปอร์เช่ 06, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:20:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_036, Name: จากัวร์ 05, LOAD: 3250, Capacity: 3250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 08:05:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_007, Name: SP 42, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-05 07:20:00, Water Status: WaterBody.SEA</t>
+    <t>Barge ID: B_051, Name: จากัวร์ 25, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 07:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_011, Name: SP 55, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_044, Name: จากัวร์ 16, LOAD: 3500, Capacity: 3500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-26 06:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_066, Name: จากัวร์ 44, LOAD: 850, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_013, Name: SP 57, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-01 09:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_074, Name: จากัวร์ 55, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 08:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_089, Name: ปอร์เช่ 17, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 07:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_055, Name: จากัวร์ 30, LOAD: 4750, Capacity: 4750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 07:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_021, Name: SPI 01, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-06 08:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_067, Name: จากัวร์ 45, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 09:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_008, Name: SP 43, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 07:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_046, Name: จากัวร์ 18, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:20:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_084, Name: ปอร์เช่ 07, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-29 05:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_060, Name: จากัวร์ 36, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 08:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_052, Name: จากัวร์ 26, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-05 07:20:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_020, Name: SP 77, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-18 08:20:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_088, Name: ปอร์เช่ 16, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_023, Name: SPI 03, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 08:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_049, Name: จากัวร์ 22, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_026, Name: SPI 06, LOAD: 2700, Capacity: 2700, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-31 06:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_031, Name: SPI 17, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-05 07:20:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_075, Name: จากัวร์ 56, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_069, Name: จากัวร์ 47, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_087, Name: ปอร์เช่ 12, LOAD: 3300, Capacity: 3300, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-28 05:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_014, Name: SP 59, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-12 09:50:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
     <t>Barge ID: B_062, Name: จากัวร์ 40, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-06 08:30:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_016, Name: SP 64, LOAD: 2300, Capacity: 2300, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-28 04:55:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_096, Name: ปอร์เช่ 25, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:15:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_072, Name: จากัวร์ 52, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-31 05:35:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_064, Name: จากัวร์ 42, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:15:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_035, Name: จากัวร์ 04, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 08:05:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_025, Name: SPI 05, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 09:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_067, Name: จากัวร์ 45, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 09:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_084, Name: ปอร์เช่ 07, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-29 05:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_023, Name: SPI 03, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 08:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_060, Name: จากัวร์ 36, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 08:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_070, Name: จากัวร์ 49, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 07:50:00, Water Status: WaterBody.SEA</t>
+    <t>Barge ID: B_029, Name: SPI 13, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-16 10:45:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
     <t>Barge ID: B_042, Name: จากัวร์ 13, LOAD: 3000, Capacity: 3000, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_022, Name: SPI 02, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_033, Name: จากัวร์ 02, LOAD: 3250, Capacity: 3250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_012, Name: SP 56, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-04 09:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_052, Name: จากัวร์ 26, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-05 07:20:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_088, Name: ปอร์เช่ 16, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_009, Name: SP 46, LOAD: 2150, Capacity: 2150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_020, Name: SP 77, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-18 08:20:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_056, Name: จากัวร์ 31, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
     <t>Barge ID: B_024, Name: SPI 04, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-16 10:25:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_061, Name: จากัวร์ 37, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 09:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_032, Name: SPI 18, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_051, Name: จากัวร์ 25, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 07:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_066, Name: จากัวร์ 44, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_019, Name: SP 76, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_097, Name: เอาดี้ 01, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-01 09:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_058, Name: จากัวร์ 34, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 09:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_044, Name: จากัวร์ 16, LOAD: 3500, Capacity: 3500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-26 06:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_011, Name: SP 55, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_074, Name: จากัวร์ 55, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 08:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_014, Name: SP 59, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-12 09:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_086, Name: ปอร์เช่ 10, LOAD: 3300, Capacity: 3300, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-01 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_041, Name: จากัวร์ 12, LOAD: 3500, Capacity: 3500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
+    <t>Barge ID: B_034, Name: จากัวร์ 03, LOAD: 3250, Capacity: 3250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_073, Name: จากัวร์ 53, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
     <t>Barge ID: B_082, Name: ปอร์เช่ 05, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-31 06:10:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_054, Name: จากัวร์ 28, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 08:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_089, Name: ปอร์เช่ 17, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 07:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_063, Name: จากัวร์ 41, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_034, Name: จากัวร์ 03, LOAD: 3250, Capacity: 3250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_075, Name: จากัวร์ 56, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_008, Name: SP 43, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 07:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_046, Name: จากัวร์ 18, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:20:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_021, Name: SPI 01, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-06 08:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_069, Name: จากัวร์ 47, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_029, Name: SPI 13, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-16 10:45:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_030, Name: SPI 15, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_068, Name: จากัวร์ 46, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 07:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_098, Name: เอาดี้ 02, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-01 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_050, Name: จากัวร์ 24, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 07:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_077, Name: จากัวร์ 60, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_087, Name: ปอร์เช่ 12, LOAD: 3300, Capacity: 3300, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-28 05:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_078, Name: ปอร์เช่ 01, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:15:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_013, Name: SP 57, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-01 09:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_031, Name: SPI 17, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-05 07:20:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_100, Name: เอาดี้ 04, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_073, Name: จากัวร์ 53, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_102, Name: เอาดี้ 07, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-15 06:25:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_085, Name: ปอร์เช่ 09, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 09:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_049, Name: จากัวร์ 22, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_055, Name: จากัวร์ 30, LOAD: 4750, Capacity: 4750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 07:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_026, Name: SPI 06, LOAD: 2700, Capacity: 2700, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-31 06:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
     <t>Barge ID: B_005, Name: SP 31, LOAD: 2100, Capacity: 2100, Location: (28.8232, 201.183), Setup Time: 20 mins, Ready Time: 2024-02-03 09:40:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
+    <t>Barge ID: B_003, Name: SP 29, LOAD: 2250, Capacity: 2250, Location: (28.8232, 201.183), Setup Time: 20 mins, Ready Time: 2024-02-06 08:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
     <t>Barge ID: B_004, Name: SP 30, LOAD: 2100, Capacity: 2100, Location: (28.8232, 201.183), Setup Time: 20 mins, Ready Time: 2024-01-18 09:00:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_003, Name: SP 29, LOAD: 2250, Capacity: 2250, Location: (28.8232, 201.183), Setup Time: 20 mins, Ready Time: 2024-02-06 08:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
     <t>Barge ID: B_006, Name: SP 32, LOAD: 2100, Capacity: 2100, Location: (28.8232, 201.183), Setup Time: 20 mins, Ready Time: 2024-02-06 09:30:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
@@ -346,45 +346,45 @@
     <t>(datetime.datetime(2025, 1, 19, 17, 0), datetime.datetime(2025, 2, 27, 0, 10))</t>
   </si>
   <si>
+    <t>(datetime.datetime(2025, 1, 25, 11, 25), datetime.datetime(2025, 2, 8, 14, 30))</t>
+  </si>
+  <si>
+    <t>(datetime.datetime(2025, 1, 30, 10, 45), datetime.datetime(2025, 2, 7, 6, 30))</t>
+  </si>
+  <si>
+    <t>(datetime.datetime(2025, 1, 25, 11, 25), datetime.datetime(2025, 2, 11, 13, 50))</t>
+  </si>
+  <si>
     <t>(datetime.datetime(2025, 1, 23, 13, 30), datetime.datetime(2025, 2, 15, 6, 20))</t>
   </si>
   <si>
-    <t>(datetime.datetime(2025, 1, 25, 11, 25), datetime.datetime(2025, 2, 8, 14, 30))</t>
-  </si>
-  <si>
-    <t>(datetime.datetime(2025, 1, 25, 11, 25), datetime.datetime(2025, 2, 11, 13, 50))</t>
-  </si>
-  <si>
     <t>(datetime.datetime(2025, 1, 26, 8, 40), datetime.datetime(2025, 2, 16, 2, 0))</t>
   </si>
   <si>
+    <t>(datetime.datetime(2025, 2, 2, 8, 40), datetime.datetime(2025, 2, 26, 2, 0))</t>
+  </si>
+  <si>
     <t>(datetime.datetime(2025, 1, 28, 9, 30), datetime.datetime(2025, 2, 17, 8, 0))</t>
   </si>
   <si>
-    <t>(datetime.datetime(2025, 1, 30, 10, 45), datetime.datetime(2025, 2, 7, 6, 30))</t>
+    <t>(datetime.datetime(2025, 2, 9, 10, 0), datetime.datetime(2025, 2, 15, 13, 50))</t>
+  </si>
+  <si>
+    <t>(datetime.datetime(2025, 2, 4, 13, 10), datetime.datetime(2025, 2, 18, 14, 25))</t>
+  </si>
+  <si>
+    <t>(datetime.datetime(2025, 2, 10, 6, 0), datetime.datetime(2025, 2, 19, 11, 10))</t>
+  </si>
+  <si>
+    <t>(datetime.datetime(2025, 2, 3, 16, 20), datetime.datetime(2025, 2, 25, 12, 30))</t>
+  </si>
+  <si>
+    <t>(datetime.datetime(2025, 2, 1, 18, 21, 50), datetime.datetime(2025, 3, 1, 18, 21, 50))</t>
   </si>
   <si>
     <t>(datetime.datetime(2025, 2, 1, 7, 50), datetime.datetime(2025, 2, 28, 8, 20))</t>
   </si>
   <si>
-    <t>(datetime.datetime(2025, 2, 1, 18, 21, 50), datetime.datetime(2025, 3, 1, 18, 21, 50))</t>
-  </si>
-  <si>
-    <t>(datetime.datetime(2025, 2, 2, 8, 40), datetime.datetime(2025, 2, 26, 2, 0))</t>
-  </si>
-  <si>
-    <t>(datetime.datetime(2025, 2, 3, 16, 20), datetime.datetime(2025, 2, 25, 12, 30))</t>
-  </si>
-  <si>
-    <t>(datetime.datetime(2025, 2, 4, 13, 10), datetime.datetime(2025, 2, 18, 14, 25))</t>
-  </si>
-  <si>
-    <t>(datetime.datetime(2025, 2, 9, 10, 0), datetime.datetime(2025, 2, 15, 13, 50))</t>
-  </si>
-  <si>
-    <t>(datetime.datetime(2025, 2, 10, 6, 0), datetime.datetime(2025, 2, 19, 11, 10))</t>
-  </si>
-  <si>
     <t>(datetime.datetime(2025, 9, 17, 2, 9, 38), datetime.datetime(2025, 9, 18, 2, 9, 38))</t>
   </si>
   <si>
@@ -403,45 +403,45 @@
     <t>ODR_003</t>
   </si>
   <si>
+    <t>ODR_005</t>
+  </si>
+  <si>
+    <t>ODR_009</t>
+  </si>
+  <si>
+    <t>ODR_006</t>
+  </si>
+  <si>
     <t>ODR_004</t>
   </si>
   <si>
-    <t>ODR_005</t>
-  </si>
-  <si>
-    <t>ODR_006</t>
-  </si>
-  <si>
     <t>ODR_007</t>
   </si>
   <si>
+    <t>ODR_015</t>
+  </si>
+  <si>
     <t>ODR_008</t>
   </si>
   <si>
-    <t>ODR_009</t>
+    <t>ODR_013</t>
+  </si>
+  <si>
+    <t>ODR_012</t>
+  </si>
+  <si>
+    <t>ODR_014</t>
+  </si>
+  <si>
+    <t>ODR_011</t>
+  </si>
+  <si>
+    <t>ODR_016</t>
   </si>
   <si>
     <t>ODR_010</t>
   </si>
   <si>
-    <t>ODR_016</t>
-  </si>
-  <si>
-    <t>ODR_015</t>
-  </si>
-  <si>
-    <t>ODR_011</t>
-  </si>
-  <si>
-    <t>ODR_012</t>
-  </si>
-  <si>
-    <t>ODR_013</t>
-  </si>
-  <si>
-    <t>ODR_014</t>
-  </si>
-  <si>
     <t>ODR_017</t>
   </si>
   <si>
@@ -457,30 +457,30 @@
     <t>SeaTB_06</t>
   </si>
   <si>
+    <t>SeaTB_04</t>
+  </si>
+  <si>
+    <t>SeaTB_08</t>
+  </si>
+  <si>
+    <t>SeaTB_09</t>
+  </si>
+  <si>
+    <t>SeaTB_03</t>
+  </si>
+  <si>
     <t>SeaTB_02</t>
   </si>
   <si>
+    <t>SeaTB_11</t>
+  </si>
+  <si>
     <t>SeaTB_12</t>
   </si>
   <si>
-    <t>SeaTB_03</t>
-  </si>
-  <si>
-    <t>SeaTB_04</t>
-  </si>
-  <si>
-    <t>SeaTB_08</t>
-  </si>
-  <si>
-    <t>SeaTB_11</t>
-  </si>
-  <si>
     <t>SeaTB_07</t>
   </si>
   <si>
-    <t>SeaTB_09</t>
-  </si>
-  <si>
     <t>RiverTB_10</t>
   </si>
   <si>
@@ -490,22 +490,22 @@
     <t>RiverTB_08</t>
   </si>
   <si>
+    <t>RiverTB_12</t>
+  </si>
+  <si>
+    <t>RiverTB_09</t>
+  </si>
+  <si>
     <t>RiverTB_06</t>
   </si>
   <si>
-    <t>RiverTB_12</t>
+    <t>RiverTB_11</t>
+  </si>
+  <si>
+    <t>RiverTB_02</t>
   </si>
   <si>
     <t>RiverTB_13</t>
-  </si>
-  <si>
-    <t>RiverTB_11</t>
-  </si>
-  <si>
-    <t>RiverTB_02</t>
-  </si>
-  <si>
-    <t>RiverTB_09</t>
   </si>
 </sst>
 </file>
@@ -863,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G368"/>
+  <dimension ref="A1:G364"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -894,7 +894,7 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>2300</v>
+        <v>3150</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -954,7 +954,7 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -974,7 +974,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -994,7 +994,7 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>2900</v>
+        <v>1800</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1014,7 +1014,7 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>2250</v>
+        <v>3100</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1034,7 +1034,7 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1074,7 +1074,7 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>2900</v>
+        <v>3150</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1114,7 +1114,7 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>2750</v>
+        <v>3150</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1154,7 +1154,7 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>1800</v>
+        <v>2250</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1174,7 +1174,7 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>3100</v>
+        <v>2900</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1214,7 +1214,7 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1234,7 +1234,7 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>3150</v>
+        <v>2200</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>2250</v>
+        <v>2750</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>127</v>
       </c>
       <c r="F24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1354,7 +1354,7 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1374,7 +1374,7 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>2100</v>
+        <v>2600</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         <v>127</v>
       </c>
       <c r="F26" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1406,7 +1406,7 @@
         <v>127</v>
       </c>
       <c r="F27" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1414,7 +1414,7 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>3150</v>
+        <v>2500</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1426,7 +1426,7 @@
         <v>127</v>
       </c>
       <c r="F28" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1446,7 +1446,7 @@
         <v>127</v>
       </c>
       <c r="F29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1454,7 +1454,7 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -1466,7 +1466,7 @@
         <v>127</v>
       </c>
       <c r="F30" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1486,7 +1486,7 @@
         <v>127</v>
       </c>
       <c r="F31" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1494,7 +1494,7 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>3150</v>
+        <v>2500</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -1506,7 +1506,7 @@
         <v>127</v>
       </c>
       <c r="F32" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1514,7 +1514,7 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>127</v>
       </c>
       <c r="F33" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1534,7 +1534,7 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>3250</v>
+        <v>2300</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -1554,7 +1554,7 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>1800</v>
+        <v>3150</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>2300</v>
+        <v>3250</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -1606,7 +1606,7 @@
         <v>127</v>
       </c>
       <c r="F37" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1614,7 +1614,7 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>3150</v>
+        <v>1800</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -1626,7 +1626,7 @@
         <v>127</v>
       </c>
       <c r="F38" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1634,7 +1634,7 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -1646,7 +1646,7 @@
         <v>127</v>
       </c>
       <c r="F39" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1654,7 +1654,7 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>2900</v>
+        <v>2250</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -1694,7 +1694,7 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>2600</v>
+        <v>2100</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -1706,7 +1706,7 @@
         <v>127</v>
       </c>
       <c r="F42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1714,7 +1714,7 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>128</v>
       </c>
       <c r="F43" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1734,7 +1734,7 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>3150</v>
+        <v>2750</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -1746,7 +1746,7 @@
         <v>128</v>
       </c>
       <c r="F44" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1754,7 +1754,7 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>2600</v>
+        <v>2750</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -1766,7 +1766,7 @@
         <v>128</v>
       </c>
       <c r="F45" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1774,7 +1774,7 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>2250</v>
+        <v>3300</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>127</v>
       </c>
       <c r="F46" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1794,7 +1794,7 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>2500</v>
+        <v>950</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>127</v>
       </c>
       <c r="F47" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1814,7 +1814,7 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>3000</v>
+        <v>2250</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -1826,7 +1826,7 @@
         <v>127</v>
       </c>
       <c r="F48" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1834,7 +1834,7 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -1846,7 +1846,7 @@
         <v>127</v>
       </c>
       <c r="F49" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1854,7 +1854,7 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>3250</v>
+        <v>3500</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>127</v>
       </c>
       <c r="F50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -1874,7 +1874,7 @@
         <v>56</v>
       </c>
       <c r="B51">
-        <v>1800</v>
+        <v>2600</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         <v>127</v>
       </c>
       <c r="F51" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1906,7 +1906,7 @@
         <v>127</v>
       </c>
       <c r="F52" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1914,7 +1914,7 @@
         <v>58</v>
       </c>
       <c r="B53">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -1926,7 +1926,7 @@
         <v>127</v>
       </c>
       <c r="F53" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -1934,7 +1934,7 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>127</v>
       </c>
       <c r="F54" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -1954,7 +1954,7 @@
         <v>60</v>
       </c>
       <c r="B55">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>128</v>
       </c>
       <c r="F55" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -1974,7 +1974,7 @@
         <v>61</v>
       </c>
       <c r="B56">
-        <v>2250</v>
+        <v>2100</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -1986,7 +1986,7 @@
         <v>128</v>
       </c>
       <c r="F56" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -1994,7 +1994,7 @@
         <v>62</v>
       </c>
       <c r="B57">
-        <v>2600</v>
+        <v>3250</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -2006,7 +2006,7 @@
         <v>128</v>
       </c>
       <c r="F57" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2014,7 +2014,7 @@
         <v>63</v>
       </c>
       <c r="B58">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>128</v>
       </c>
       <c r="F58" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2034,7 +2034,7 @@
         <v>64</v>
       </c>
       <c r="B59">
-        <v>2900</v>
+        <v>2250</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -2046,7 +2046,7 @@
         <v>128</v>
       </c>
       <c r="F59" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2054,7 +2054,7 @@
         <v>65</v>
       </c>
       <c r="B60">
-        <v>2250</v>
+        <v>2900</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>128</v>
       </c>
       <c r="F60" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2086,7 +2086,7 @@
         <v>128</v>
       </c>
       <c r="F61" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2094,7 +2094,7 @@
         <v>67</v>
       </c>
       <c r="B62">
-        <v>2100</v>
+        <v>2750</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -2106,7 +2106,7 @@
         <v>128</v>
       </c>
       <c r="F62" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2126,7 +2126,7 @@
         <v>128</v>
       </c>
       <c r="F63" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2134,7 +2134,7 @@
         <v>69</v>
       </c>
       <c r="B64">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -2146,7 +2146,7 @@
         <v>128</v>
       </c>
       <c r="F64" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2154,7 +2154,7 @@
         <v>70</v>
       </c>
       <c r="B65">
-        <v>3500</v>
+        <v>2250</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -2166,7 +2166,7 @@
         <v>128</v>
       </c>
       <c r="F65" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2174,7 +2174,7 @@
         <v>71</v>
       </c>
       <c r="B66">
-        <v>1800</v>
+        <v>2250</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -2186,7 +2186,7 @@
         <v>128</v>
       </c>
       <c r="F66" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2194,7 +2194,7 @@
         <v>72</v>
       </c>
       <c r="B67">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -2206,7 +2206,7 @@
         <v>128</v>
       </c>
       <c r="F67" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2214,7 +2214,7 @@
         <v>73</v>
       </c>
       <c r="B68">
-        <v>2100</v>
+        <v>3500</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -2226,7 +2226,7 @@
         <v>128</v>
       </c>
       <c r="F68" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2234,7 +2234,7 @@
         <v>74</v>
       </c>
       <c r="B69">
-        <v>3300</v>
+        <v>2500</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2246,7 +2246,7 @@
         <v>128</v>
       </c>
       <c r="F69" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2254,7 +2254,7 @@
         <v>75</v>
       </c>
       <c r="B70">
-        <v>3500</v>
+        <v>2100</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>128</v>
       </c>
       <c r="F70" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2274,7 +2274,7 @@
         <v>76</v>
       </c>
       <c r="B71">
-        <v>3150</v>
+        <v>2500</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -2286,7 +2286,7 @@
         <v>128</v>
       </c>
       <c r="F71" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2294,7 +2294,7 @@
         <v>77</v>
       </c>
       <c r="B72">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2306,7 +2306,7 @@
         <v>128</v>
       </c>
       <c r="F72" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -2314,7 +2314,7 @@
         <v>78</v>
       </c>
       <c r="B73">
-        <v>3150</v>
+        <v>4750</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2326,7 +2326,7 @@
         <v>128</v>
       </c>
       <c r="F73" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -2334,19 +2334,19 @@
         <v>79</v>
       </c>
       <c r="B74">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E74" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F74" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2354,7 +2354,7 @@
         <v>80</v>
       </c>
       <c r="B75">
-        <v>3250</v>
+        <v>2500</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2374,7 +2374,7 @@
         <v>81</v>
       </c>
       <c r="B76">
-        <v>2500</v>
+        <v>1650</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2394,19 +2394,19 @@
         <v>82</v>
       </c>
       <c r="B77">
-        <v>1800</v>
+        <v>2250</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E77" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F77" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -2414,16 +2414,16 @@
         <v>83</v>
       </c>
       <c r="B78">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E78" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F78" t="s">
         <v>146</v>
@@ -2434,16 +2434,16 @@
         <v>84</v>
       </c>
       <c r="B79">
-        <v>2600</v>
+        <v>2250</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E79" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F79" t="s">
         <v>146</v>
@@ -2454,16 +2454,16 @@
         <v>85</v>
       </c>
       <c r="B80">
-        <v>950</v>
+        <v>2250</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E80" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F80" t="s">
         <v>146</v>
@@ -2474,7 +2474,7 @@
         <v>86</v>
       </c>
       <c r="B81">
-        <v>2900</v>
+        <v>2100</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>128</v>
       </c>
       <c r="F81" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -2494,7 +2494,7 @@
         <v>87</v>
       </c>
       <c r="B82">
-        <v>2900</v>
+        <v>3150</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2506,7 +2506,7 @@
         <v>128</v>
       </c>
       <c r="F82" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -2514,7 +2514,7 @@
         <v>88</v>
       </c>
       <c r="B83">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2526,7 +2526,7 @@
         <v>128</v>
       </c>
       <c r="F83" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -2534,7 +2534,7 @@
         <v>89</v>
       </c>
       <c r="B84">
-        <v>2750</v>
+        <v>2250</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2546,7 +2546,7 @@
         <v>128</v>
       </c>
       <c r="F84" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2554,7 +2554,7 @@
         <v>90</v>
       </c>
       <c r="B85">
-        <v>2250</v>
+        <v>2700</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2566,7 +2566,7 @@
         <v>128</v>
       </c>
       <c r="F85" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -2574,7 +2574,7 @@
         <v>91</v>
       </c>
       <c r="B86">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2586,7 +2586,7 @@
         <v>128</v>
       </c>
       <c r="F86" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -2594,7 +2594,7 @@
         <v>92</v>
       </c>
       <c r="B87">
-        <v>3300</v>
+        <v>2500</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2606,7 +2606,7 @@
         <v>128</v>
       </c>
       <c r="F87" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -2614,7 +2614,7 @@
         <v>93</v>
       </c>
       <c r="B88">
-        <v>3150</v>
+        <v>2500</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2626,7 +2626,7 @@
         <v>128</v>
       </c>
       <c r="F88" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -2634,7 +2634,7 @@
         <v>94</v>
       </c>
       <c r="B89">
-        <v>2100</v>
+        <v>3300</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2646,7 +2646,7 @@
         <v>128</v>
       </c>
       <c r="F89" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -2654,7 +2654,7 @@
         <v>95</v>
       </c>
       <c r="B90">
-        <v>2900</v>
+        <v>2100</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2666,7 +2666,7 @@
         <v>128</v>
       </c>
       <c r="F90" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -2674,7 +2674,7 @@
         <v>96</v>
       </c>
       <c r="B91">
-        <v>2750</v>
+        <v>2500</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2686,7 +2686,7 @@
         <v>128</v>
       </c>
       <c r="F91" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -2694,7 +2694,7 @@
         <v>97</v>
       </c>
       <c r="B92">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2706,7 +2706,7 @@
         <v>128</v>
       </c>
       <c r="F92" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -2714,7 +2714,7 @@
         <v>98</v>
       </c>
       <c r="B93">
-        <v>2750</v>
+        <v>3000</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>128</v>
       </c>
       <c r="F93" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -2734,7 +2734,7 @@
         <v>99</v>
       </c>
       <c r="B94">
-        <v>3150</v>
+        <v>2600</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2746,7 +2746,7 @@
         <v>128</v>
       </c>
       <c r="F94" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -2754,7 +2754,7 @@
         <v>100</v>
       </c>
       <c r="B95">
-        <v>2250</v>
+        <v>3250</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2766,7 +2766,7 @@
         <v>128</v>
       </c>
       <c r="F95" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -2774,7 +2774,7 @@
         <v>101</v>
       </c>
       <c r="B96">
-        <v>4750</v>
+        <v>2500</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -2786,7 +2786,7 @@
         <v>128</v>
       </c>
       <c r="F96" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -2794,107 +2794,107 @@
         <v>102</v>
       </c>
       <c r="B97">
-        <v>2700</v>
+        <v>3150</v>
       </c>
       <c r="C97">
         <v>0</v>
       </c>
       <c r="D97" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E97" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F97" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="B98">
-        <v>3150</v>
+        <v>100</v>
       </c>
       <c r="C98">
-        <v>56.09574693011376</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D98" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E98" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F98" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B99">
-        <v>2300</v>
+        <v>3150</v>
       </c>
       <c r="C99">
-        <v>56.09574693011376</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D99" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E99" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F99" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B100">
         <v>3150</v>
       </c>
       <c r="C100">
-        <v>56.09574693011376</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D100" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E100" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F100" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="B101">
-        <v>1300</v>
+        <v>3300</v>
       </c>
       <c r="C101">
-        <v>56.09574693011376</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D101" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E101" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F101" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B102">
-        <v>2250</v>
+        <v>1700</v>
       </c>
       <c r="C102">
         <v>56.09574693011376</v>
@@ -2906,24 +2906,24 @@
         <v>131</v>
       </c>
       <c r="F102" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="B103">
-        <v>1400</v>
+        <v>100</v>
       </c>
       <c r="C103">
-        <v>10284.89209676953</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D103" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E103" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F103" t="s">
         <v>147</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B104">
-        <v>2500</v>
+        <v>2350</v>
       </c>
       <c r="C104">
         <v>56.09574693011376</v>
       </c>
       <c r="D104" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E104" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F104" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -2954,56 +2954,56 @@
         <v>13</v>
       </c>
       <c r="B105">
-        <v>2250</v>
+        <v>3100</v>
       </c>
       <c r="C105">
         <v>56.09574693011376</v>
       </c>
       <c r="D105" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E105" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F105" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B106">
-        <v>2900</v>
+        <v>2250</v>
       </c>
       <c r="C106">
         <v>56.09574693011376</v>
       </c>
       <c r="D106" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E106" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F106" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="B107">
-        <v>1750</v>
+        <v>2500</v>
       </c>
       <c r="C107">
-        <v>10284.89209676953</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D107" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E107" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F107" t="s">
         <v>147</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B108">
-        <v>2100</v>
+        <v>3150</v>
       </c>
       <c r="C108">
-        <v>50.30315431564902</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D108" t="s">
         <v>113</v>
@@ -3031,133 +3031,133 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="B109">
-        <v>3150</v>
+        <v>2100</v>
       </c>
       <c r="C109">
-        <v>50.30315431564902</v>
+        <v>10284.89209676953</v>
       </c>
       <c r="D109" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E109" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F109" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>29</v>
+        <v>104</v>
       </c>
       <c r="B110">
         <v>2250</v>
       </c>
       <c r="C110">
-        <v>50.30315431564902</v>
+        <v>10284.89209676953</v>
       </c>
       <c r="D110" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E110" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F110" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="B111">
-        <v>2250</v>
+        <v>2100</v>
       </c>
       <c r="C111">
-        <v>50.30315431564902</v>
+        <v>10284.89209676953</v>
       </c>
       <c r="D111" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E111" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F111" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="B112">
-        <v>2250</v>
+        <v>1400</v>
       </c>
       <c r="C112">
-        <v>50.30315431564902</v>
+        <v>10284.89209676953</v>
       </c>
       <c r="D112" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E112" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F112" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B113">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C113">
         <v>56.09574693011376</v>
       </c>
       <c r="D113" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E113" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F113" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B114">
-        <v>1700</v>
+        <v>3150</v>
       </c>
       <c r="C114">
         <v>56.09574693011376</v>
       </c>
       <c r="D114" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E114" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F114" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="B115">
-        <v>3150</v>
+        <v>1800</v>
       </c>
       <c r="C115">
-        <v>50.30315431564902</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D115" t="s">
         <v>114</v>
@@ -3166,524 +3166,524 @@
         <v>133</v>
       </c>
       <c r="F115" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B116">
+        <v>3250</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+      <c r="D116" t="s">
+        <v>115</v>
+      </c>
+      <c r="E116" t="s">
+        <v>134</v>
+      </c>
+      <c r="G116" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" t="s">
+        <v>63</v>
+      </c>
+      <c r="B117">
+        <v>2500</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="D117" t="s">
+        <v>115</v>
+      </c>
+      <c r="E117" t="s">
+        <v>134</v>
+      </c>
+      <c r="G117" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" t="s">
+        <v>83</v>
+      </c>
+      <c r="B118">
         <v>3150</v>
       </c>
-      <c r="C116">
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="D118" t="s">
+        <v>115</v>
+      </c>
+      <c r="E118" t="s">
+        <v>134</v>
+      </c>
+      <c r="G118" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" t="s">
+        <v>84</v>
+      </c>
+      <c r="B119">
+        <v>2250</v>
+      </c>
+      <c r="C119">
+        <v>0</v>
+      </c>
+      <c r="D119" t="s">
+        <v>115</v>
+      </c>
+      <c r="E119" t="s">
+        <v>134</v>
+      </c>
+      <c r="G119" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" t="s">
+        <v>82</v>
+      </c>
+      <c r="B120">
+        <v>2250</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+      <c r="D120" t="s">
+        <v>115</v>
+      </c>
+      <c r="E120" t="s">
+        <v>134</v>
+      </c>
+      <c r="G120" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" t="s">
+        <v>49</v>
+      </c>
+      <c r="B121">
+        <v>2750</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121" t="s">
+        <v>115</v>
+      </c>
+      <c r="E121" t="s">
+        <v>134</v>
+      </c>
+      <c r="G121" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" t="s">
+        <v>61</v>
+      </c>
+      <c r="B122">
+        <v>2100</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+      <c r="D122" t="s">
+        <v>115</v>
+      </c>
+      <c r="E122" t="s">
+        <v>134</v>
+      </c>
+      <c r="G122" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" t="s">
+        <v>48</v>
+      </c>
+      <c r="B123">
+        <v>3150</v>
+      </c>
+      <c r="C123">
+        <v>0</v>
+      </c>
+      <c r="D123" t="s">
+        <v>115</v>
+      </c>
+      <c r="E123" t="s">
+        <v>134</v>
+      </c>
+      <c r="G123" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" t="s">
+        <v>60</v>
+      </c>
+      <c r="B124">
+        <v>2500</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+      <c r="D124" t="s">
+        <v>115</v>
+      </c>
+      <c r="E124" t="s">
+        <v>134</v>
+      </c>
+      <c r="G124" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" t="s">
+        <v>64</v>
+      </c>
+      <c r="B125">
+        <v>2250</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+      <c r="D125" t="s">
+        <v>115</v>
+      </c>
+      <c r="E125" t="s">
+        <v>134</v>
+      </c>
+      <c r="G125" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" t="s">
+        <v>50</v>
+      </c>
+      <c r="B126">
+        <v>2750</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126" t="s">
+        <v>115</v>
+      </c>
+      <c r="E126" t="s">
+        <v>134</v>
+      </c>
+      <c r="G126" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" t="s">
+        <v>26</v>
+      </c>
+      <c r="B127">
+        <v>1100</v>
+      </c>
+      <c r="C127">
+        <v>10285.36152801761</v>
+      </c>
+      <c r="D127" t="s">
+        <v>115</v>
+      </c>
+      <c r="E127" t="s">
+        <v>134</v>
+      </c>
+      <c r="G127" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" t="s">
+        <v>43</v>
+      </c>
+      <c r="B128">
+        <v>1800</v>
+      </c>
+      <c r="C128">
         <v>50.30315431564902</v>
       </c>
-      <c r="D116" t="s">
-        <v>114</v>
-      </c>
-      <c r="E116" t="s">
-        <v>133</v>
-      </c>
-      <c r="F116" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117">
-        <v>3150</v>
-      </c>
-      <c r="C117">
-        <v>56.09574693011376</v>
-      </c>
-      <c r="D117" t="s">
-        <v>114</v>
-      </c>
-      <c r="E117" t="s">
-        <v>133</v>
-      </c>
-      <c r="F117" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118" t="s">
-        <v>51</v>
-      </c>
-      <c r="B118">
-        <v>2250</v>
-      </c>
-      <c r="C118">
-        <v>50.30315431564902</v>
-      </c>
-      <c r="D118" t="s">
-        <v>114</v>
-      </c>
-      <c r="E118" t="s">
-        <v>133</v>
-      </c>
-      <c r="F118" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119" t="s">
-        <v>39</v>
-      </c>
-      <c r="B119">
-        <v>3250</v>
-      </c>
-      <c r="C119">
-        <v>50.30315431564902</v>
-      </c>
-      <c r="D119" t="s">
-        <v>114</v>
-      </c>
-      <c r="E119" t="s">
-        <v>133</v>
-      </c>
-      <c r="F119" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120" t="s">
-        <v>53</v>
-      </c>
-      <c r="B120">
-        <v>3000</v>
-      </c>
-      <c r="C120">
-        <v>50.30315431564902</v>
-      </c>
-      <c r="D120" t="s">
-        <v>114</v>
-      </c>
-      <c r="E120" t="s">
-        <v>133</v>
-      </c>
-      <c r="F120" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121" t="s">
-        <v>40</v>
-      </c>
-      <c r="B121">
-        <v>1800</v>
-      </c>
-      <c r="C121">
-        <v>50.30315431564902</v>
-      </c>
-      <c r="D121" t="s">
-        <v>114</v>
-      </c>
-      <c r="E121" t="s">
-        <v>133</v>
-      </c>
-      <c r="F121" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122" t="s">
-        <v>38</v>
-      </c>
-      <c r="B122">
-        <v>3150</v>
-      </c>
-      <c r="C122">
-        <v>50.30315431564902</v>
-      </c>
-      <c r="D122" t="s">
-        <v>114</v>
-      </c>
-      <c r="E122" t="s">
-        <v>133</v>
-      </c>
-      <c r="F122" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123" t="s">
-        <v>54</v>
-      </c>
-      <c r="B123">
-        <v>2600</v>
-      </c>
-      <c r="C123">
-        <v>50.30315431564902</v>
-      </c>
-      <c r="D123" t="s">
-        <v>114</v>
-      </c>
-      <c r="E123" t="s">
-        <v>133</v>
-      </c>
-      <c r="F123" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124" t="s">
-        <v>35</v>
-      </c>
-      <c r="B124">
-        <v>3150</v>
-      </c>
-      <c r="C124">
-        <v>50.30315431564902</v>
-      </c>
-      <c r="D124" t="s">
-        <v>114</v>
-      </c>
-      <c r="E124" t="s">
-        <v>133</v>
-      </c>
-      <c r="F124" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125" t="s">
-        <v>34</v>
-      </c>
-      <c r="B125">
-        <v>2900</v>
-      </c>
-      <c r="C125">
-        <v>50.30315431564902</v>
-      </c>
-      <c r="D125" t="s">
-        <v>114</v>
-      </c>
-      <c r="E125" t="s">
-        <v>133</v>
-      </c>
-      <c r="F125" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126" t="s">
-        <v>52</v>
-      </c>
-      <c r="B126">
-        <v>2500</v>
-      </c>
-      <c r="C126">
-        <v>50.30315431564902</v>
-      </c>
-      <c r="D126" t="s">
-        <v>114</v>
-      </c>
-      <c r="E126" t="s">
-        <v>133</v>
-      </c>
-      <c r="F126" t="s">
+      <c r="D128" t="s">
+        <v>116</v>
+      </c>
+      <c r="E128" t="s">
+        <v>135</v>
+      </c>
+      <c r="F128" t="s">
         <v>150</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127" t="s">
-        <v>21</v>
-      </c>
-      <c r="B127">
-        <v>3100</v>
-      </c>
-      <c r="C127">
-        <v>56.09574693011376</v>
-      </c>
-      <c r="D127" t="s">
-        <v>114</v>
-      </c>
-      <c r="E127" t="s">
-        <v>133</v>
-      </c>
-      <c r="F127" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128" t="s">
-        <v>17</v>
-      </c>
-      <c r="B128">
-        <v>2200</v>
-      </c>
-      <c r="C128">
-        <v>56.09574693011376</v>
-      </c>
-      <c r="D128" t="s">
-        <v>114</v>
-      </c>
-      <c r="E128" t="s">
-        <v>133</v>
-      </c>
-      <c r="F128" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="B129">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C129">
-        <v>56.09574693011376</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D129" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E129" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F129" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="B130">
-        <v>2750</v>
+        <v>2600</v>
       </c>
       <c r="C130">
-        <v>56.09574693011376</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D130" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E130" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F130" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B131">
-        <v>2250</v>
+        <v>2300</v>
       </c>
       <c r="C131">
-        <v>56.09574693011376</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D131" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E131" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F131" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B132">
-        <v>2900</v>
+        <v>2250</v>
       </c>
       <c r="C132">
-        <v>56.09574693011376</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D132" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E132" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F132" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B133">
-        <v>1800</v>
+        <v>3150</v>
       </c>
       <c r="C133">
-        <v>56.09574693011376</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D133" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E133" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F133" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="B134">
-        <v>2600</v>
+        <v>3150</v>
       </c>
       <c r="C134">
-        <v>10284.73661716383</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D134" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E134" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F134" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B135">
-        <v>550</v>
+        <v>2900</v>
       </c>
       <c r="C135">
-        <v>10284.73661716383</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D135" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E135" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F135" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B136">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C136">
-        <v>56.09574693011376</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D136" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E136" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F136" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="B137">
         <v>2250</v>
       </c>
       <c r="C137">
-        <v>10284.89209676953</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D137" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E137" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F137" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="B138">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="C138">
-        <v>10284.89209676953</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D138" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E138" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F138" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B139">
-        <v>3150</v>
+        <v>3250</v>
       </c>
       <c r="C139">
-        <v>10284.73661716383</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D139" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E139" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F139" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="B140">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="C140">
-        <v>10284.73661716383</v>
+        <v>55.17460674463854</v>
       </c>
       <c r="D140" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E140" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F140" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="B141">
-        <v>1150</v>
+        <v>2600</v>
       </c>
       <c r="C141">
-        <v>10284.73661716383</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D141" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E141" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F141" t="s">
         <v>150</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B142">
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="C142">
         <v>50.30315431564902</v>
@@ -3706,18 +3706,18 @@
         <v>135</v>
       </c>
       <c r="F142" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="B143">
-        <v>1350</v>
+        <v>2500</v>
       </c>
       <c r="C143">
-        <v>56.09574693011376</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D143" t="s">
         <v>116</v>
@@ -3726,15 +3726,15 @@
         <v>135</v>
       </c>
       <c r="F143" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B144">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C144">
         <v>50.30315431564902</v>
@@ -3746,15 +3746,15 @@
         <v>135</v>
       </c>
       <c r="F144" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B145">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="C145">
         <v>50.30315431564902</v>
@@ -3766,15 +3766,15 @@
         <v>135</v>
       </c>
       <c r="F145" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B146">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C146">
         <v>50.30315431564902</v>
@@ -3786,18 +3786,18 @@
         <v>135</v>
       </c>
       <c r="F146" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="B147">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C147">
-        <v>10229.86188614189</v>
+        <v>0</v>
       </c>
       <c r="D147" t="s">
         <v>117</v>
@@ -3805,19 +3805,19 @@
       <c r="E147" t="s">
         <v>136</v>
       </c>
-      <c r="G147" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7">
+      <c r="F147" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="B148">
-        <v>1800</v>
+        <v>3050</v>
       </c>
       <c r="C148">
-        <v>10229.86188614189</v>
+        <v>0</v>
       </c>
       <c r="D148" t="s">
         <v>117</v>
@@ -3825,19 +3825,19 @@
       <c r="E148" t="s">
         <v>136</v>
       </c>
-      <c r="G148" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7">
+      <c r="F148" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B149">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="C149">
-        <v>10229.86188614189</v>
+        <v>0</v>
       </c>
       <c r="D149" t="s">
         <v>117</v>
@@ -3845,465 +3845,465 @@
       <c r="E149" t="s">
         <v>136</v>
       </c>
-      <c r="G149" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7">
+      <c r="F149" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="B150">
-        <v>1800</v>
+        <v>750</v>
       </c>
       <c r="C150">
-        <v>10229.86188614189</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D150" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E150" t="s">
-        <v>136</v>
-      </c>
-      <c r="G150" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7">
+        <v>137</v>
+      </c>
+      <c r="F150" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="B151">
+        <v>3150</v>
+      </c>
+      <c r="C151">
+        <v>50.30315431564902</v>
+      </c>
+      <c r="D151" t="s">
+        <v>118</v>
+      </c>
+      <c r="E151" t="s">
+        <v>137</v>
+      </c>
+      <c r="F151" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" t="s">
+        <v>46</v>
+      </c>
+      <c r="B152">
+        <v>2250</v>
+      </c>
+      <c r="C152">
+        <v>50.30315431564902</v>
+      </c>
+      <c r="D152" t="s">
+        <v>118</v>
+      </c>
+      <c r="E152" t="s">
+        <v>137</v>
+      </c>
+      <c r="F152" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" t="s">
+        <v>17</v>
+      </c>
+      <c r="B153">
         <v>2500</v>
       </c>
-      <c r="C151">
-        <v>10229.86188614189</v>
-      </c>
-      <c r="D151" t="s">
-        <v>117</v>
-      </c>
-      <c r="E151" t="s">
-        <v>136</v>
-      </c>
-      <c r="G151" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7">
-      <c r="A152" t="s">
-        <v>68</v>
-      </c>
-      <c r="B152">
-        <v>2750</v>
-      </c>
-      <c r="C152">
-        <v>10229.86188614189</v>
-      </c>
-      <c r="D152" t="s">
-        <v>117</v>
-      </c>
-      <c r="E152" t="s">
-        <v>136</v>
-      </c>
-      <c r="G152" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7">
-      <c r="A153" t="s">
-        <v>74</v>
-      </c>
-      <c r="B153">
-        <v>3300</v>
-      </c>
       <c r="C153">
-        <v>10229.86188614189</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D153" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E153" t="s">
-        <v>136</v>
-      </c>
-      <c r="G153" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7">
+        <v>135</v>
+      </c>
+      <c r="F153" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="B154">
+        <v>1100</v>
+      </c>
+      <c r="C154">
+        <v>56.09574693011376</v>
+      </c>
+      <c r="D154" t="s">
+        <v>116</v>
+      </c>
+      <c r="E154" t="s">
+        <v>135</v>
+      </c>
+      <c r="F154" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" t="s">
+        <v>22</v>
+      </c>
+      <c r="B155">
         <v>2250</v>
       </c>
-      <c r="C154">
-        <v>10229.86188614189</v>
-      </c>
-      <c r="D154" t="s">
-        <v>117</v>
-      </c>
-      <c r="E154" t="s">
-        <v>136</v>
-      </c>
-      <c r="G154" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7">
-      <c r="A155" t="s">
-        <v>73</v>
-      </c>
-      <c r="B155">
-        <v>2100</v>
-      </c>
       <c r="C155">
-        <v>10229.86188614189</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D155" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E155" t="s">
-        <v>136</v>
-      </c>
-      <c r="G155" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7">
+        <v>135</v>
+      </c>
+      <c r="F155" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="B156">
-        <v>3250</v>
+        <v>3150</v>
       </c>
       <c r="C156">
-        <v>10229.86188614189</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D156" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E156" t="s">
-        <v>136</v>
-      </c>
-      <c r="G156" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7">
+        <v>135</v>
+      </c>
+      <c r="F156" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="B157">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="C157">
-        <v>10229.86188614189</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D157" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E157" t="s">
-        <v>136</v>
-      </c>
-      <c r="G157" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7">
+        <v>135</v>
+      </c>
+      <c r="F157" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="B158">
-        <v>2900</v>
+        <v>2250</v>
       </c>
       <c r="C158">
-        <v>10229.86188614189</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D158" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E158" t="s">
-        <v>136</v>
-      </c>
-      <c r="G158" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7">
+        <v>135</v>
+      </c>
+      <c r="F158" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B159">
         <v>2250</v>
       </c>
       <c r="C159">
-        <v>10229.86188614189</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D159" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E159" t="s">
-        <v>136</v>
-      </c>
-      <c r="G159" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7">
+        <v>138</v>
+      </c>
+      <c r="F159" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B160">
-        <v>2900</v>
+        <v>1800</v>
       </c>
       <c r="C160">
-        <v>101.0490418703856</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D160" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E160" t="s">
-        <v>136</v>
-      </c>
-      <c r="G160" t="s">
-        <v>155</v>
+        <v>138</v>
+      </c>
+      <c r="F160" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="B161">
         <v>2600</v>
       </c>
       <c r="C161">
-        <v>101.0490418703856</v>
+        <v>55.17460674463854</v>
       </c>
       <c r="D161" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E161" t="s">
-        <v>136</v>
-      </c>
-      <c r="G161" t="s">
-        <v>155</v>
+        <v>139</v>
+      </c>
+      <c r="F161" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="B162">
-        <v>2250</v>
+        <v>1800</v>
       </c>
       <c r="C162">
-        <v>10229.86188614189</v>
+        <v>55.17460674463854</v>
       </c>
       <c r="D162" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E162" t="s">
-        <v>136</v>
-      </c>
-      <c r="G162" t="s">
-        <v>155</v>
+        <v>139</v>
+      </c>
+      <c r="F162" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="B163">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="C163">
-        <v>10229.86188614189</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D163" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E163" t="s">
-        <v>136</v>
-      </c>
-      <c r="G163" t="s">
-        <v>155</v>
+        <v>139</v>
+      </c>
+      <c r="F163" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="B164">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="C164">
-        <v>10229.86188614189</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D164" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E164" t="s">
-        <v>136</v>
-      </c>
-      <c r="G164" t="s">
-        <v>155</v>
+        <v>139</v>
+      </c>
+      <c r="F164" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="B165">
-        <v>3150</v>
+        <v>50</v>
       </c>
       <c r="C165">
-        <v>95.89167399587038</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D165" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E165" t="s">
-        <v>136</v>
-      </c>
-      <c r="G165" t="s">
-        <v>155</v>
+        <v>139</v>
+      </c>
+      <c r="F165" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B166">
-        <v>3150</v>
+        <v>2300</v>
       </c>
       <c r="C166">
-        <v>95.89167399587038</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D166" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E166" t="s">
-        <v>136</v>
-      </c>
-      <c r="G166" t="s">
-        <v>155</v>
+        <v>139</v>
+      </c>
+      <c r="F166" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="B167">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D167" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E167" t="s">
-        <v>137</v>
-      </c>
-      <c r="G167" t="s">
-        <v>156</v>
+        <v>139</v>
+      </c>
+      <c r="F167" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="B168">
         <v>3150</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D168" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E168" t="s">
-        <v>137</v>
-      </c>
-      <c r="G168" t="s">
-        <v>156</v>
+        <v>139</v>
+      </c>
+      <c r="F168" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="169" spans="1:7">
       <c r="A169" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="B169">
-        <v>2600</v>
+        <v>2750</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D169" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E169" t="s">
-        <v>137</v>
-      </c>
-      <c r="G169" t="s">
-        <v>156</v>
+        <v>139</v>
+      </c>
+      <c r="F169" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="170" spans="1:7">
       <c r="A170" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="B170">
-        <v>2900</v>
+        <v>3150</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D170" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E170" t="s">
-        <v>137</v>
-      </c>
-      <c r="G170" t="s">
-        <v>157</v>
+        <v>139</v>
+      </c>
+      <c r="F170" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B171">
         <v>2500</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D171" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E171" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G171" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="172" spans="1:7">
       <c r="A172" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B172">
         <v>2250</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D172" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E172" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G172" t="s">
         <v>158</v>
@@ -4311,19 +4311,19 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B173">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D173" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E173" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G173" t="s">
         <v>158</v>
@@ -4331,79 +4331,79 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B174">
-        <v>2250</v>
+        <v>4750</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D174" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E174" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G174" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="175" spans="1:7">
       <c r="A175" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B175">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D175" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E175" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G175" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="176" spans="1:7">
       <c r="A176" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="B176">
-        <v>3150</v>
+        <v>2500</v>
       </c>
       <c r="C176">
-        <v>10286.02331245808</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D176" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E176" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G176" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="177" spans="1:7">
       <c r="A177" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B177">
-        <v>1800</v>
+        <v>2750</v>
       </c>
       <c r="C177">
-        <v>10286.02331245808</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D177" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E177" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G177" t="s">
         <v>159</v>
@@ -4411,19 +4411,19 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="B178">
-        <v>250</v>
+        <v>2100</v>
       </c>
       <c r="C178">
-        <v>10286.02331245808</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D178" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E178" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G178" t="s">
         <v>159</v>
@@ -4431,353 +4431,353 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="B179">
-        <v>2150</v>
+        <v>2250</v>
       </c>
       <c r="C179">
-        <v>50.30315431564902</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D179" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E179" t="s">
-        <v>138</v>
-      </c>
-      <c r="F179" t="s">
-        <v>149</v>
+        <v>140</v>
+      </c>
+      <c r="G179" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="B180">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C180">
-        <v>50.30315431564902</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D180" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E180" t="s">
-        <v>138</v>
-      </c>
-      <c r="F180" t="s">
-        <v>149</v>
+        <v>140</v>
+      </c>
+      <c r="G180" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="181" spans="1:7">
       <c r="A181" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="B181">
-        <v>3250</v>
+        <v>1800</v>
       </c>
       <c r="C181">
-        <v>50.30315431564902</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D181" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E181" t="s">
-        <v>138</v>
-      </c>
-      <c r="F181" t="s">
-        <v>149</v>
+        <v>140</v>
+      </c>
+      <c r="G181" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="182" spans="1:7">
       <c r="A182" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B182">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C182">
-        <v>10284.73661716383</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D182" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E182" t="s">
-        <v>138</v>
-      </c>
-      <c r="F182" t="s">
-        <v>150</v>
+        <v>140</v>
+      </c>
+      <c r="G182" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="B183">
-        <v>3300</v>
+        <v>3150</v>
       </c>
       <c r="C183">
-        <v>10284.73661716383</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D183" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E183" t="s">
-        <v>138</v>
-      </c>
-      <c r="F183" t="s">
-        <v>150</v>
+        <v>140</v>
+      </c>
+      <c r="G183" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B184">
         <v>2500</v>
       </c>
       <c r="C184">
-        <v>10284.73661716383</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D184" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E184" t="s">
-        <v>138</v>
-      </c>
-      <c r="F184" t="s">
-        <v>150</v>
+        <v>140</v>
+      </c>
+      <c r="G184" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="185" spans="1:7">
       <c r="A185" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B185">
-        <v>2500</v>
+        <v>2100</v>
       </c>
       <c r="C185">
-        <v>10284.73661716383</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D185" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E185" t="s">
-        <v>138</v>
-      </c>
-      <c r="F185" t="s">
-        <v>147</v>
+        <v>140</v>
+      </c>
+      <c r="G185" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B186">
-        <v>2500</v>
+        <v>2100</v>
       </c>
       <c r="C186">
-        <v>10284.73661716383</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D186" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E186" t="s">
-        <v>138</v>
-      </c>
-      <c r="F186" t="s">
-        <v>147</v>
+        <v>140</v>
+      </c>
+      <c r="G186" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B187">
-        <v>2750</v>
+        <v>2700</v>
       </c>
       <c r="C187">
-        <v>10284.73661716383</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D187" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E187" t="s">
-        <v>138</v>
-      </c>
-      <c r="F187" t="s">
-        <v>150</v>
+        <v>140</v>
+      </c>
+      <c r="G187" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="B188">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C188">
-        <v>55.17460674463854</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D188" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E188" t="s">
-        <v>139</v>
-      </c>
-      <c r="F188" t="s">
-        <v>146</v>
+        <v>140</v>
+      </c>
+      <c r="G188" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="B189">
-        <v>500</v>
+        <v>2900</v>
       </c>
       <c r="C189">
-        <v>55.17460674463854</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D189" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E189" t="s">
-        <v>139</v>
-      </c>
-      <c r="F189" t="s">
-        <v>146</v>
+        <v>140</v>
+      </c>
+      <c r="G189" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="B190">
-        <v>3150</v>
+        <v>2600</v>
       </c>
       <c r="C190">
-        <v>55.17460674463854</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D190" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E190" t="s">
-        <v>139</v>
-      </c>
-      <c r="F190" t="s">
-        <v>147</v>
+        <v>140</v>
+      </c>
+      <c r="G190" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="B191">
-        <v>2500</v>
+        <v>800</v>
       </c>
       <c r="C191">
-        <v>10229.86188614189</v>
+        <v>117.129363815579</v>
       </c>
       <c r="D191" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E191" t="s">
-        <v>136</v>
-      </c>
-      <c r="G191" t="s">
-        <v>160</v>
+        <v>141</v>
+      </c>
+      <c r="F191" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="192" spans="1:7">
       <c r="A192" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B192">
-        <v>2250</v>
+        <v>2200</v>
       </c>
       <c r="C192">
-        <v>10229.86188614189</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D192" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E192" t="s">
-        <v>136</v>
-      </c>
-      <c r="G192" t="s">
-        <v>160</v>
+        <v>141</v>
+      </c>
+      <c r="F192" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B193">
-        <v>2250</v>
+        <v>2750</v>
       </c>
       <c r="C193">
-        <v>10229.86188614189</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D193" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E193" t="s">
-        <v>136</v>
-      </c>
-      <c r="G193" t="s">
-        <v>160</v>
+        <v>141</v>
+      </c>
+      <c r="F193" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="194" spans="1:7">
       <c r="A194" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="B194">
-        <v>1200</v>
+        <v>2900</v>
       </c>
       <c r="C194">
-        <v>10229.86188614189</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D194" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E194" t="s">
-        <v>136</v>
-      </c>
-      <c r="G194" t="s">
-        <v>160</v>
+        <v>141</v>
+      </c>
+      <c r="F194" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="195" spans="1:7">
       <c r="A195" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B195">
-        <v>2750</v>
+        <v>3150</v>
       </c>
       <c r="C195">
-        <v>10284.73661716383</v>
+        <v>117.129363815579</v>
       </c>
       <c r="D195" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E195" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F195" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="196" spans="1:7">
       <c r="A196" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="B196">
-        <v>3150</v>
+        <v>3300</v>
       </c>
       <c r="C196">
-        <v>10284.73661716383</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D196" t="s">
         <v>121</v>
@@ -4785,19 +4785,19 @@
       <c r="E196" t="s">
         <v>140</v>
       </c>
-      <c r="F196" t="s">
-        <v>151</v>
+      <c r="G196" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="197" spans="1:7">
       <c r="A197" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B197">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="C197">
-        <v>10284.73661716383</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D197" t="s">
         <v>121</v>
@@ -4805,19 +4805,19 @@
       <c r="E197" t="s">
         <v>140</v>
       </c>
-      <c r="F197" t="s">
-        <v>151</v>
+      <c r="G197" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="198" spans="1:7">
       <c r="A198" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B198">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="C198">
-        <v>10284.73661716383</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D198" t="s">
         <v>121</v>
@@ -4825,56 +4825,56 @@
       <c r="E198" t="s">
         <v>140</v>
       </c>
-      <c r="F198" t="s">
-        <v>151</v>
+      <c r="G198" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="199" spans="1:7">
       <c r="A199" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="B199">
-        <v>1150</v>
+        <v>3150</v>
       </c>
       <c r="C199">
-        <v>10284.73661716383</v>
+        <v>5.315090988968437</v>
       </c>
       <c r="D199" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E199" t="s">
-        <v>141</v>
-      </c>
-      <c r="F199" t="s">
-        <v>151</v>
+        <v>142</v>
+      </c>
+      <c r="G199" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="200" spans="1:7">
       <c r="A200" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B200">
-        <v>2900</v>
+        <v>3150</v>
       </c>
       <c r="C200">
-        <v>10284.73661716383</v>
+        <v>5.315090988968437</v>
       </c>
       <c r="D200" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E200" t="s">
-        <v>141</v>
-      </c>
-      <c r="F200" t="s">
-        <v>151</v>
+        <v>142</v>
+      </c>
+      <c r="G200" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="201" spans="1:7">
       <c r="A201" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B201">
-        <v>2100</v>
+        <v>2600</v>
       </c>
       <c r="C201">
         <v>5.315090988968437</v>
@@ -4886,15 +4886,15 @@
         <v>142</v>
       </c>
       <c r="G201" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="202" spans="1:7">
       <c r="A202" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="B202">
-        <v>3150</v>
+        <v>2500</v>
       </c>
       <c r="C202">
         <v>5.315090988968437</v>
@@ -4906,15 +4906,15 @@
         <v>142</v>
       </c>
       <c r="G202" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B203">
-        <v>1550</v>
+        <v>3250</v>
       </c>
       <c r="C203">
         <v>5.315090988968437</v>
@@ -4926,15 +4926,15 @@
         <v>142</v>
       </c>
       <c r="G203" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B204">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C204">
         <v>5.315090988968437</v>
@@ -4946,15 +4946,15 @@
         <v>142</v>
       </c>
       <c r="G204" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B205">
-        <v>4750</v>
+        <v>2100</v>
       </c>
       <c r="C205">
         <v>5.315090988968437</v>
@@ -4966,15 +4966,15 @@
         <v>142</v>
       </c>
       <c r="G205" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B206">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="C206">
         <v>5.315090988968437</v>
@@ -4986,15 +4986,15 @@
         <v>142</v>
       </c>
       <c r="G206" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="207" spans="1:7">
       <c r="A207" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="B207">
-        <v>3150</v>
+        <v>3500</v>
       </c>
       <c r="C207">
         <v>5.315090988968437</v>
@@ -5006,15 +5006,15 @@
         <v>142</v>
       </c>
       <c r="G207" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="208" spans="1:7">
       <c r="A208" t="s">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="B208">
-        <v>2700</v>
+        <v>100</v>
       </c>
       <c r="C208">
         <v>5.315090988968437</v>
@@ -5026,15 +5026,15 @@
         <v>142</v>
       </c>
       <c r="G208" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="209" spans="1:7">
       <c r="A209" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B209">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C209">
         <v>5.315090988968437</v>
@@ -5046,12 +5046,12 @@
         <v>142</v>
       </c>
       <c r="G209" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="210" spans="1:7">
       <c r="A210" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B210">
         <v>2250</v>
@@ -5066,15 +5066,15 @@
         <v>142</v>
       </c>
       <c r="G210" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="211" spans="1:7">
       <c r="A211" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B211">
-        <v>2250</v>
+        <v>1800</v>
       </c>
       <c r="C211">
         <v>5.315090988968437</v>
@@ -5086,35 +5086,35 @@
         <v>142</v>
       </c>
       <c r="G211" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="212" spans="1:7">
       <c r="A212" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="B212">
-        <v>2100</v>
+        <v>3300</v>
       </c>
       <c r="C212">
-        <v>5.315090988968437</v>
+        <v>0</v>
       </c>
       <c r="D212" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E212" t="s">
-        <v>142</v>
-      </c>
-      <c r="G212" t="s">
-        <v>160</v>
+        <v>143</v>
+      </c>
+      <c r="F212" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="213" spans="1:7">
       <c r="A213" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="B213">
-        <v>1800</v>
+        <v>3150</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -5126,15 +5126,15 @@
         <v>143</v>
       </c>
       <c r="F213" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="214" spans="1:7">
       <c r="A214" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="B214">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -5146,15 +5146,15 @@
         <v>143</v>
       </c>
       <c r="F214" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="215" spans="1:7">
       <c r="A215" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="B215">
-        <v>3150</v>
+        <v>2100</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -5166,15 +5166,15 @@
         <v>143</v>
       </c>
       <c r="F215" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="216" spans="1:7">
       <c r="A216" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="B216">
-        <v>1800</v>
+        <v>2900</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -5186,15 +5186,15 @@
         <v>143</v>
       </c>
       <c r="F216" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="217" spans="1:7">
       <c r="A217" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B217">
-        <v>2500</v>
+        <v>2100</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -5206,15 +5206,15 @@
         <v>143</v>
       </c>
       <c r="F217" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="218" spans="1:7">
       <c r="A218" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="B218">
-        <v>2750</v>
+        <v>3150</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -5226,15 +5226,15 @@
         <v>143</v>
       </c>
       <c r="F218" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="219" spans="1:7">
       <c r="A219" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="B219">
-        <v>2100</v>
+        <v>2600</v>
       </c>
       <c r="C219">
         <v>0</v>
@@ -5246,15 +5246,15 @@
         <v>143</v>
       </c>
       <c r="F219" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="220" spans="1:7">
       <c r="A220" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="B220">
-        <v>2900</v>
+        <v>1800</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -5266,15 +5266,15 @@
         <v>143</v>
       </c>
       <c r="F220" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="221" spans="1:7">
       <c r="A221" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="B221">
-        <v>2100</v>
+        <v>3300</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -5286,15 +5286,15 @@
         <v>143</v>
       </c>
       <c r="F221" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="222" spans="1:7">
       <c r="A222" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="B222">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -5306,15 +5306,15 @@
         <v>143</v>
       </c>
       <c r="F222" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="223" spans="1:7">
       <c r="A223" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="B223">
-        <v>2100</v>
+        <v>4750</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -5326,15 +5326,15 @@
         <v>143</v>
       </c>
       <c r="F223" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="224" spans="1:7">
       <c r="A224" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B224">
-        <v>2900</v>
+        <v>2250</v>
       </c>
       <c r="C224">
         <v>0</v>
@@ -5346,15 +5346,15 @@
         <v>143</v>
       </c>
       <c r="F224" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="225" spans="1:7">
       <c r="A225" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B225">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -5366,12 +5366,12 @@
         <v>143</v>
       </c>
       <c r="F225" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="226" spans="1:7">
       <c r="A226" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="B226">
         <v>2250</v>
@@ -5386,15 +5386,15 @@
         <v>143</v>
       </c>
       <c r="F226" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="227" spans="1:7">
       <c r="A227" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B227">
-        <v>2600</v>
+        <v>2100</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -5406,15 +5406,15 @@
         <v>143</v>
       </c>
       <c r="F227" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="228" spans="1:7">
       <c r="A228" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B228">
-        <v>3150</v>
+        <v>2500</v>
       </c>
       <c r="C228">
         <v>0</v>
@@ -5426,15 +5426,15 @@
         <v>143</v>
       </c>
       <c r="F228" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="229" spans="1:7">
       <c r="A229" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="B229">
-        <v>3300</v>
+        <v>1800</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -5446,15 +5446,15 @@
         <v>143</v>
       </c>
       <c r="F229" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="230" spans="1:7">
       <c r="A230" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="B230">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -5466,58 +5466,58 @@
         <v>143</v>
       </c>
       <c r="F230" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="231" spans="1:7">
       <c r="A231" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="B231">
-        <v>3150</v>
+        <v>3250</v>
       </c>
       <c r="C231">
-        <v>0</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D231" t="s">
         <v>124</v>
       </c>
       <c r="E231" t="s">
-        <v>143</v>
-      </c>
-      <c r="F231" t="s">
-        <v>148</v>
+        <v>144</v>
+      </c>
+      <c r="G231" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="232" spans="1:7">
       <c r="A232" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="B232">
-        <v>3250</v>
+        <v>2250</v>
       </c>
       <c r="C232">
-        <v>0</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D232" t="s">
         <v>124</v>
       </c>
       <c r="E232" t="s">
-        <v>143</v>
-      </c>
-      <c r="F232" t="s">
-        <v>148</v>
+        <v>144</v>
+      </c>
+      <c r="G232" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="233" spans="1:7">
       <c r="A233" t="s">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="B233">
-        <v>2900</v>
+        <v>3100</v>
       </c>
       <c r="C233">
-        <v>0</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D233" t="s">
         <v>124</v>
@@ -5526,18 +5526,18 @@
         <v>144</v>
       </c>
       <c r="G233" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="234" spans="1:7">
       <c r="A234" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="B234">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C234">
-        <v>0</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D234" t="s">
         <v>124</v>
@@ -5546,15 +5546,15 @@
         <v>144</v>
       </c>
       <c r="G234" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="235" spans="1:7">
       <c r="A235" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="B235">
-        <v>2150</v>
+        <v>2300</v>
       </c>
       <c r="C235">
         <v>0</v>
@@ -5566,15 +5566,15 @@
         <v>144</v>
       </c>
       <c r="G235" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="236" spans="1:7">
       <c r="A236" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B236">
-        <v>3300</v>
+        <v>1800</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -5586,15 +5586,15 @@
         <v>144</v>
       </c>
       <c r="G236" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="237" spans="1:7">
       <c r="A237" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="B237">
-        <v>2750</v>
+        <v>2500</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -5606,15 +5606,15 @@
         <v>144</v>
       </c>
       <c r="G237" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="238" spans="1:7">
       <c r="A238" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B238">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -5626,18 +5626,18 @@
         <v>144</v>
       </c>
       <c r="G238" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="239" spans="1:7">
       <c r="A239" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="B239">
-        <v>2750</v>
+        <v>2500</v>
       </c>
       <c r="C239">
-        <v>10228.71383241515</v>
+        <v>0</v>
       </c>
       <c r="D239" t="s">
         <v>124</v>
@@ -5646,15 +5646,15 @@
         <v>144</v>
       </c>
       <c r="G239" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="240" spans="1:7">
       <c r="A240" t="s">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="B240">
-        <v>2750</v>
+        <v>2250</v>
       </c>
       <c r="C240">
         <v>10228.71383241515</v>
@@ -5666,15 +5666,15 @@
         <v>144</v>
       </c>
       <c r="G240" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="241" spans="1:7">
       <c r="A241" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="B241">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -5686,15 +5686,15 @@
         <v>144</v>
       </c>
       <c r="G241" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="242" spans="1:7">
       <c r="A242" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="B242">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -5706,15 +5706,15 @@
         <v>144</v>
       </c>
       <c r="G242" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="243" spans="1:7">
       <c r="A243" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="B243">
-        <v>3250</v>
+        <v>3150</v>
       </c>
       <c r="C243">
         <v>0</v>
@@ -5726,18 +5726,18 @@
         <v>144</v>
       </c>
       <c r="G243" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="244" spans="1:7">
       <c r="A244" t="s">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="B244">
-        <v>3150</v>
+        <v>2750</v>
       </c>
       <c r="C244">
-        <v>10228.71383241515</v>
+        <v>0</v>
       </c>
       <c r="D244" t="s">
         <v>124</v>
@@ -5746,18 +5746,18 @@
         <v>144</v>
       </c>
       <c r="G244" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="245" spans="1:7">
       <c r="A245" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B245">
-        <v>2750</v>
+        <v>2250</v>
       </c>
       <c r="C245">
-        <v>10228.71383241515</v>
+        <v>0</v>
       </c>
       <c r="D245" t="s">
         <v>124</v>
@@ -5766,15 +5766,15 @@
         <v>144</v>
       </c>
       <c r="G245" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="246" spans="1:7">
       <c r="A246" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="B246">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C246">
         <v>10228.71383241515</v>
@@ -5786,15 +5786,15 @@
         <v>144</v>
       </c>
       <c r="G246" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="247" spans="1:7">
       <c r="A247" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B247">
-        <v>2250</v>
+        <v>2900</v>
       </c>
       <c r="C247">
         <v>10228.71383241515</v>
@@ -5806,15 +5806,15 @@
         <v>144</v>
       </c>
       <c r="G247" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="248" spans="1:7">
       <c r="A248" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="B248">
-        <v>2100</v>
+        <v>2900</v>
       </c>
       <c r="C248">
         <v>10228.71383241515</v>
@@ -5826,15 +5826,15 @@
         <v>144</v>
       </c>
       <c r="G248" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="249" spans="1:7">
       <c r="A249" t="s">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="B249">
-        <v>2900</v>
+        <v>2100</v>
       </c>
       <c r="C249">
         <v>10228.71383241515</v>
@@ -5846,47 +5846,47 @@
         <v>144</v>
       </c>
       <c r="G249" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="250" spans="1:7">
       <c r="A250" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="B250">
-        <v>2600</v>
+        <v>2250</v>
       </c>
       <c r="C250">
-        <v>34.67893341108023</v>
+        <v>0</v>
       </c>
       <c r="D250" t="s">
         <v>124</v>
       </c>
       <c r="E250" t="s">
-        <v>144</v>
-      </c>
-      <c r="G250" t="s">
-        <v>161</v>
+        <v>143</v>
+      </c>
+      <c r="F250" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="251" spans="1:7">
       <c r="A251" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B251">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="C251">
-        <v>34.67893341108023</v>
+        <v>0</v>
       </c>
       <c r="D251" t="s">
         <v>124</v>
       </c>
       <c r="E251" t="s">
-        <v>144</v>
-      </c>
-      <c r="G251" t="s">
-        <v>161</v>
+        <v>143</v>
+      </c>
+      <c r="F251" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -5894,24 +5894,24 @@
         <v>85</v>
       </c>
       <c r="B252">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C252">
-        <v>146.7282500315447</v>
+        <v>0</v>
       </c>
       <c r="D252" t="s">
         <v>124</v>
       </c>
       <c r="E252" t="s">
-        <v>144</v>
-      </c>
-      <c r="G252" t="s">
-        <v>156</v>
+        <v>143</v>
+      </c>
+      <c r="F252" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="253" spans="1:7">
       <c r="A253" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B253">
         <v>2250</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B254">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C254">
         <v>0</v>
@@ -5946,15 +5946,15 @@
         <v>143</v>
       </c>
       <c r="F254" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="255" spans="1:7">
       <c r="A255" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="B255">
-        <v>2250</v>
+        <v>2750</v>
       </c>
       <c r="C255">
         <v>0</v>
@@ -5966,15 +5966,15 @@
         <v>143</v>
       </c>
       <c r="F255" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="256" spans="1:7">
       <c r="A256" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="B256">
-        <v>3500</v>
+        <v>3250</v>
       </c>
       <c r="C256">
         <v>0</v>
@@ -5989,9 +5989,9 @@
         <v>148</v>
       </c>
     </row>
-    <row r="257" spans="1:6">
+    <row r="257" spans="1:7">
       <c r="A257" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="B257">
         <v>3150</v>
@@ -6006,15 +6006,15 @@
         <v>143</v>
       </c>
       <c r="F257" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
       <c r="A258" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B258">
-        <v>4750</v>
+        <v>2250</v>
       </c>
       <c r="C258">
         <v>0</v>
@@ -6026,15 +6026,15 @@
         <v>143</v>
       </c>
       <c r="F258" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
       <c r="A259" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B259">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C259">
         <v>0</v>
@@ -6046,15 +6046,15 @@
         <v>143</v>
       </c>
       <c r="F259" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
       <c r="A260" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="B260">
-        <v>2250</v>
+        <v>2700</v>
       </c>
       <c r="C260">
         <v>0</v>
@@ -6066,15 +6066,15 @@
         <v>143</v>
       </c>
       <c r="F260" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
       <c r="A261" t="s">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="B261">
-        <v>3150</v>
+        <v>2500</v>
       </c>
       <c r="C261">
         <v>0</v>
@@ -6086,15 +6086,15 @@
         <v>143</v>
       </c>
       <c r="F261" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
       <c r="A262" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B262">
-        <v>2700</v>
+        <v>2250</v>
       </c>
       <c r="C262">
         <v>0</v>
@@ -6106,15 +6106,15 @@
         <v>143</v>
       </c>
       <c r="F262" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
       <c r="A263" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="B263">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="C263">
         <v>0</v>
@@ -6126,12 +6126,12 @@
         <v>143</v>
       </c>
       <c r="F263" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
       <c r="A264" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B264">
         <v>2250</v>
@@ -6146,15 +6146,15 @@
         <v>143</v>
       </c>
       <c r="F264" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
       <c r="A265" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B265">
-        <v>2600</v>
+        <v>1450</v>
       </c>
       <c r="C265">
         <v>0</v>
@@ -6169,9 +6169,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="266" spans="1:6">
+    <row r="266" spans="1:7">
       <c r="A266" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="B266">
         <v>2500</v>
@@ -6186,15 +6186,15 @@
         <v>143</v>
       </c>
       <c r="F266" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
       <c r="A267" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="B267">
-        <v>2250</v>
+        <v>2100</v>
       </c>
       <c r="C267">
         <v>0</v>
@@ -6209,12 +6209,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="268" spans="1:6">
+    <row r="268" spans="1:7">
       <c r="A268" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B268">
-        <v>2250</v>
+        <v>2750</v>
       </c>
       <c r="C268">
         <v>0</v>
@@ -6226,15 +6226,15 @@
         <v>143</v>
       </c>
       <c r="F268" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
       <c r="A269" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B269">
-        <v>1800</v>
+        <v>3150</v>
       </c>
       <c r="C269">
         <v>0</v>
@@ -6246,78 +6246,78 @@
         <v>143</v>
       </c>
       <c r="F269" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
       <c r="A270" t="s">
-        <v>103</v>
+        <v>29</v>
       </c>
       <c r="B270">
-        <v>2100</v>
+        <v>3150</v>
       </c>
       <c r="C270">
         <v>0</v>
       </c>
       <c r="D270" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E270" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F270" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
       <c r="A271" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="B271">
-        <v>300</v>
+        <v>850</v>
       </c>
       <c r="C271">
-        <v>0</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D271" t="s">
         <v>124</v>
       </c>
       <c r="E271" t="s">
-        <v>143</v>
-      </c>
-      <c r="F271" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6">
+        <v>144</v>
+      </c>
+      <c r="G271" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
       <c r="A272" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B272">
         <v>2100</v>
       </c>
       <c r="C272">
-        <v>0</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D272" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E272" t="s">
-        <v>145</v>
-      </c>
-      <c r="F272" t="s">
-        <v>148</v>
+        <v>144</v>
+      </c>
+      <c r="G272" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="273" spans="1:7">
       <c r="A273" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B273">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C273">
-        <v>10279.27513802618</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D273" t="s">
         <v>124</v>
@@ -6326,18 +6326,18 @@
         <v>144</v>
       </c>
       <c r="G273" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="274" spans="1:7">
       <c r="A274" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B274">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="C274">
-        <v>10279.27513802618</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D274" t="s">
         <v>124</v>
@@ -6346,18 +6346,18 @@
         <v>144</v>
       </c>
       <c r="G274" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="275" spans="1:7">
       <c r="A275" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="B275">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C275">
-        <v>10279.27513802618</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D275" t="s">
         <v>124</v>
@@ -6366,18 +6366,18 @@
         <v>144</v>
       </c>
       <c r="G275" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="276" spans="1:7">
       <c r="A276" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="B276">
-        <v>2500</v>
+        <v>2100</v>
       </c>
       <c r="C276">
-        <v>146.7282500315447</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D276" t="s">
         <v>124</v>
@@ -6386,18 +6386,18 @@
         <v>144</v>
       </c>
       <c r="G276" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="277" spans="1:7">
       <c r="A277" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="B277">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="C277">
-        <v>146.7282500315447</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D277" t="s">
         <v>124</v>
@@ -6406,18 +6406,18 @@
         <v>144</v>
       </c>
       <c r="G277" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="278" spans="1:7">
       <c r="A278" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="B278">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="C278">
-        <v>146.7282500315447</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D278" t="s">
         <v>124</v>
@@ -6426,18 +6426,18 @@
         <v>144</v>
       </c>
       <c r="G278" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="279" spans="1:7">
       <c r="A279" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="B279">
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="C279">
-        <v>146.7282500315447</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D279" t="s">
         <v>124</v>
@@ -6446,18 +6446,18 @@
         <v>144</v>
       </c>
       <c r="G279" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="280" spans="1:7">
       <c r="A280" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B280">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="C280">
-        <v>146.7282500315447</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D280" t="s">
         <v>124</v>
@@ -6466,18 +6466,18 @@
         <v>144</v>
       </c>
       <c r="G280" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="281" spans="1:7">
       <c r="A281" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="B281">
-        <v>2900</v>
+        <v>3250</v>
       </c>
       <c r="C281">
-        <v>146.7282500315447</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D281" t="s">
         <v>124</v>
@@ -6486,18 +6486,18 @@
         <v>144</v>
       </c>
       <c r="G281" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="282" spans="1:7">
       <c r="A282" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B282">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="C282">
-        <v>146.7282500315447</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D282" t="s">
         <v>124</v>
@@ -6506,18 +6506,18 @@
         <v>144</v>
       </c>
       <c r="G282" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="283" spans="1:7">
       <c r="A283" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="B283">
-        <v>2750</v>
+        <v>2100</v>
       </c>
       <c r="C283">
-        <v>102.7772492139699</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D283" t="s">
         <v>124</v>
@@ -6526,18 +6526,18 @@
         <v>144</v>
       </c>
       <c r="G283" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="284" spans="1:7">
       <c r="A284" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="B284">
-        <v>500</v>
+        <v>2250</v>
       </c>
       <c r="C284">
-        <v>102.7772492139699</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D284" t="s">
         <v>124</v>
@@ -6546,18 +6546,18 @@
         <v>144</v>
       </c>
       <c r="G284" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="285" spans="1:7">
       <c r="A285" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="B285">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C285">
-        <v>10279.27513802618</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D285" t="s">
         <v>124</v>
@@ -6566,18 +6566,18 @@
         <v>144</v>
       </c>
       <c r="G285" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="286" spans="1:7">
       <c r="A286" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="B286">
-        <v>2300</v>
+        <v>4750</v>
       </c>
       <c r="C286">
-        <v>10279.27513802618</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D286" t="s">
         <v>124</v>
@@ -6586,18 +6586,18 @@
         <v>144</v>
       </c>
       <c r="G286" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="287" spans="1:7">
       <c r="A287" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="B287">
-        <v>3100</v>
+        <v>2900</v>
       </c>
       <c r="C287">
-        <v>102.7772492139699</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D287" t="s">
         <v>124</v>
@@ -6606,18 +6606,18 @@
         <v>144</v>
       </c>
       <c r="G287" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="288" spans="1:7">
       <c r="A288" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B288">
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="C288">
-        <v>97.62540947766647</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D288" t="s">
         <v>124</v>
@@ -6626,18 +6626,18 @@
         <v>144</v>
       </c>
       <c r="G288" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="289" spans="1:7">
       <c r="A289" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B289">
         <v>3150</v>
       </c>
       <c r="C289">
-        <v>146.7282500315447</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D289" t="s">
         <v>124</v>
@@ -6646,55 +6646,55 @@
         <v>144</v>
       </c>
       <c r="G289" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="290" spans="1:7">
       <c r="A290" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="B290">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="C290">
-        <v>97.62540947766647</v>
+        <v>0</v>
       </c>
       <c r="D290" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E290" t="s">
-        <v>144</v>
-      </c>
-      <c r="G290" t="s">
-        <v>158</v>
+        <v>145</v>
+      </c>
+      <c r="F290" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="291" spans="1:7">
       <c r="A291" t="s">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="B291">
         <v>3150</v>
       </c>
       <c r="C291">
-        <v>97.62540947766647</v>
+        <v>0</v>
       </c>
       <c r="D291" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E291" t="s">
-        <v>144</v>
-      </c>
-      <c r="G291" t="s">
-        <v>158</v>
+        <v>145</v>
+      </c>
+      <c r="F291" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="292" spans="1:7">
       <c r="A292" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="B292">
-        <v>3250</v>
+        <v>2100</v>
       </c>
       <c r="C292">
         <v>0</v>
@@ -6711,10 +6711,10 @@
     </row>
     <row r="293" spans="1:7">
       <c r="A293" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="B293">
-        <v>2500</v>
+        <v>3100</v>
       </c>
       <c r="C293">
         <v>0</v>
@@ -6731,10 +6731,10 @@
     </row>
     <row r="294" spans="1:7">
       <c r="A294" t="s">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="B294">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="C294">
         <v>0</v>
@@ -6751,10 +6751,10 @@
     </row>
     <row r="295" spans="1:7">
       <c r="A295" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B295">
-        <v>2750</v>
+        <v>2250</v>
       </c>
       <c r="C295">
         <v>0</v>
@@ -6766,15 +6766,15 @@
         <v>145</v>
       </c>
       <c r="F295" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="296" spans="1:7">
       <c r="A296" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="B296">
-        <v>2150</v>
+        <v>3150</v>
       </c>
       <c r="C296">
         <v>0</v>
@@ -6786,15 +6786,15 @@
         <v>145</v>
       </c>
       <c r="F296" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="297" spans="1:7">
       <c r="A297" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="B297">
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="C297">
         <v>0</v>
@@ -6806,15 +6806,15 @@
         <v>145</v>
       </c>
       <c r="F297" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="298" spans="1:7">
       <c r="A298" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="B298">
-        <v>2750</v>
+        <v>2900</v>
       </c>
       <c r="C298">
         <v>0</v>
@@ -6826,15 +6826,15 @@
         <v>145</v>
       </c>
       <c r="F298" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="299" spans="1:7">
       <c r="A299" t="s">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="B299">
-        <v>3300</v>
+        <v>3150</v>
       </c>
       <c r="C299">
         <v>0</v>
@@ -6846,15 +6846,15 @@
         <v>145</v>
       </c>
       <c r="F299" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="300" spans="1:7">
       <c r="A300" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B300">
-        <v>2750</v>
+        <v>2100</v>
       </c>
       <c r="C300">
         <v>0</v>
@@ -6866,15 +6866,15 @@
         <v>145</v>
       </c>
       <c r="F300" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="301" spans="1:7">
       <c r="A301" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="B301">
-        <v>3150</v>
+        <v>2500</v>
       </c>
       <c r="C301">
         <v>0</v>
@@ -6886,15 +6886,15 @@
         <v>145</v>
       </c>
       <c r="F301" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="302" spans="1:7">
       <c r="A302" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="B302">
-        <v>2250</v>
+        <v>2600</v>
       </c>
       <c r="C302">
         <v>0</v>
@@ -6906,15 +6906,15 @@
         <v>145</v>
       </c>
       <c r="F302" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="303" spans="1:7">
       <c r="A303" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="B303">
-        <v>2900</v>
+        <v>2600</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -6926,15 +6926,15 @@
         <v>145</v>
       </c>
       <c r="F303" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="304" spans="1:7">
       <c r="A304" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="B304">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="C304">
         <v>0</v>
@@ -6946,15 +6946,15 @@
         <v>145</v>
       </c>
       <c r="F304" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="305" spans="1:6">
       <c r="A305" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="B305">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -6966,15 +6966,15 @@
         <v>145</v>
       </c>
       <c r="F305" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="306" spans="1:6">
       <c r="A306" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="B306">
-        <v>2250</v>
+        <v>1800</v>
       </c>
       <c r="C306">
         <v>0</v>
@@ -6991,7 +6991,7 @@
     </row>
     <row r="307" spans="1:6">
       <c r="A307" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B307">
         <v>2250</v>
@@ -7011,10 +7011,10 @@
     </row>
     <row r="308" spans="1:6">
       <c r="A308" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B308">
-        <v>2600</v>
+        <v>2900</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -7026,15 +7026,15 @@
         <v>145</v>
       </c>
       <c r="F308" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="309" spans="1:6">
       <c r="A309" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B309">
-        <v>2750</v>
+        <v>2500</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -7046,15 +7046,15 @@
         <v>145</v>
       </c>
       <c r="F309" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="310" spans="1:6">
       <c r="A310" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="B310">
-        <v>2500</v>
+        <v>3250</v>
       </c>
       <c r="C310">
         <v>0</v>
@@ -7066,18 +7066,18 @@
         <v>145</v>
       </c>
       <c r="F310" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="311" spans="1:6">
       <c r="A311" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="B311">
-        <v>3000</v>
+        <v>3150</v>
       </c>
       <c r="C311">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D311" t="s">
         <v>125</v>
@@ -7086,18 +7086,18 @@
         <v>145</v>
       </c>
       <c r="F311" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="312" spans="1:6">
       <c r="A312" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="B312">
-        <v>3150</v>
+        <v>3500</v>
       </c>
       <c r="C312">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D312" t="s">
         <v>125</v>
@@ -7106,15 +7106,15 @@
         <v>145</v>
       </c>
       <c r="F312" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="313" spans="1:6">
       <c r="A313" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="B313">
-        <v>2100</v>
+        <v>3150</v>
       </c>
       <c r="C313">
         <v>50.30315431564902</v>
@@ -7126,15 +7126,15 @@
         <v>145</v>
       </c>
       <c r="F313" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="314" spans="1:6">
       <c r="A314" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B314">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C314">
         <v>50.30315431564902</v>
@@ -7146,15 +7146,15 @@
         <v>145</v>
       </c>
       <c r="F314" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="315" spans="1:6">
       <c r="A315" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="B315">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C315">
         <v>50.30315431564902</v>
@@ -7166,15 +7166,15 @@
         <v>145</v>
       </c>
       <c r="F315" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="316" spans="1:6">
       <c r="A316" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="B316">
-        <v>3150</v>
+        <v>1800</v>
       </c>
       <c r="C316">
         <v>50.30315431564902</v>
@@ -7191,10 +7191,10 @@
     </row>
     <row r="317" spans="1:6">
       <c r="A317" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B317">
-        <v>1800</v>
+        <v>2500</v>
       </c>
       <c r="C317">
         <v>50.30315431564902</v>
@@ -7206,15 +7206,15 @@
         <v>145</v>
       </c>
       <c r="F317" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="318" spans="1:6">
       <c r="A318" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B318">
-        <v>3250</v>
+        <v>3150</v>
       </c>
       <c r="C318">
         <v>50.30315431564902</v>
@@ -7226,15 +7226,15 @@
         <v>145</v>
       </c>
       <c r="F318" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="319" spans="1:6">
       <c r="A319" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="B319">
-        <v>2600</v>
+        <v>2900</v>
       </c>
       <c r="C319">
         <v>50.30315431564902</v>
@@ -7246,15 +7246,15 @@
         <v>145</v>
       </c>
       <c r="F319" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="320" spans="1:6">
       <c r="A320" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="B320">
-        <v>2600</v>
+        <v>2250</v>
       </c>
       <c r="C320">
         <v>50.30315431564902</v>
@@ -7266,18 +7266,18 @@
         <v>145</v>
       </c>
       <c r="F320" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="321" spans="1:6">
       <c r="A321" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="B321">
-        <v>2500</v>
+        <v>2750</v>
       </c>
       <c r="C321">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D321" t="s">
         <v>125</v>
@@ -7286,15 +7286,15 @@
         <v>145</v>
       </c>
       <c r="F321" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="322" spans="1:6">
       <c r="A322" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="B322">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C322">
         <v>50.30315431564902</v>
@@ -7306,15 +7306,15 @@
         <v>145</v>
       </c>
       <c r="F322" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="323" spans="1:6">
       <c r="A323" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="B323">
-        <v>2250</v>
+        <v>1800</v>
       </c>
       <c r="C323">
         <v>50.30315431564902</v>
@@ -7326,15 +7326,15 @@
         <v>145</v>
       </c>
       <c r="F323" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="324" spans="1:6">
       <c r="A324" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B324">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C324">
         <v>50.30315431564902</v>
@@ -7346,15 +7346,15 @@
         <v>145</v>
       </c>
       <c r="F324" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="325" spans="1:6">
       <c r="A325" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B325">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="C325">
         <v>50.30315431564902</v>
@@ -7366,15 +7366,15 @@
         <v>145</v>
       </c>
       <c r="F325" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="326" spans="1:6">
       <c r="A326" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="B326">
-        <v>2250</v>
+        <v>2600</v>
       </c>
       <c r="C326">
         <v>50.30315431564902</v>
@@ -7386,15 +7386,15 @@
         <v>145</v>
       </c>
       <c r="F326" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="327" spans="1:6">
       <c r="A327" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="B327">
-        <v>2200</v>
+        <v>3500</v>
       </c>
       <c r="C327">
         <v>50.30315431564902</v>
@@ -7406,15 +7406,15 @@
         <v>145</v>
       </c>
       <c r="F327" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="328" spans="1:6">
       <c r="A328" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="B328">
-        <v>1800</v>
+        <v>2500</v>
       </c>
       <c r="C328">
         <v>50.30315431564902</v>
@@ -7426,12 +7426,12 @@
         <v>145</v>
       </c>
       <c r="F328" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="329" spans="1:6">
       <c r="A329" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="B329">
         <v>2250</v>
@@ -7451,10 +7451,10 @@
     </row>
     <row r="330" spans="1:6">
       <c r="A330" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B330">
-        <v>2900</v>
+        <v>2600</v>
       </c>
       <c r="C330">
         <v>50.30315431564902</v>
@@ -7471,10 +7471,10 @@
     </row>
     <row r="331" spans="1:6">
       <c r="A331" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B331">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="C331">
         <v>50.30315431564902</v>
@@ -7491,10 +7491,10 @@
     </row>
     <row r="332" spans="1:6">
       <c r="A332" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B332">
-        <v>3150</v>
+        <v>3250</v>
       </c>
       <c r="C332">
         <v>50.30315431564902</v>
@@ -7506,18 +7506,18 @@
         <v>145</v>
       </c>
       <c r="F332" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="333" spans="1:6">
       <c r="A333" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="B333">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="C333">
-        <v>114.8097329106024</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D333" t="s">
         <v>125</v>
@@ -7526,18 +7526,18 @@
         <v>145</v>
       </c>
       <c r="F333" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="334" spans="1:6">
       <c r="A334" t="s">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="B334">
-        <v>2700</v>
+        <v>3150</v>
       </c>
       <c r="C334">
-        <v>10284.89209676953</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D334" t="s">
         <v>125</v>
@@ -7546,18 +7546,18 @@
         <v>145</v>
       </c>
       <c r="F334" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="335" spans="1:6">
       <c r="A335" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B335">
-        <v>2250</v>
+        <v>2900</v>
       </c>
       <c r="C335">
-        <v>10284.89209676953</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D335" t="s">
         <v>125</v>
@@ -7566,18 +7566,18 @@
         <v>145</v>
       </c>
       <c r="F335" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="336" spans="1:6">
       <c r="A336" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="B336">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C336">
-        <v>10284.89209676953</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D336" t="s">
         <v>125</v>
@@ -7586,18 +7586,18 @@
         <v>145</v>
       </c>
       <c r="F336" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="337" spans="1:6">
       <c r="A337" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="B337">
-        <v>2100</v>
+        <v>3150</v>
       </c>
       <c r="C337">
-        <v>10284.89209676953</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D337" t="s">
         <v>125</v>
@@ -7606,18 +7606,18 @@
         <v>145</v>
       </c>
       <c r="F337" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="338" spans="1:6">
       <c r="A338" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="B338">
-        <v>3150</v>
+        <v>2100</v>
       </c>
       <c r="C338">
-        <v>10284.89209676953</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D338" t="s">
         <v>125</v>
@@ -7631,13 +7631,13 @@
     </row>
     <row r="339" spans="1:6">
       <c r="A339" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="B339">
-        <v>3250</v>
+        <v>2250</v>
       </c>
       <c r="C339">
-        <v>10284.89209676953</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D339" t="s">
         <v>125</v>
@@ -7646,18 +7646,18 @@
         <v>145</v>
       </c>
       <c r="F339" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="340" spans="1:6">
       <c r="A340" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B340">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C340">
-        <v>10284.89209676953</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D340" t="s">
         <v>125</v>
@@ -7671,13 +7671,13 @@
     </row>
     <row r="341" spans="1:6">
       <c r="A341" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="B341">
-        <v>2250</v>
+        <v>2750</v>
       </c>
       <c r="C341">
-        <v>10284.89209676953</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D341" t="s">
         <v>125</v>
@@ -7686,18 +7686,18 @@
         <v>145</v>
       </c>
       <c r="F341" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="342" spans="1:6">
       <c r="A342" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B342">
-        <v>2900</v>
+        <v>2200</v>
       </c>
       <c r="C342">
-        <v>10284.89209676953</v>
+        <v>10331.50326630582</v>
       </c>
       <c r="D342" t="s">
         <v>125</v>
@@ -7706,18 +7706,18 @@
         <v>145</v>
       </c>
       <c r="F342" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="343" spans="1:6">
       <c r="A343" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B343">
-        <v>2250</v>
+        <v>2150</v>
       </c>
       <c r="C343">
-        <v>10284.89209676953</v>
+        <v>10331.50326630582</v>
       </c>
       <c r="D343" t="s">
         <v>125</v>
@@ -7726,18 +7726,18 @@
         <v>145</v>
       </c>
       <c r="F343" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="344" spans="1:6">
       <c r="A344" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="B344">
-        <v>1800</v>
+        <v>2900</v>
       </c>
       <c r="C344">
-        <v>10284.89209676953</v>
+        <v>10331.50326630582</v>
       </c>
       <c r="D344" t="s">
         <v>125</v>
@@ -7746,18 +7746,18 @@
         <v>145</v>
       </c>
       <c r="F344" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="345" spans="1:6">
       <c r="A345" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="B345">
         <v>3150</v>
       </c>
       <c r="C345">
-        <v>10284.89209676953</v>
+        <v>10331.50326630582</v>
       </c>
       <c r="D345" t="s">
         <v>125</v>
@@ -7766,18 +7766,18 @@
         <v>145</v>
       </c>
       <c r="F345" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="346" spans="1:6">
       <c r="A346" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="B346">
         <v>2250</v>
       </c>
       <c r="C346">
-        <v>10284.89209676953</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D346" t="s">
         <v>125</v>
@@ -7786,18 +7786,18 @@
         <v>145</v>
       </c>
       <c r="F346" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="347" spans="1:6">
       <c r="A347" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B347">
-        <v>2250</v>
+        <v>2750</v>
       </c>
       <c r="C347">
-        <v>10284.89209676953</v>
+        <v>10331.50326630582</v>
       </c>
       <c r="D347" t="s">
         <v>125</v>
@@ -7806,18 +7806,18 @@
         <v>145</v>
       </c>
       <c r="F347" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="348" spans="1:6">
       <c r="A348" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="B348">
-        <v>2600</v>
+        <v>2250</v>
       </c>
       <c r="C348">
-        <v>10284.89209676953</v>
+        <v>114.8097329106024</v>
       </c>
       <c r="D348" t="s">
         <v>125</v>
@@ -7826,18 +7826,18 @@
         <v>145</v>
       </c>
       <c r="F348" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="349" spans="1:6">
       <c r="A349" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="B349">
-        <v>2100</v>
+        <v>2900</v>
       </c>
       <c r="C349">
-        <v>10284.89209676953</v>
+        <v>114.8097329106024</v>
       </c>
       <c r="D349" t="s">
         <v>125</v>
@@ -7846,18 +7846,18 @@
         <v>145</v>
       </c>
       <c r="F349" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="350" spans="1:6">
       <c r="A350" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B350">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="C350">
-        <v>10284.89209676953</v>
+        <v>114.8097329106024</v>
       </c>
       <c r="D350" t="s">
         <v>125</v>
@@ -7866,18 +7866,18 @@
         <v>145</v>
       </c>
       <c r="F350" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="351" spans="1:6">
       <c r="A351" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="B351">
-        <v>2750</v>
+        <v>2500</v>
       </c>
       <c r="C351">
-        <v>10284.89209676953</v>
+        <v>114.8097329106024</v>
       </c>
       <c r="D351" t="s">
         <v>125</v>
@@ -7886,18 +7886,18 @@
         <v>145</v>
       </c>
       <c r="F351" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="352" spans="1:6">
       <c r="A352" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="B352">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="C352">
-        <v>10284.89209676953</v>
+        <v>114.8097329106024</v>
       </c>
       <c r="D352" t="s">
         <v>125</v>
@@ -7906,18 +7906,18 @@
         <v>145</v>
       </c>
       <c r="F352" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="353" spans="1:6">
       <c r="A353" t="s">
-        <v>11</v>
+        <v>103</v>
       </c>
       <c r="B353">
-        <v>950</v>
+        <v>2100</v>
       </c>
       <c r="C353">
-        <v>10284.89209676953</v>
+        <v>114.8097329106024</v>
       </c>
       <c r="D353" t="s">
         <v>125</v>
@@ -7926,18 +7926,18 @@
         <v>145</v>
       </c>
       <c r="F353" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="354" spans="1:6">
       <c r="A354" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B354">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C354">
-        <v>10284.89209676953</v>
+        <v>114.8097329106024</v>
       </c>
       <c r="D354" t="s">
         <v>125</v>
@@ -7946,18 +7946,18 @@
         <v>145</v>
       </c>
       <c r="F354" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="355" spans="1:6">
       <c r="A355" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="B355">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C355">
-        <v>10284.89209676953</v>
+        <v>114.8097329106024</v>
       </c>
       <c r="D355" t="s">
         <v>125</v>
@@ -7966,18 +7966,18 @@
         <v>145</v>
       </c>
       <c r="F355" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="356" spans="1:6">
       <c r="A356" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="B356">
-        <v>3500</v>
+        <v>2300</v>
       </c>
       <c r="C356">
-        <v>10284.89209676953</v>
+        <v>114.8097329106024</v>
       </c>
       <c r="D356" t="s">
         <v>125</v>
@@ -7986,18 +7986,18 @@
         <v>145</v>
       </c>
       <c r="F356" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="357" spans="1:6">
       <c r="A357" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="B357">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C357">
-        <v>10284.89209676953</v>
+        <v>114.8097329106024</v>
       </c>
       <c r="D357" t="s">
         <v>125</v>
@@ -8006,15 +8006,15 @@
         <v>145</v>
       </c>
       <c r="F357" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="358" spans="1:6">
       <c r="A358" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="B358">
-        <v>2100</v>
+        <v>3150</v>
       </c>
       <c r="C358">
         <v>114.8097329106024</v>
@@ -8026,15 +8026,15 @@
         <v>145</v>
       </c>
       <c r="F358" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="359" spans="1:6">
       <c r="A359" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="B359">
-        <v>2150</v>
+        <v>2850</v>
       </c>
       <c r="C359">
         <v>114.8097329106024</v>
@@ -8046,15 +8046,15 @@
         <v>145</v>
       </c>
       <c r="F359" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="360" spans="1:6">
       <c r="A360" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="B360">
-        <v>3300</v>
+        <v>2500</v>
       </c>
       <c r="C360">
         <v>114.8097329106024</v>
@@ -8066,15 +8066,15 @@
         <v>145</v>
       </c>
       <c r="F360" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="361" spans="1:6">
       <c r="A361" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="B361">
-        <v>3250</v>
+        <v>3100</v>
       </c>
       <c r="C361">
         <v>114.8097329106024</v>
@@ -8086,15 +8086,15 @@
         <v>145</v>
       </c>
       <c r="F361" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="362" spans="1:6">
       <c r="A362" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="B362">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="C362">
         <v>114.8097329106024</v>
@@ -8106,15 +8106,15 @@
         <v>145</v>
       </c>
       <c r="F362" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="363" spans="1:6">
       <c r="A363" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="B363">
-        <v>2750</v>
+        <v>2250</v>
       </c>
       <c r="C363">
         <v>114.8097329106024</v>
@@ -8131,10 +8131,10 @@
     </row>
     <row r="364" spans="1:6">
       <c r="A364" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="B364">
-        <v>2750</v>
+        <v>2100</v>
       </c>
       <c r="C364">
         <v>114.8097329106024</v>
@@ -8146,86 +8146,6 @@
         <v>145</v>
       </c>
       <c r="F364" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="365" spans="1:6">
-      <c r="A365" t="s">
-        <v>75</v>
-      </c>
-      <c r="B365">
-        <v>3500</v>
-      </c>
-      <c r="C365">
-        <v>10284.89209676953</v>
-      </c>
-      <c r="D365" t="s">
-        <v>125</v>
-      </c>
-      <c r="E365" t="s">
-        <v>145</v>
-      </c>
-      <c r="F365" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="366" spans="1:6">
-      <c r="A366" t="s">
-        <v>30</v>
-      </c>
-      <c r="B366">
-        <v>2250</v>
-      </c>
-      <c r="C366">
-        <v>10284.89209676953</v>
-      </c>
-      <c r="D366" t="s">
-        <v>125</v>
-      </c>
-      <c r="E366" t="s">
-        <v>145</v>
-      </c>
-      <c r="F366" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="367" spans="1:6">
-      <c r="A367" t="s">
-        <v>85</v>
-      </c>
-      <c r="B367">
-        <v>2500</v>
-      </c>
-      <c r="C367">
-        <v>114.8097329106024</v>
-      </c>
-      <c r="D367" t="s">
-        <v>125</v>
-      </c>
-      <c r="E367" t="s">
-        <v>145</v>
-      </c>
-      <c r="F367" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="368" spans="1:6">
-      <c r="A368" t="s">
-        <v>56</v>
-      </c>
-      <c r="B368">
-        <v>1800</v>
-      </c>
-      <c r="C368">
-        <v>10284.89209676953</v>
-      </c>
-      <c r="D368" t="s">
-        <v>125</v>
-      </c>
-      <c r="E368" t="s">
-        <v>145</v>
-      </c>
-      <c r="F368" t="s">
         <v>146</v>
       </c>
     </row>

--- a/CodeVS/data/output/barge_schedule_ORDER_9_22.xlsx
+++ b/CodeVS/data/output/barge_schedule_ORDER_9_22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="164">
   <si>
     <t>barge</t>
   </si>
@@ -37,10 +37,55 @@
     <t>tugboat_id_to_customer</t>
   </si>
   <si>
+    <t>Barge ID: B_039, Name: จากัวร์ 10, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 08:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_037, Name: จากัวร์ 08, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_015, Name: SP 63, LOAD: 2200, Capacity: 2200, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 07:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_101, Name: เอาดี้ 05, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 09:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_065, Name: จากัวร์ 43, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 07:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_010, Name: SP 53, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-06 07:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_038, Name: จากัวร์ 09, LOAD: 3100, Capacity: 3100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 09:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_099, Name: เอาดี้ 03, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_053, Name: จากัวร์ 27, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_027, Name: SPI 09, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:20:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_040, Name: จากัวร์ 11, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_076, Name: จากัวร์ 58, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 08:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_081, Name: ปอร์เช่ 04, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 07:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_093, Name: ปอร์เช่ 21, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_080, Name: ปอร์เช่ 03, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-07 08:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
     <t>Barge ID: B_048, Name: จากัวร์ 21, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 08:10:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_090, Name: ปอร์เช่ 18, LOAD: 2850, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-06 09:30:00, Water Status: WaterBody.SEA</t>
+    <t>Barge ID: B_090, Name: ปอร์เช่ 18, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-06 09:30:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
     <t>Barge ID: B_092, Name: ปอร์เช่ 20, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-16 10:45:00, Water Status: WaterBody.SEA</t>
@@ -49,51 +94,6 @@
     <t>Barge ID: B_017, Name: SP 65, LOAD: 2300, Capacity: 2300, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:15:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_065, Name: จากัวร์ 43, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 07:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_010, Name: SP 53, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-06 07:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_038, Name: จากัวร์ 09, LOAD: 3100, Capacity: 3100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 09:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_039, Name: จากัวร์ 10, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 08:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_093, Name: ปอร์เช่ 21, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_080, Name: ปอร์เช่ 03, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-07 08:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_076, Name: จากัวร์ 58, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 08:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_081, Name: ปอร์เช่ 04, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 07:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_099, Name: เอาดี้ 03, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_053, Name: จากัวร์ 27, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_027, Name: SPI 09, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:20:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_040, Name: จากัวร์ 11, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_037, Name: จากัวร์ 08, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_015, Name: SP 63, LOAD: 2200, Capacity: 2200, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 07:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_101, Name: เอาดี้ 05, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 09:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
     <t>Barge ID: B_045, Name: จากัวร์ 17, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:10:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
@@ -103,226 +103,232 @@
     <t>Barge ID: B_047, Name: จากัวร์ 19, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 09:00:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
+    <t>Barge ID: B_035, Name: จากัวร์ 04, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 08:05:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_025, Name: SPI 05, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 09:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_057, Name: จากัวร์ 32, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:20:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_097, Name: เอาดี้ 01, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-01 09:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_060, Name: จากัวร์ 36, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 08:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_091, Name: ปอร์เช่ 19, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:20:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_023, Name: SPI 03, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 08:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_028, Name: SPI 12, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-04 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_078, Name: ปอร์เช่ 01, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:15:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_036, Name: จากัวร์ 05, LOAD: 3250, Capacity: 3250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 08:05:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_007, Name: SP 42, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-05 07:20:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_055, Name: จากัวร์ 30, LOAD: 4750, Capacity: 4750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 07:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
     <t>Barge ID: B_095, Name: ปอร์เช่ 24, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
+    <t>Barge ID: B_041, Name: จากัวร์ 12, LOAD: 3500, Capacity: 3500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_018, Name: SP 75, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_096, Name: ปอร์เช่ 25, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:15:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_082, Name: ปอร์เช่ 05, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-31 06:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_062, Name: จากัวร์ 40, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-06 08:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_063, Name: จากัวร์ 41, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_102, Name: เอาดี้ 07, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-15 06:25:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_016, Name: SP 64, LOAD: 2300, Capacity: 2300, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-28 04:55:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_086, Name: ปอร์เช่ 10, LOAD: 3300, Capacity: 3300, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-01 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_058, Name: จากัวร์ 34, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 09:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_069, Name: จากัวร์ 47, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_022, Name: SPI 02, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_050, Name: จากัวร์ 24, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 07:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_033, Name: จากัวร์ 02, LOAD: 3250, Capacity: 3250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_012, Name: SP 56, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-04 09:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_085, Name: ปอร์เช่ 09, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 09:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_009, Name: SP 46, LOAD: 2150, Capacity: 2150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_032, Name: SPI 18, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_044, Name: จากัวร์ 16, LOAD: 3500, Capacity: 3500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-26 06:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_075, Name: จากัวร์ 56, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
     <t>Barge ID: B_083, Name: ปอร์เช่ 06, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:20:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_025, Name: SPI 05, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 09:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_058, Name: จากัวร์ 34, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 09:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_063, Name: จากัวร์ 41, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_035, Name: จากัวร์ 04, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 08:05:00, Water Status: WaterBody.SEA</t>
+    <t>Barge ID: B_011, Name: SP 55, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:00:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
     <t>Barge ID: B_056, Name: จากัวร์ 31, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:00:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_091, Name: ปอร์เช่ 19, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:20:00, Water Status: WaterBody.SEA</t>
+    <t>Barge ID: B_100, Name: เอาดี้ 04, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_061, Name: จากัวร์ 37, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 09:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_052, Name: จากัวร์ 26, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-05 07:20:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_094, Name: ปอร์เช่ 23, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-04 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_030, Name: SPI 15, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_049, Name: จากัวร์ 22, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_019, Name: SP 76, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_014, Name: SP 59, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-12 09:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_026, Name: SPI 06, LOAD: 2200, Capacity: 2700, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-31 06:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_042, Name: จากัวร์ 13, LOAD: 3000, Capacity: 3000, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_013, Name: SP 57, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-01 09:10:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
     <t>Barge ID: B_072, Name: จากัวร์ 52, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-31 05:35:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_061, Name: จากัวร์ 37, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 09:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_016, Name: SP 64, LOAD: 2300, Capacity: 2300, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-28 04:55:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_096, Name: ปอร์เช่ 25, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:15:00, Water Status: WaterBody.SEA</t>
+    <t>Barge ID: B_089, Name: ปอร์เช่ 17, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 07:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_054, Name: จากัวร์ 28, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 08:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_074, Name: จากัวร์ 55, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 08:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_020, Name: SP 77, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-18 08:20:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_087, Name: ปอร์เช่ 12, LOAD: 3300, Capacity: 3300, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-28 05:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_031, Name: SPI 17, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-05 07:20:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_046, Name: จากัวร์ 18, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:20:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_088, Name: ปอร์เช่ 16, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_064, Name: จากัวร์ 42, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:15:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_008, Name: SP 43, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 07:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_066, Name: จากัวร์ 44, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_021, Name: SPI 01, LOAD: 300, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-06 08:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_070, Name: จากัวร์ 49, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 07:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_059, Name: จากัวร์ 35, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_024, Name: SPI 04, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-16 10:25:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_073, Name: จากัวร์ 53, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_068, Name: จากัวร์ 46, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 07:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_098, Name: เอาดี้ 02, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-01 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_084, Name: ปอร์เช่ 07, LOAD: 1500, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-29 05:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_034, Name: จากัวร์ 03, LOAD: 3250, Capacity: 3250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_043, Name: จากัวร์ 15, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-07 07:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_029, Name: SPI 13, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-16 10:45:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
     <t>Barge ID: B_079, Name: ปอร์เช่ 02, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-04 09:40:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_036, Name: จากัวร์ 05, LOAD: 3250, Capacity: 3250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 08:05:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_007, Name: SP 42, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-05 07:20:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_028, Name: SPI 12, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-04 08:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_094, Name: ปอร์เช่ 23, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-04 08:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_043, Name: จากัวร์ 15, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-07 07:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_018, Name: SP 75, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_085, Name: ปอร์เช่ 09, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 09:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_097, Name: เอาดี้ 01, LOAD: 1450, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-01 09:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_100, Name: เอาดี้ 04, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_086, Name: ปอร์เช่ 10, LOAD: 3300, Capacity: 3300, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-01 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_009, Name: SP 46, LOAD: 2150, Capacity: 2150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_057, Name: จากัวร์ 32, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:20:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_068, Name: จากัวร์ 46, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 07:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_041, Name: จากัวร์ 12, LOAD: 3500, Capacity: 3500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_022, Name: SPI 02, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_050, Name: จากัวร์ 24, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 07:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_032, Name: SPI 18, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_012, Name: SP 56, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-04 09:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_064, Name: จากัวร์ 42, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:15:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_019, Name: SP 76, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_033, Name: จากัวร์ 02, LOAD: 3250, Capacity: 3250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_070, Name: จากัวร์ 49, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 07:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_054, Name: จากัวร์ 28, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 08:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_030, Name: SPI 15, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:30:00, Water Status: WaterBody.SEA</t>
+    <t>Barge ID: B_067, Name: จากัวร์ 45, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 09:00:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
     <t>Barge ID: B_077, Name: จากัวร์ 60, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_102, Name: เอาดี้ 07, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-15 06:25:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_098, Name: เอาดี้ 02, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-01 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_078, Name: ปอร์เช่ 01, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:15:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_059, Name: จากัวร์ 35, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
     <t>Barge ID: B_051, Name: จากัวร์ 25, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 07:50:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_011, Name: SP 55, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_044, Name: จากัวร์ 16, LOAD: 3500, Capacity: 3500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-26 06:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_066, Name: จากัวร์ 44, LOAD: 850, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_013, Name: SP 57, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-01 09:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_074, Name: จากัวร์ 55, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 08:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_089, Name: ปอร์เช่ 17, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 07:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_055, Name: จากัวร์ 30, LOAD: 4750, Capacity: 4750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 07:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_021, Name: SPI 01, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-06 08:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_067, Name: จากัวร์ 45, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 09:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_008, Name: SP 43, LOAD: 1800, Capacity: 1800, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 07:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_046, Name: จากัวร์ 18, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:20:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_084, Name: ปอร์เช่ 07, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-29 05:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_060, Name: จากัวร์ 36, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 08:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_052, Name: จากัวร์ 26, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-05 07:20:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_020, Name: SP 77, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-18 08:20:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_088, Name: ปอร์เช่ 16, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_023, Name: SPI 03, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 08:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_049, Name: จากัวร์ 22, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_026, Name: SPI 06, LOAD: 2700, Capacity: 2700, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-31 06:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_031, Name: SPI 17, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-05 07:20:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_075, Name: จากัวร์ 56, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_069, Name: จากัวร์ 47, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_087, Name: ปอร์เช่ 12, LOAD: 3300, Capacity: 3300, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-28 05:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_014, Name: SP 59, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-12 09:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_062, Name: จากัวร์ 40, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-06 08:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_029, Name: SPI 13, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-16 10:45:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_042, Name: จากัวร์ 13, LOAD: 3000, Capacity: 3000, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_024, Name: SPI 04, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-16 10:25:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_034, Name: จากัวร์ 03, LOAD: 3250, Capacity: 3250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_073, Name: จากัวร์ 53, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_082, Name: ปอร์เช่ 05, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-31 06:10:00, Water Status: WaterBody.SEA</t>
+    <t>Barge ID: B_006, Name: SP 32, LOAD: 2100, Capacity: 2100, Location: (28.8232, 201.183), Setup Time: 20 mins, Ready Time: 2024-02-06 09:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_004, Name: SP 30, LOAD: 2100, Capacity: 2100, Location: (28.8232, 201.183), Setup Time: 20 mins, Ready Time: 2024-01-18 09:00:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
     <t>Barge ID: B_005, Name: SP 31, LOAD: 2100, Capacity: 2100, Location: (28.8232, 201.183), Setup Time: 20 mins, Ready Time: 2024-02-03 09:40:00, Water Status: WaterBody.SEA</t>
@@ -331,12 +337,6 @@
     <t>Barge ID: B_003, Name: SP 29, LOAD: 2250, Capacity: 2250, Location: (28.8232, 201.183), Setup Time: 20 mins, Ready Time: 2024-02-06 08:30:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_004, Name: SP 30, LOAD: 2100, Capacity: 2100, Location: (28.8232, 201.183), Setup Time: 20 mins, Ready Time: 2024-01-18 09:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_006, Name: SP 32, LOAD: 2100, Capacity: 2100, Location: (28.8232, 201.183), Setup Time: 20 mins, Ready Time: 2024-02-06 09:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
     <t>(datetime.datetime(2025, 1, 9, 17, 50), datetime.datetime(2025, 2, 8, 10, 15))</t>
   </si>
   <si>
@@ -349,42 +349,42 @@
     <t>(datetime.datetime(2025, 1, 25, 11, 25), datetime.datetime(2025, 2, 8, 14, 30))</t>
   </si>
   <si>
+    <t>(datetime.datetime(2025, 1, 25, 11, 25), datetime.datetime(2025, 2, 11, 13, 50))</t>
+  </si>
+  <si>
     <t>(datetime.datetime(2025, 1, 30, 10, 45), datetime.datetime(2025, 2, 7, 6, 30))</t>
   </si>
   <si>
-    <t>(datetime.datetime(2025, 1, 25, 11, 25), datetime.datetime(2025, 2, 11, 13, 50))</t>
-  </si>
-  <si>
     <t>(datetime.datetime(2025, 1, 23, 13, 30), datetime.datetime(2025, 2, 15, 6, 20))</t>
   </si>
   <si>
     <t>(datetime.datetime(2025, 1, 26, 8, 40), datetime.datetime(2025, 2, 16, 2, 0))</t>
   </si>
   <si>
+    <t>(datetime.datetime(2025, 1, 28, 9, 30), datetime.datetime(2025, 2, 17, 8, 0))</t>
+  </si>
+  <si>
     <t>(datetime.datetime(2025, 2, 2, 8, 40), datetime.datetime(2025, 2, 26, 2, 0))</t>
   </si>
   <si>
-    <t>(datetime.datetime(2025, 1, 28, 9, 30), datetime.datetime(2025, 2, 17, 8, 0))</t>
+    <t>(datetime.datetime(2025, 2, 4, 13, 10), datetime.datetime(2025, 2, 18, 14, 25))</t>
   </si>
   <si>
     <t>(datetime.datetime(2025, 2, 9, 10, 0), datetime.datetime(2025, 2, 15, 13, 50))</t>
   </si>
   <si>
-    <t>(datetime.datetime(2025, 2, 4, 13, 10), datetime.datetime(2025, 2, 18, 14, 25))</t>
+    <t>(datetime.datetime(2025, 2, 3, 16, 20), datetime.datetime(2025, 2, 25, 12, 30))</t>
+  </si>
+  <si>
+    <t>(datetime.datetime(2025, 2, 1, 7, 50), datetime.datetime(2025, 2, 28, 8, 20))</t>
   </si>
   <si>
     <t>(datetime.datetime(2025, 2, 10, 6, 0), datetime.datetime(2025, 2, 19, 11, 10))</t>
   </si>
   <si>
-    <t>(datetime.datetime(2025, 2, 3, 16, 20), datetime.datetime(2025, 2, 25, 12, 30))</t>
-  </si>
-  <si>
     <t>(datetime.datetime(2025, 2, 1, 18, 21, 50), datetime.datetime(2025, 3, 1, 18, 21, 50))</t>
   </si>
   <si>
-    <t>(datetime.datetime(2025, 2, 1, 7, 50), datetime.datetime(2025, 2, 28, 8, 20))</t>
-  </si>
-  <si>
     <t>(datetime.datetime(2025, 9, 17, 2, 9, 38), datetime.datetime(2025, 9, 18, 2, 9, 38))</t>
   </si>
   <si>
@@ -406,42 +406,42 @@
     <t>ODR_005</t>
   </si>
   <si>
+    <t>ODR_006</t>
+  </si>
+  <si>
     <t>ODR_009</t>
   </si>
   <si>
-    <t>ODR_006</t>
-  </si>
-  <si>
     <t>ODR_004</t>
   </si>
   <si>
     <t>ODR_007</t>
   </si>
   <si>
+    <t>ODR_008</t>
+  </si>
+  <si>
     <t>ODR_015</t>
   </si>
   <si>
-    <t>ODR_008</t>
+    <t>ODR_012</t>
   </si>
   <si>
     <t>ODR_013</t>
   </si>
   <si>
-    <t>ODR_012</t>
+    <t>ODR_011</t>
+  </si>
+  <si>
+    <t>ODR_010</t>
   </si>
   <si>
     <t>ODR_014</t>
   </si>
   <si>
-    <t>ODR_011</t>
-  </si>
-  <si>
     <t>ODR_016</t>
   </si>
   <si>
-    <t>ODR_010</t>
-  </si>
-  <si>
     <t>ODR_017</t>
   </si>
   <si>
@@ -457,55 +457,55 @@
     <t>SeaTB_06</t>
   </si>
   <si>
+    <t>SeaTB_07</t>
+  </si>
+  <si>
+    <t>SeaTB_02</t>
+  </si>
+  <si>
+    <t>SeaTB_08</t>
+  </si>
+  <si>
+    <t>SeaTB_11</t>
+  </si>
+  <si>
+    <t>SeaTB_12</t>
+  </si>
+  <si>
+    <t>SeaTB_09</t>
+  </si>
+  <si>
     <t>SeaTB_04</t>
   </si>
   <si>
-    <t>SeaTB_08</t>
-  </si>
-  <si>
-    <t>SeaTB_09</t>
-  </si>
-  <si>
     <t>SeaTB_03</t>
   </si>
   <si>
-    <t>SeaTB_02</t>
-  </si>
-  <si>
-    <t>SeaTB_11</t>
-  </si>
-  <si>
-    <t>SeaTB_12</t>
-  </si>
-  <si>
-    <t>SeaTB_07</t>
+    <t>RiverTB_13</t>
+  </si>
+  <si>
+    <t>RiverTB_08</t>
+  </si>
+  <si>
+    <t>RiverTB_06</t>
+  </si>
+  <si>
+    <t>RiverTB_01</t>
   </si>
   <si>
     <t>RiverTB_10</t>
   </si>
   <si>
-    <t>RiverTB_01</t>
-  </si>
-  <si>
-    <t>RiverTB_08</t>
+    <t>RiverTB_02</t>
+  </si>
+  <si>
+    <t>RiverTB_09</t>
+  </si>
+  <si>
+    <t>RiverTB_11</t>
   </si>
   <si>
     <t>RiverTB_12</t>
-  </si>
-  <si>
-    <t>RiverTB_09</t>
-  </si>
-  <si>
-    <t>RiverTB_06</t>
-  </si>
-  <si>
-    <t>RiverTB_11</t>
-  </si>
-  <si>
-    <t>RiverTB_02</t>
-  </si>
-  <si>
-    <t>RiverTB_13</t>
   </si>
 </sst>
 </file>
@@ -863,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G364"/>
+  <dimension ref="A1:G368"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -914,7 +914,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>3150</v>
+        <v>2200</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -946,7 +946,7 @@
         <v>126</v>
       </c>
       <c r="F4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -954,7 +954,7 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>2300</v>
+        <v>2750</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -966,7 +966,7 @@
         <v>126</v>
       </c>
       <c r="F5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1034,7 +1034,7 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>2250</v>
+        <v>2750</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1046,7 +1046,7 @@
         <v>126</v>
       </c>
       <c r="F9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1054,7 +1054,7 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1066,7 +1066,7 @@
         <v>126</v>
       </c>
       <c r="F10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1074,7 +1074,7 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1086,7 +1086,7 @@
         <v>126</v>
       </c>
       <c r="F11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1094,7 +1094,7 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1106,7 +1106,7 @@
         <v>126</v>
       </c>
       <c r="F12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1114,7 +1114,7 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>3150</v>
+        <v>2500</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1134,7 +1134,7 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>2750</v>
+        <v>3150</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1154,7 +1154,7 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1166,7 +1166,7 @@
         <v>126</v>
       </c>
       <c r="F15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1174,7 +1174,7 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>2900</v>
+        <v>3150</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1186,7 +1186,7 @@
         <v>126</v>
       </c>
       <c r="F16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1206,7 +1206,7 @@
         <v>126</v>
       </c>
       <c r="F17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1214,7 +1214,7 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>2900</v>
+        <v>3150</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1226,7 +1226,7 @@
         <v>126</v>
       </c>
       <c r="F18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1234,7 +1234,7 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>2200</v>
+        <v>3150</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1246,7 +1246,7 @@
         <v>126</v>
       </c>
       <c r="F19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1254,7 +1254,7 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>2750</v>
+        <v>2300</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1266,7 +1266,7 @@
         <v>126</v>
       </c>
       <c r="F20" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1286,7 +1286,7 @@
         <v>126</v>
       </c>
       <c r="F21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1306,7 +1306,7 @@
         <v>126</v>
       </c>
       <c r="F22" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1326,7 +1326,7 @@
         <v>126</v>
       </c>
       <c r="F23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1334,7 +1334,7 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>127</v>
       </c>
       <c r="F24" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1354,7 +1354,7 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>3150</v>
+        <v>2600</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1366,7 +1366,7 @@
         <v>127</v>
       </c>
       <c r="F25" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1374,7 +1374,7 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>2600</v>
+        <v>2250</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>2250</v>
+        <v>2750</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1406,7 +1406,7 @@
         <v>127</v>
       </c>
       <c r="F27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1414,7 +1414,7 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1426,7 +1426,7 @@
         <v>127</v>
       </c>
       <c r="F28" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1434,7 +1434,7 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>2900</v>
+        <v>3150</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -1446,7 +1446,7 @@
         <v>127</v>
       </c>
       <c r="F29" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1454,7 +1454,7 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>2250</v>
+        <v>2600</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -1474,7 +1474,7 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>127</v>
       </c>
       <c r="F31" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1494,7 +1494,7 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -1506,7 +1506,7 @@
         <v>127</v>
       </c>
       <c r="F32" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1514,7 +1514,7 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>2250</v>
+        <v>3250</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>127</v>
       </c>
       <c r="F33" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1534,7 +1534,7 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>2300</v>
+        <v>1800</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -1546,7 +1546,7 @@
         <v>127</v>
       </c>
       <c r="F34" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1554,7 +1554,7 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>3150</v>
+        <v>4750</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -1566,7 +1566,7 @@
         <v>127</v>
       </c>
       <c r="F35" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1586,7 +1586,7 @@
         <v>127</v>
       </c>
       <c r="F36" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1594,7 +1594,7 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>3250</v>
+        <v>3500</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -1606,7 +1606,7 @@
         <v>127</v>
       </c>
       <c r="F37" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1614,7 +1614,7 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -1626,7 +1626,7 @@
         <v>127</v>
       </c>
       <c r="F38" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1634,7 +1634,7 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>2900</v>
+        <v>3150</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -1666,7 +1666,7 @@
         <v>127</v>
       </c>
       <c r="F40" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1674,7 +1674,7 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -1686,7 +1686,7 @@
         <v>127</v>
       </c>
       <c r="F41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1694,19 +1694,19 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E42" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F42" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1714,7 +1714,7 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>3150</v>
+        <v>2750</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>128</v>
       </c>
       <c r="F43" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1734,7 +1734,7 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>2750</v>
+        <v>2300</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -1746,7 +1746,7 @@
         <v>128</v>
       </c>
       <c r="F44" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1754,7 +1754,7 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>2750</v>
+        <v>3300</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -1766,7 +1766,7 @@
         <v>128</v>
       </c>
       <c r="F45" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1774,7 +1774,7 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>3300</v>
+        <v>2250</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -1794,7 +1794,7 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>950</v>
+        <v>2500</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -1814,7 +1814,7 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>2250</v>
+        <v>2600</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -1834,7 +1834,7 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>3500</v>
+        <v>3250</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -1874,7 +1874,7 @@
         <v>56</v>
       </c>
       <c r="B51">
-        <v>2600</v>
+        <v>1800</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         <v>127</v>
       </c>
       <c r="F51" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1894,7 +1894,7 @@
         <v>57</v>
       </c>
       <c r="B52">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>127</v>
       </c>
       <c r="F52" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1914,7 +1914,7 @@
         <v>58</v>
       </c>
       <c r="B53">
-        <v>2900</v>
+        <v>2150</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -1926,7 +1926,7 @@
         <v>127</v>
       </c>
       <c r="F53" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -1934,7 +1934,7 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>1800</v>
+        <v>950</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>127</v>
       </c>
       <c r="F54" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -1954,7 +1954,7 @@
         <v>60</v>
       </c>
       <c r="B55">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -1974,7 +1974,7 @@
         <v>61</v>
       </c>
       <c r="B56">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -1986,7 +1986,7 @@
         <v>128</v>
       </c>
       <c r="F56" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -1994,7 +1994,7 @@
         <v>62</v>
       </c>
       <c r="B57">
-        <v>3250</v>
+        <v>3150</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -2014,7 +2014,7 @@
         <v>63</v>
       </c>
       <c r="B58">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -2054,7 +2054,7 @@
         <v>65</v>
       </c>
       <c r="B60">
-        <v>2900</v>
+        <v>2750</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>128</v>
       </c>
       <c r="F60" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2074,7 +2074,7 @@
         <v>66</v>
       </c>
       <c r="B61">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -2086,7 +2086,7 @@
         <v>128</v>
       </c>
       <c r="F61" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2094,7 +2094,7 @@
         <v>67</v>
       </c>
       <c r="B62">
-        <v>2750</v>
+        <v>2250</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -2106,7 +2106,7 @@
         <v>128</v>
       </c>
       <c r="F62" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2114,7 +2114,7 @@
         <v>68</v>
       </c>
       <c r="B63">
-        <v>2750</v>
+        <v>3150</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -2126,7 +2126,7 @@
         <v>128</v>
       </c>
       <c r="F63" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2134,7 +2134,7 @@
         <v>69</v>
       </c>
       <c r="B64">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -2146,7 +2146,7 @@
         <v>128</v>
       </c>
       <c r="F64" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2166,7 +2166,7 @@
         <v>128</v>
       </c>
       <c r="F65" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2174,7 +2174,7 @@
         <v>71</v>
       </c>
       <c r="B66">
-        <v>2250</v>
+        <v>2100</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -2186,7 +2186,7 @@
         <v>128</v>
       </c>
       <c r="F66" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2194,7 +2194,7 @@
         <v>72</v>
       </c>
       <c r="B67">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -2206,7 +2206,7 @@
         <v>128</v>
       </c>
       <c r="F67" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2214,7 +2214,7 @@
         <v>73</v>
       </c>
       <c r="B68">
-        <v>3500</v>
+        <v>2700</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -2226,7 +2226,7 @@
         <v>128</v>
       </c>
       <c r="F68" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2234,7 +2234,7 @@
         <v>74</v>
       </c>
       <c r="B69">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2246,7 +2246,7 @@
         <v>128</v>
       </c>
       <c r="F69" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2266,7 +2266,7 @@
         <v>128</v>
       </c>
       <c r="F70" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2286,7 +2286,7 @@
         <v>128</v>
       </c>
       <c r="F71" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2306,7 +2306,7 @@
         <v>128</v>
       </c>
       <c r="F72" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -2314,7 +2314,7 @@
         <v>78</v>
       </c>
       <c r="B73">
-        <v>4750</v>
+        <v>2250</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2326,7 +2326,7 @@
         <v>128</v>
       </c>
       <c r="F73" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -2334,19 +2334,19 @@
         <v>79</v>
       </c>
       <c r="B74">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E74" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F74" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2354,7 +2354,7 @@
         <v>80</v>
       </c>
       <c r="B75">
-        <v>2500</v>
+        <v>2100</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2366,7 +2366,7 @@
         <v>129</v>
       </c>
       <c r="F75" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -2374,7 +2374,7 @@
         <v>81</v>
       </c>
       <c r="B76">
-        <v>1650</v>
+        <v>3300</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2386,7 +2386,7 @@
         <v>129</v>
       </c>
       <c r="F76" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2394,19 +2394,19 @@
         <v>82</v>
       </c>
       <c r="B77">
-        <v>2250</v>
+        <v>1350</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E77" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F77" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -2414,7 +2414,7 @@
         <v>83</v>
       </c>
       <c r="B78">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2426,7 +2426,7 @@
         <v>128</v>
       </c>
       <c r="F78" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -2434,7 +2434,7 @@
         <v>84</v>
       </c>
       <c r="B79">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2446,7 +2446,7 @@
         <v>128</v>
       </c>
       <c r="F79" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -2454,7 +2454,7 @@
         <v>85</v>
       </c>
       <c r="B80">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2466,7 +2466,7 @@
         <v>128</v>
       </c>
       <c r="F80" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -2474,7 +2474,7 @@
         <v>86</v>
       </c>
       <c r="B81">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>128</v>
       </c>
       <c r="F81" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -2494,7 +2494,7 @@
         <v>87</v>
       </c>
       <c r="B82">
-        <v>3150</v>
+        <v>2500</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2506,7 +2506,7 @@
         <v>128</v>
       </c>
       <c r="F82" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -2526,7 +2526,7 @@
         <v>128</v>
       </c>
       <c r="F83" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -2534,7 +2534,7 @@
         <v>89</v>
       </c>
       <c r="B84">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2546,7 +2546,7 @@
         <v>128</v>
       </c>
       <c r="F84" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2554,7 +2554,7 @@
         <v>90</v>
       </c>
       <c r="B85">
-        <v>2700</v>
+        <v>2250</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2566,7 +2566,7 @@
         <v>128</v>
       </c>
       <c r="F85" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -2574,7 +2574,7 @@
         <v>91</v>
       </c>
       <c r="B86">
-        <v>2900</v>
+        <v>2600</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2586,7 +2586,7 @@
         <v>128</v>
       </c>
       <c r="F86" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -2606,7 +2606,7 @@
         <v>128</v>
       </c>
       <c r="F87" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -2626,7 +2626,7 @@
         <v>128</v>
       </c>
       <c r="F88" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -2634,7 +2634,7 @@
         <v>94</v>
       </c>
       <c r="B89">
-        <v>3300</v>
+        <v>2750</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2646,7 +2646,7 @@
         <v>128</v>
       </c>
       <c r="F89" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -2654,7 +2654,7 @@
         <v>95</v>
       </c>
       <c r="B90">
-        <v>2100</v>
+        <v>3150</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2666,7 +2666,7 @@
         <v>128</v>
       </c>
       <c r="F90" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -2674,7 +2674,7 @@
         <v>96</v>
       </c>
       <c r="B91">
-        <v>2500</v>
+        <v>3250</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2686,7 +2686,7 @@
         <v>128</v>
       </c>
       <c r="F91" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -2694,7 +2694,7 @@
         <v>97</v>
       </c>
       <c r="B92">
-        <v>2900</v>
+        <v>2250</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2706,7 +2706,7 @@
         <v>128</v>
       </c>
       <c r="F92" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -2714,7 +2714,7 @@
         <v>98</v>
       </c>
       <c r="B93">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2734,7 +2734,7 @@
         <v>99</v>
       </c>
       <c r="B94">
-        <v>2600</v>
+        <v>2250</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         <v>100</v>
       </c>
       <c r="B95">
-        <v>3250</v>
+        <v>2500</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2766,7 +2766,7 @@
         <v>128</v>
       </c>
       <c r="F95" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -2786,7 +2786,7 @@
         <v>128</v>
       </c>
       <c r="F96" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -2794,27 +2794,27 @@
         <v>102</v>
       </c>
       <c r="B97">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C97">
         <v>0</v>
       </c>
       <c r="D97" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E97" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F97" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="B98">
-        <v>100</v>
+        <v>2600</v>
       </c>
       <c r="C98">
         <v>50.30315431564902</v>
@@ -2831,19 +2831,19 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B99">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C99">
         <v>50.30315431564902</v>
       </c>
       <c r="D99" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E99" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F99" t="s">
         <v>146</v>
@@ -2851,59 +2851,59 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="B100">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C100">
-        <v>50.30315431564902</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D100" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E100" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F100" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="B101">
-        <v>3300</v>
+        <v>650</v>
       </c>
       <c r="C101">
-        <v>50.30315431564902</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D101" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E101" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F101" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B102">
-        <v>1700</v>
+        <v>2900</v>
       </c>
       <c r="C102">
-        <v>56.09574693011376</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D102" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E102" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F102" t="s">
         <v>146</v>
@@ -2911,42 +2911,42 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B103">
-        <v>100</v>
+        <v>3150</v>
       </c>
       <c r="C103">
-        <v>56.09574693011376</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D103" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E103" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F103" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="B104">
-        <v>2350</v>
+        <v>100</v>
       </c>
       <c r="C104">
-        <v>56.09574693011376</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D104" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E104" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F104" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -2966,18 +2966,18 @@
         <v>132</v>
       </c>
       <c r="F105" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="B106">
-        <v>2250</v>
+        <v>1250</v>
       </c>
       <c r="C106">
-        <v>56.09574693011376</v>
+        <v>10284.89209676953</v>
       </c>
       <c r="D106" t="s">
         <v>113</v>
@@ -2986,15 +2986,15 @@
         <v>132</v>
       </c>
       <c r="F106" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B107">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C107">
         <v>56.09574693011376</v>
@@ -3006,15 +3006,15 @@
         <v>132</v>
       </c>
       <c r="F107" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B108">
-        <v>3150</v>
+        <v>2200</v>
       </c>
       <c r="C108">
         <v>56.09574693011376</v>
@@ -3026,58 +3026,58 @@
         <v>132</v>
       </c>
       <c r="F108" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="B109">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="C109">
-        <v>10284.89209676953</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D109" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E109" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F109" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="B110">
-        <v>2250</v>
+        <v>2750</v>
       </c>
       <c r="C110">
-        <v>10284.89209676953</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D110" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E110" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F110" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="B111">
-        <v>2100</v>
+        <v>2600</v>
       </c>
       <c r="C111">
-        <v>10284.89209676953</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D111" t="s">
         <v>114</v>
@@ -3086,18 +3086,18 @@
         <v>133</v>
       </c>
       <c r="F111" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="B112">
-        <v>1400</v>
+        <v>2300</v>
       </c>
       <c r="C112">
-        <v>10284.89209676953</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D112" t="s">
         <v>114</v>
@@ -3106,18 +3106,18 @@
         <v>133</v>
       </c>
       <c r="F112" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="B113">
-        <v>3150</v>
+        <v>1850</v>
       </c>
       <c r="C113">
-        <v>56.09574693011376</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D113" t="s">
         <v>114</v>
@@ -3126,18 +3126,18 @@
         <v>133</v>
       </c>
       <c r="F113" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="B114">
-        <v>3150</v>
+        <v>2100</v>
       </c>
       <c r="C114">
-        <v>56.09574693011376</v>
+        <v>10284.89209676953</v>
       </c>
       <c r="D114" t="s">
         <v>114</v>
@@ -3146,18 +3146,18 @@
         <v>133</v>
       </c>
       <c r="F114" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="B115">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="C115">
-        <v>56.09574693011376</v>
+        <v>10284.89209676953</v>
       </c>
       <c r="D115" t="s">
         <v>114</v>
@@ -3166,58 +3166,58 @@
         <v>133</v>
       </c>
       <c r="F115" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="B116">
-        <v>3250</v>
+        <v>2750</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D116" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E116" t="s">
-        <v>134</v>
-      </c>
-      <c r="G116" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
+        <v>133</v>
+      </c>
+      <c r="F116" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="B117">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>10284.89209676953</v>
       </c>
       <c r="D117" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E117" t="s">
-        <v>134</v>
-      </c>
-      <c r="G117" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
+        <v>133</v>
+      </c>
+      <c r="F117" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="B118">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D118" t="s">
         <v>115</v>
@@ -3225,19 +3225,19 @@
       <c r="E118" t="s">
         <v>134</v>
       </c>
-      <c r="G118" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
+      <c r="F118" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="B119">
-        <v>2250</v>
+        <v>2900</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D119" t="s">
         <v>115</v>
@@ -3245,19 +3245,19 @@
       <c r="E119" t="s">
         <v>134</v>
       </c>
-      <c r="G119" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
+      <c r="F119" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="B120">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D120" t="s">
         <v>115</v>
@@ -3265,19 +3265,19 @@
       <c r="E120" t="s">
         <v>134</v>
       </c>
-      <c r="G120" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
+      <c r="F120" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B121">
-        <v>2750</v>
+        <v>4750</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D121" t="s">
         <v>115</v>
@@ -3285,19 +3285,19 @@
       <c r="E121" t="s">
         <v>134</v>
       </c>
-      <c r="G121" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
+      <c r="F121" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B122">
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D122" t="s">
         <v>115</v>
@@ -3305,19 +3305,19 @@
       <c r="E122" t="s">
         <v>134</v>
       </c>
-      <c r="G122" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
+      <c r="F122" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B123">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D123" t="s">
         <v>115</v>
@@ -3325,19 +3325,19 @@
       <c r="E123" t="s">
         <v>134</v>
       </c>
-      <c r="G123" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
+      <c r="F123" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B124">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D124" t="s">
         <v>115</v>
@@ -3345,19 +3345,19 @@
       <c r="E124" t="s">
         <v>134</v>
       </c>
-      <c r="G124" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7">
+      <c r="F124" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="B125">
-        <v>2250</v>
+        <v>3250</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D125" t="s">
         <v>115</v>
@@ -3365,19 +3365,19 @@
       <c r="E125" t="s">
         <v>134</v>
       </c>
-      <c r="G125" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
+      <c r="F125" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="B126">
         <v>2750</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D126" t="s">
         <v>115</v>
@@ -3385,19 +3385,19 @@
       <c r="E126" t="s">
         <v>134</v>
       </c>
-      <c r="G126" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
+      <c r="F126" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B127">
-        <v>1100</v>
+        <v>2600</v>
       </c>
       <c r="C127">
-        <v>10285.36152801761</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D127" t="s">
         <v>115</v>
@@ -3405,199 +3405,199 @@
       <c r="E127" t="s">
         <v>134</v>
       </c>
-      <c r="G127" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
+      <c r="F127" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="B128">
-        <v>1800</v>
+        <v>3300</v>
       </c>
       <c r="C128">
-        <v>50.30315431564902</v>
+        <v>55.17460674463854</v>
       </c>
       <c r="D128" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E128" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F128" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="B129">
-        <v>2250</v>
+        <v>2750</v>
       </c>
       <c r="C129">
-        <v>50.30315431564902</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D129" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E129" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F129" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="B130">
-        <v>2600</v>
+        <v>2900</v>
       </c>
       <c r="C130">
-        <v>50.30315431564902</v>
+        <v>55.17460674463854</v>
       </c>
       <c r="D130" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E130" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F130" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
       <c r="A131" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="B131">
-        <v>2300</v>
+        <v>2100</v>
       </c>
       <c r="C131">
-        <v>50.30315431564902</v>
+        <v>55.17460674463854</v>
       </c>
       <c r="D131" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E131" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F131" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="B132">
+        <v>1800</v>
+      </c>
+      <c r="C132">
+        <v>10284.73661716383</v>
+      </c>
+      <c r="D132" t="s">
+        <v>115</v>
+      </c>
+      <c r="E132" t="s">
+        <v>134</v>
+      </c>
+      <c r="F132" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" t="s">
+        <v>17</v>
+      </c>
+      <c r="B133">
         <v>2250</v>
       </c>
-      <c r="C132">
-        <v>50.30315431564902</v>
-      </c>
-      <c r="D132" t="s">
-        <v>116</v>
-      </c>
-      <c r="E132" t="s">
-        <v>135</v>
-      </c>
-      <c r="F132" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133" t="s">
-        <v>40</v>
-      </c>
-      <c r="B133">
-        <v>3150</v>
-      </c>
       <c r="C133">
-        <v>50.30315431564902</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D133" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E133" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F133" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
       <c r="A134" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B134">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C134">
-        <v>50.30315431564902</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D134" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E134" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F134" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="B135">
-        <v>2900</v>
+        <v>2250</v>
       </c>
       <c r="C135">
-        <v>50.30315431564902</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D135" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E135" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F135" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B136">
-        <v>3150</v>
+        <v>2500</v>
       </c>
       <c r="C136">
-        <v>50.30315431564902</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D136" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E136" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F136" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="B137">
-        <v>2250</v>
+        <v>2600</v>
       </c>
       <c r="C137">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D137" t="s">
         <v>116</v>
@@ -3605,19 +3605,19 @@
       <c r="E137" t="s">
         <v>135</v>
       </c>
-      <c r="F137" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
+      <c r="G137" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="B138">
         <v>2500</v>
       </c>
       <c r="C138">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D138" t="s">
         <v>116</v>
@@ -3625,19 +3625,19 @@
       <c r="E138" t="s">
         <v>135</v>
       </c>
-      <c r="F138" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
+      <c r="G138" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="B139">
-        <v>3250</v>
+        <v>2700</v>
       </c>
       <c r="C139">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D139" t="s">
         <v>116</v>
@@ -3645,19 +3645,19 @@
       <c r="E139" t="s">
         <v>135</v>
       </c>
-      <c r="F139" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="G139" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
       <c r="A140" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="B140">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="C140">
-        <v>55.17460674463854</v>
+        <v>0</v>
       </c>
       <c r="D140" t="s">
         <v>116</v>
@@ -3665,19 +3665,19 @@
       <c r="E140" t="s">
         <v>135</v>
       </c>
-      <c r="F140" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
+      <c r="G140" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
       <c r="A141" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B141">
-        <v>2600</v>
+        <v>2900</v>
       </c>
       <c r="C141">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D141" t="s">
         <v>116</v>
@@ -3685,19 +3685,19 @@
       <c r="E141" t="s">
         <v>135</v>
       </c>
-      <c r="F141" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
+      <c r="G141" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
       <c r="A142" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="B142">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C142">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D142" t="s">
         <v>116</v>
@@ -3705,19 +3705,19 @@
       <c r="E142" t="s">
         <v>135</v>
       </c>
-      <c r="F142" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+      <c r="G142" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
       <c r="A143" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B143">
-        <v>2500</v>
+        <v>1250</v>
       </c>
       <c r="C143">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D143" t="s">
         <v>116</v>
@@ -3725,19 +3725,19 @@
       <c r="E143" t="s">
         <v>135</v>
       </c>
-      <c r="F143" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
+      <c r="G143" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="B144">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C144">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D144" t="s">
         <v>116</v>
@@ -3745,19 +3745,19 @@
       <c r="E144" t="s">
         <v>135</v>
       </c>
-      <c r="F144" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
+      <c r="G144" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
       <c r="A145" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="B145">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="C145">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D145" t="s">
         <v>116</v>
@@ -3765,19 +3765,19 @@
       <c r="E145" t="s">
         <v>135</v>
       </c>
-      <c r="F145" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
+      <c r="G145" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
       <c r="A146" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="B146">
-        <v>2900</v>
+        <v>2250</v>
       </c>
       <c r="C146">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D146" t="s">
         <v>116</v>
@@ -3785,113 +3785,113 @@
       <c r="E146" t="s">
         <v>135</v>
       </c>
-      <c r="F146" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
+      <c r="G146" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
       <c r="A147" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B147">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C147">
         <v>0</v>
       </c>
       <c r="D147" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E147" t="s">
-        <v>136</v>
-      </c>
-      <c r="F147" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
+        <v>135</v>
+      </c>
+      <c r="G147" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
       <c r="A148" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="B148">
-        <v>3050</v>
+        <v>2500</v>
       </c>
       <c r="C148">
         <v>0</v>
       </c>
       <c r="D148" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E148" t="s">
-        <v>136</v>
-      </c>
-      <c r="F148" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
+        <v>135</v>
+      </c>
+      <c r="G148" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
       <c r="A149" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="B149">
         <v>2500</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D149" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E149" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F149" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
       <c r="A150" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="B150">
-        <v>750</v>
+        <v>300</v>
       </c>
       <c r="C150">
-        <v>50.30315431564902</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D150" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E150" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F150" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
       <c r="A151" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B151">
-        <v>3150</v>
+        <v>2600</v>
       </c>
       <c r="C151">
         <v>50.30315431564902</v>
       </c>
       <c r="D151" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E151" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F151" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:7">
       <c r="A152" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B152">
         <v>2250</v>
@@ -3900,524 +3900,524 @@
         <v>50.30315431564902</v>
       </c>
       <c r="D152" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E152" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F152" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:7">
       <c r="A153" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="B153">
+        <v>2250</v>
+      </c>
+      <c r="C153">
+        <v>50.30315431564902</v>
+      </c>
+      <c r="D153" t="s">
+        <v>115</v>
+      </c>
+      <c r="E153" t="s">
+        <v>134</v>
+      </c>
+      <c r="F153" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" t="s">
+        <v>52</v>
+      </c>
+      <c r="B154">
         <v>2500</v>
       </c>
-      <c r="C153">
-        <v>56.09574693011376</v>
-      </c>
-      <c r="D153" t="s">
-        <v>116</v>
-      </c>
-      <c r="E153" t="s">
-        <v>135</v>
-      </c>
-      <c r="F153" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="A154" t="s">
-        <v>19</v>
-      </c>
-      <c r="B154">
-        <v>1100</v>
-      </c>
       <c r="C154">
-        <v>56.09574693011376</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D154" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E154" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F154" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
       <c r="A155" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="B155">
-        <v>2250</v>
+        <v>2700</v>
       </c>
       <c r="C155">
-        <v>56.09574693011376</v>
+        <v>0</v>
       </c>
       <c r="D155" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E155" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F155" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
       <c r="A156" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="B156">
+        <v>300</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+      <c r="D156" t="s">
+        <v>117</v>
+      </c>
+      <c r="E156" t="s">
+        <v>136</v>
+      </c>
+      <c r="F156" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" t="s">
+        <v>62</v>
+      </c>
+      <c r="B157">
         <v>3150</v>
       </c>
-      <c r="C156">
-        <v>56.09574693011376</v>
-      </c>
-      <c r="D156" t="s">
-        <v>116</v>
-      </c>
-      <c r="E156" t="s">
-        <v>135</v>
-      </c>
-      <c r="F156" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6">
-      <c r="A157" t="s">
-        <v>21</v>
-      </c>
-      <c r="B157">
-        <v>2900</v>
-      </c>
       <c r="C157">
-        <v>56.09574693011376</v>
+        <v>0</v>
       </c>
       <c r="D157" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E157" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F157" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="B158">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C158">
-        <v>56.09574693011376</v>
+        <v>0</v>
       </c>
       <c r="D158" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E158" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F158" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
       <c r="A159" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B159">
-        <v>2250</v>
+        <v>3250</v>
       </c>
       <c r="C159">
         <v>50.30315431564902</v>
       </c>
       <c r="D159" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E159" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F159" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
       <c r="A160" t="s">
         <v>58</v>
       </c>
       <c r="B160">
-        <v>1800</v>
+        <v>2150</v>
       </c>
       <c r="C160">
         <v>50.30315431564902</v>
       </c>
       <c r="D160" t="s">
+        <v>118</v>
+      </c>
+      <c r="E160" t="s">
+        <v>137</v>
+      </c>
+      <c r="F160" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" t="s">
+        <v>31</v>
+      </c>
+      <c r="B161">
+        <v>800</v>
+      </c>
+      <c r="C161">
+        <v>50.30315431564902</v>
+      </c>
+      <c r="D161" t="s">
+        <v>118</v>
+      </c>
+      <c r="E161" t="s">
+        <v>137</v>
+      </c>
+      <c r="F161" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" t="s">
+        <v>19</v>
+      </c>
+      <c r="B162">
+        <v>3150</v>
+      </c>
+      <c r="C162">
+        <v>56.09574693011376</v>
+      </c>
+      <c r="D162" t="s">
         <v>119</v>
       </c>
-      <c r="E160" t="s">
+      <c r="E162" t="s">
         <v>138</v>
       </c>
-      <c r="F160" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7">
-      <c r="A161" t="s">
-        <v>79</v>
-      </c>
-      <c r="B161">
-        <v>2600</v>
-      </c>
-      <c r="C161">
-        <v>55.17460674463854</v>
-      </c>
-      <c r="D161" t="s">
-        <v>120</v>
-      </c>
-      <c r="E161" t="s">
-        <v>139</v>
-      </c>
-      <c r="F161" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7">
-      <c r="A162" t="s">
-        <v>81</v>
-      </c>
-      <c r="B162">
+      <c r="F162" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" t="s">
+        <v>39</v>
+      </c>
+      <c r="B163">
         <v>1800</v>
       </c>
-      <c r="C162">
-        <v>55.17460674463854</v>
-      </c>
-      <c r="D162" t="s">
-        <v>120</v>
-      </c>
-      <c r="E162" t="s">
-        <v>139</v>
-      </c>
-      <c r="F162" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7">
-      <c r="A163" t="s">
-        <v>27</v>
-      </c>
-      <c r="B163">
-        <v>2500</v>
-      </c>
       <c r="C163">
-        <v>56.09574693011376</v>
+        <v>117.129363815579</v>
       </c>
       <c r="D163" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E163" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F163" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="B164">
+        <v>500</v>
+      </c>
+      <c r="C164">
+        <v>117.129363815579</v>
+      </c>
+      <c r="D164" t="s">
+        <v>119</v>
+      </c>
+      <c r="E164" t="s">
+        <v>138</v>
+      </c>
+      <c r="F164" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" t="s">
+        <v>8</v>
+      </c>
+      <c r="B165">
         <v>2900</v>
       </c>
-      <c r="C164">
-        <v>10284.73661716383</v>
-      </c>
-      <c r="D164" t="s">
-        <v>120</v>
-      </c>
-      <c r="E164" t="s">
-        <v>139</v>
-      </c>
-      <c r="F164" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7">
-      <c r="A165" t="s">
-        <v>66</v>
-      </c>
-      <c r="B165">
-        <v>50</v>
-      </c>
       <c r="C165">
-        <v>10284.73661716383</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D165" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E165" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F165" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B166">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="C166">
-        <v>10284.73661716383</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D166" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E166" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F166" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B167">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C167">
         <v>56.09574693011376</v>
       </c>
       <c r="D167" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E167" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F167" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="B168">
+        <v>2500</v>
+      </c>
+      <c r="C168">
+        <v>50.30315431564902</v>
+      </c>
+      <c r="D168" t="s">
+        <v>119</v>
+      </c>
+      <c r="E168" t="s">
+        <v>138</v>
+      </c>
+      <c r="F168" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" t="s">
+        <v>57</v>
+      </c>
+      <c r="B169">
         <v>3150</v>
       </c>
-      <c r="C168">
-        <v>10284.73661716383</v>
-      </c>
-      <c r="D168" t="s">
-        <v>120</v>
-      </c>
-      <c r="E168" t="s">
-        <v>139</v>
-      </c>
-      <c r="F168" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7">
-      <c r="A169" t="s">
-        <v>68</v>
-      </c>
-      <c r="B169">
-        <v>2750</v>
-      </c>
       <c r="C169">
-        <v>10284.73661716383</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D169" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E169" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F169" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="B170">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C170">
-        <v>10284.73661716383</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D170" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E170" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F170" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="B171">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="C171">
-        <v>10229.86188614189</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D171" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E171" t="s">
-        <v>140</v>
-      </c>
-      <c r="G171" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7">
+        <v>138</v>
+      </c>
+      <c r="F171" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B172">
         <v>2250</v>
       </c>
       <c r="C172">
-        <v>10229.86188614189</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D172" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E172" t="s">
-        <v>140</v>
-      </c>
-      <c r="G172" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7">
+        <v>139</v>
+      </c>
+      <c r="F172" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B173">
-        <v>3150</v>
+        <v>2100</v>
       </c>
       <c r="C173">
-        <v>10229.86188614189</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D173" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E173" t="s">
-        <v>140</v>
-      </c>
-      <c r="G173" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7">
+        <v>139</v>
+      </c>
+      <c r="F173" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B174">
-        <v>4750</v>
+        <v>2100</v>
       </c>
       <c r="C174">
-        <v>10229.86188614189</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D174" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E174" t="s">
-        <v>140</v>
-      </c>
-      <c r="G174" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7">
+        <v>139</v>
+      </c>
+      <c r="F174" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="B175">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C175">
-        <v>10229.86188614189</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D175" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E175" t="s">
-        <v>140</v>
-      </c>
-      <c r="G175" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7">
+        <v>139</v>
+      </c>
+      <c r="F175" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B176">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="C176">
-        <v>10229.86188614189</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D176" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E176" t="s">
-        <v>140</v>
-      </c>
-      <c r="G176" t="s">
-        <v>155</v>
+        <v>139</v>
+      </c>
+      <c r="F176" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="177" spans="1:7">
       <c r="A177" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="B177">
-        <v>2750</v>
+        <v>1300</v>
       </c>
       <c r="C177">
-        <v>10229.86188614189</v>
+        <v>10284.73661716383</v>
       </c>
       <c r="D177" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E177" t="s">
-        <v>140</v>
-      </c>
-      <c r="G177" t="s">
-        <v>159</v>
+        <v>139</v>
+      </c>
+      <c r="F177" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="B178">
-        <v>2100</v>
+        <v>2900</v>
       </c>
       <c r="C178">
-        <v>10229.86188614189</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D178" t="s">
         <v>121</v>
@@ -4425,19 +4425,19 @@
       <c r="E178" t="s">
         <v>140</v>
       </c>
-      <c r="G178" t="s">
-        <v>159</v>
+      <c r="F178" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="B179">
-        <v>2250</v>
+        <v>1150</v>
       </c>
       <c r="C179">
-        <v>10229.86188614189</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D179" t="s">
         <v>121</v>
@@ -4445,48 +4445,48 @@
       <c r="E179" t="s">
         <v>140</v>
       </c>
-      <c r="G179" t="s">
-        <v>159</v>
+      <c r="F179" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B180">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C180">
         <v>10229.86188614189</v>
       </c>
       <c r="D180" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E180" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G180" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="181" spans="1:7">
       <c r="A181" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B181">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="C181">
         <v>10229.86188614189</v>
       </c>
       <c r="D181" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E181" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G181" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -4500,184 +4500,184 @@
         <v>10229.86188614189</v>
       </c>
       <c r="D182" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E182" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G182" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B183">
-        <v>3150</v>
+        <v>2100</v>
       </c>
       <c r="C183">
         <v>10229.86188614189</v>
       </c>
       <c r="D183" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E183" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G183" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B184">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C184">
         <v>10229.86188614189</v>
       </c>
       <c r="D184" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E184" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G184" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="185" spans="1:7">
       <c r="A185" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B185">
-        <v>2100</v>
+        <v>2600</v>
       </c>
       <c r="C185">
         <v>10229.86188614189</v>
       </c>
       <c r="D185" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E185" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G185" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B186">
-        <v>2100</v>
+        <v>2750</v>
       </c>
       <c r="C186">
         <v>10229.86188614189</v>
       </c>
       <c r="D186" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E186" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G186" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="B187">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="C187">
         <v>10229.86188614189</v>
       </c>
       <c r="D187" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E187" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G187" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="B188">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C188">
         <v>10229.86188614189</v>
       </c>
       <c r="D188" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E188" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G188" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B189">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="C189">
         <v>10229.86188614189</v>
       </c>
       <c r="D189" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E189" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G189" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B190">
-        <v>2600</v>
+        <v>3150</v>
       </c>
       <c r="C190">
         <v>10229.86188614189</v>
       </c>
       <c r="D190" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E190" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G190" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="B191">
-        <v>800</v>
+        <v>3250</v>
       </c>
       <c r="C191">
-        <v>117.129363815579</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D191" t="s">
         <v>122</v>
@@ -4685,19 +4685,19 @@
       <c r="E191" t="s">
         <v>141</v>
       </c>
-      <c r="F191" t="s">
-        <v>148</v>
+      <c r="G191" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="192" spans="1:7">
       <c r="A192" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B192">
-        <v>2200</v>
+        <v>2250</v>
       </c>
       <c r="C192">
-        <v>56.09574693011376</v>
+        <v>95.89167399587038</v>
       </c>
       <c r="D192" t="s">
         <v>122</v>
@@ -4705,19 +4705,19 @@
       <c r="E192" t="s">
         <v>141</v>
       </c>
-      <c r="F192" t="s">
-        <v>148</v>
+      <c r="G192" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B193">
-        <v>2750</v>
+        <v>3150</v>
       </c>
       <c r="C193">
-        <v>56.09574693011376</v>
+        <v>95.89167399587038</v>
       </c>
       <c r="D193" t="s">
         <v>122</v>
@@ -4725,19 +4725,19 @@
       <c r="E193" t="s">
         <v>141</v>
       </c>
-      <c r="F193" t="s">
-        <v>148</v>
+      <c r="G193" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="194" spans="1:7">
       <c r="A194" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="B194">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="C194">
-        <v>56.09574693011376</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D194" t="s">
         <v>122</v>
@@ -4745,19 +4745,19 @@
       <c r="E194" t="s">
         <v>141</v>
       </c>
-      <c r="F194" t="s">
-        <v>148</v>
+      <c r="G194" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="195" spans="1:7">
       <c r="A195" t="s">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="B195">
         <v>3150</v>
       </c>
       <c r="C195">
-        <v>117.129363815579</v>
+        <v>95.89167399587038</v>
       </c>
       <c r="D195" t="s">
         <v>122</v>
@@ -4765,156 +4765,156 @@
       <c r="E195" t="s">
         <v>141</v>
       </c>
-      <c r="F195" t="s">
-        <v>148</v>
+      <c r="G195" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="196" spans="1:7">
       <c r="A196" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B196">
-        <v>3300</v>
+        <v>3500</v>
       </c>
       <c r="C196">
-        <v>10229.86188614189</v>
+        <v>101.0490418703856</v>
       </c>
       <c r="D196" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E196" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G196" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="197" spans="1:7">
       <c r="A197" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="B197">
-        <v>3300</v>
+        <v>3150</v>
       </c>
       <c r="C197">
-        <v>10229.86188614189</v>
+        <v>101.0490418703856</v>
       </c>
       <c r="D197" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E197" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G197" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="198" spans="1:7">
       <c r="A198" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="B198">
-        <v>900</v>
+        <v>2100</v>
       </c>
       <c r="C198">
-        <v>10229.86188614189</v>
+        <v>101.0490418703856</v>
       </c>
       <c r="D198" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E198" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G198" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="199" spans="1:7">
       <c r="A199" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B199">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C199">
-        <v>5.315090988968437</v>
+        <v>10229.86188614189</v>
       </c>
       <c r="D199" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E199" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G199" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="200" spans="1:7">
       <c r="A200" t="s">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="B200">
         <v>3150</v>
       </c>
       <c r="C200">
-        <v>5.315090988968437</v>
+        <v>95.89167399587038</v>
       </c>
       <c r="D200" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E200" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G200" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="201" spans="1:7">
       <c r="A201" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="B201">
-        <v>2600</v>
+        <v>2300</v>
       </c>
       <c r="C201">
-        <v>5.315090988968437</v>
+        <v>95.89167399587038</v>
       </c>
       <c r="D201" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E201" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G201" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="202" spans="1:7">
       <c r="A202" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="B202">
-        <v>2500</v>
+        <v>250</v>
       </c>
       <c r="C202">
-        <v>5.315090988968437</v>
+        <v>95.89167399587038</v>
       </c>
       <c r="D202" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E202" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G202" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B203">
-        <v>3250</v>
+        <v>2100</v>
       </c>
       <c r="C203">
         <v>5.315090988968437</v>
@@ -4926,15 +4926,15 @@
         <v>142</v>
       </c>
       <c r="G203" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B204">
-        <v>3150</v>
+        <v>950</v>
       </c>
       <c r="C204">
         <v>5.315090988968437</v>
@@ -4946,15 +4946,15 @@
         <v>142</v>
       </c>
       <c r="G204" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="B205">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="C205">
         <v>5.315090988968437</v>
@@ -4966,15 +4966,15 @@
         <v>142</v>
       </c>
       <c r="G205" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" t="s">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="B206">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="C206">
         <v>5.315090988968437</v>
@@ -4986,15 +4986,15 @@
         <v>142</v>
       </c>
       <c r="G206" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="207" spans="1:7">
       <c r="A207" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="B207">
-        <v>3500</v>
+        <v>2250</v>
       </c>
       <c r="C207">
         <v>5.315090988968437</v>
@@ -5006,15 +5006,15 @@
         <v>142</v>
       </c>
       <c r="G207" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="208" spans="1:7">
       <c r="A208" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B208">
-        <v>100</v>
+        <v>2300</v>
       </c>
       <c r="C208">
         <v>5.315090988968437</v>
@@ -5026,15 +5026,15 @@
         <v>142</v>
       </c>
       <c r="G208" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="209" spans="1:7">
       <c r="A209" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B209">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C209">
         <v>5.315090988968437</v>
@@ -5046,15 +5046,15 @@
         <v>142</v>
       </c>
       <c r="G209" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="210" spans="1:7">
       <c r="A210" t="s">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="B210">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C210">
         <v>5.315090988968437</v>
@@ -5066,15 +5066,15 @@
         <v>142</v>
       </c>
       <c r="G210" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="211" spans="1:7">
       <c r="A211" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B211">
-        <v>1800</v>
+        <v>2600</v>
       </c>
       <c r="C211">
         <v>5.315090988968437</v>
@@ -5086,115 +5086,115 @@
         <v>142</v>
       </c>
       <c r="G211" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="212" spans="1:7">
       <c r="A212" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B212">
-        <v>3300</v>
+        <v>2250</v>
       </c>
       <c r="C212">
-        <v>0</v>
+        <v>5.315090988968437</v>
       </c>
       <c r="D212" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E212" t="s">
-        <v>143</v>
-      </c>
-      <c r="F212" t="s">
-        <v>153</v>
+        <v>142</v>
+      </c>
+      <c r="G212" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="213" spans="1:7">
       <c r="A213" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="B213">
-        <v>3150</v>
+        <v>2100</v>
       </c>
       <c r="C213">
-        <v>0</v>
+        <v>5.315090988968437</v>
       </c>
       <c r="D213" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E213" t="s">
-        <v>143</v>
-      </c>
-      <c r="F213" t="s">
-        <v>146</v>
+        <v>142</v>
+      </c>
+      <c r="G213" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="214" spans="1:7">
       <c r="A214" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B214">
         <v>2500</v>
       </c>
       <c r="C214">
-        <v>0</v>
+        <v>5.315090988968437</v>
       </c>
       <c r="D214" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E214" t="s">
-        <v>143</v>
-      </c>
-      <c r="F214" t="s">
-        <v>146</v>
+        <v>142</v>
+      </c>
+      <c r="G214" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="215" spans="1:7">
       <c r="A215" t="s">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="B215">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="C215">
-        <v>0</v>
+        <v>5.315090988968437</v>
       </c>
       <c r="D215" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E215" t="s">
-        <v>143</v>
-      </c>
-      <c r="F215" t="s">
-        <v>146</v>
+        <v>142</v>
+      </c>
+      <c r="G215" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="216" spans="1:7">
       <c r="A216" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="B216">
-        <v>2900</v>
+        <v>3100</v>
       </c>
       <c r="C216">
-        <v>0</v>
+        <v>5.315090988968437</v>
       </c>
       <c r="D216" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E216" t="s">
-        <v>143</v>
-      </c>
-      <c r="F216" t="s">
-        <v>148</v>
+        <v>142</v>
+      </c>
+      <c r="G216" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="217" spans="1:7">
       <c r="A217" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="B217">
-        <v>2100</v>
+        <v>3150</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -5206,15 +5206,15 @@
         <v>143</v>
       </c>
       <c r="F217" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="218" spans="1:7">
       <c r="A218" t="s">
-        <v>9</v>
+        <v>103</v>
       </c>
       <c r="B218">
-        <v>3150</v>
+        <v>2100</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -5226,15 +5226,15 @@
         <v>143</v>
       </c>
       <c r="F218" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="219" spans="1:7">
       <c r="A219" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="B219">
-        <v>2600</v>
+        <v>3500</v>
       </c>
       <c r="C219">
         <v>0</v>
@@ -5246,15 +5246,15 @@
         <v>143</v>
       </c>
       <c r="F219" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="220" spans="1:7">
       <c r="A220" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="B220">
-        <v>1800</v>
+        <v>3150</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -5266,15 +5266,15 @@
         <v>143</v>
       </c>
       <c r="F220" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="221" spans="1:7">
       <c r="A221" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B221">
-        <v>3300</v>
+        <v>2600</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -5286,15 +5286,15 @@
         <v>143</v>
       </c>
       <c r="F221" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="222" spans="1:7">
       <c r="A222" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="B222">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -5306,15 +5306,15 @@
         <v>143</v>
       </c>
       <c r="F222" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="223" spans="1:7">
       <c r="A223" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="B223">
-        <v>4750</v>
+        <v>3150</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -5331,10 +5331,10 @@
     </row>
     <row r="224" spans="1:7">
       <c r="A224" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B224">
-        <v>2250</v>
+        <v>3250</v>
       </c>
       <c r="C224">
         <v>0</v>
@@ -5346,15 +5346,15 @@
         <v>143</v>
       </c>
       <c r="F224" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="225" spans="1:7">
       <c r="A225" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B225">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -5366,15 +5366,15 @@
         <v>143</v>
       </c>
       <c r="F225" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="226" spans="1:7">
       <c r="A226" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="B226">
-        <v>2250</v>
+        <v>2900</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -5386,12 +5386,12 @@
         <v>143</v>
       </c>
       <c r="F226" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="227" spans="1:7">
       <c r="A227" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B227">
         <v>2100</v>
@@ -5406,7 +5406,7 @@
         <v>143</v>
       </c>
       <c r="F227" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -5426,15 +5426,15 @@
         <v>143</v>
       </c>
       <c r="F228" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="229" spans="1:7">
       <c r="A229" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B229">
-        <v>1800</v>
+        <v>3150</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -5446,15 +5446,15 @@
         <v>143</v>
       </c>
       <c r="F229" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="230" spans="1:7">
       <c r="A230" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="B230">
-        <v>3150</v>
+        <v>2300</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -5466,95 +5466,95 @@
         <v>143</v>
       </c>
       <c r="F230" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="231" spans="1:7">
       <c r="A231" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="B231">
-        <v>3250</v>
+        <v>3150</v>
       </c>
       <c r="C231">
-        <v>10228.71383241515</v>
+        <v>0</v>
       </c>
       <c r="D231" t="s">
         <v>124</v>
       </c>
       <c r="E231" t="s">
-        <v>144</v>
-      </c>
-      <c r="G231" t="s">
-        <v>161</v>
+        <v>143</v>
+      </c>
+      <c r="F231" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="232" spans="1:7">
       <c r="A232" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="B232">
         <v>2250</v>
       </c>
       <c r="C232">
-        <v>10228.71383241515</v>
+        <v>0</v>
       </c>
       <c r="D232" t="s">
         <v>124</v>
       </c>
       <c r="E232" t="s">
-        <v>144</v>
-      </c>
-      <c r="G232" t="s">
-        <v>161</v>
+        <v>143</v>
+      </c>
+      <c r="F232" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="233" spans="1:7">
       <c r="A233" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="B233">
-        <v>3100</v>
+        <v>2600</v>
       </c>
       <c r="C233">
-        <v>10228.71383241515</v>
+        <v>0</v>
       </c>
       <c r="D233" t="s">
         <v>124</v>
       </c>
       <c r="E233" t="s">
-        <v>144</v>
-      </c>
-      <c r="G233" t="s">
-        <v>157</v>
+        <v>143</v>
+      </c>
+      <c r="F233" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="234" spans="1:7">
       <c r="A234" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B234">
-        <v>3150</v>
+        <v>1800</v>
       </c>
       <c r="C234">
-        <v>10228.71383241515</v>
+        <v>0</v>
       </c>
       <c r="D234" t="s">
         <v>124</v>
       </c>
       <c r="E234" t="s">
-        <v>144</v>
-      </c>
-      <c r="G234" t="s">
-        <v>157</v>
+        <v>143</v>
+      </c>
+      <c r="F234" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="235" spans="1:7">
       <c r="A235" t="s">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="B235">
-        <v>2300</v>
+        <v>2100</v>
       </c>
       <c r="C235">
         <v>0</v>
@@ -5563,18 +5563,18 @@
         <v>124</v>
       </c>
       <c r="E235" t="s">
-        <v>144</v>
-      </c>
-      <c r="G235" t="s">
-        <v>158</v>
+        <v>143</v>
+      </c>
+      <c r="F235" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="236" spans="1:7">
       <c r="A236" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="B236">
-        <v>1800</v>
+        <v>2500</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -5586,15 +5586,15 @@
         <v>144</v>
       </c>
       <c r="G236" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="237" spans="1:7">
       <c r="A237" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B237">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -5606,15 +5606,15 @@
         <v>144</v>
       </c>
       <c r="G237" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="238" spans="1:7">
       <c r="A238" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="B238">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -5626,15 +5626,15 @@
         <v>144</v>
       </c>
       <c r="G238" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="239" spans="1:7">
       <c r="A239" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="B239">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -5651,13 +5651,13 @@
     </row>
     <row r="240" spans="1:7">
       <c r="A240" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B240">
-        <v>2250</v>
+        <v>3150</v>
       </c>
       <c r="C240">
-        <v>10228.71383241515</v>
+        <v>0</v>
       </c>
       <c r="D240" t="s">
         <v>124</v>
@@ -5671,13 +5671,13 @@
     </row>
     <row r="241" spans="1:7">
       <c r="A241" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="B241">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="C241">
-        <v>0</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D241" t="s">
         <v>124</v>
@@ -5686,18 +5686,18 @@
         <v>144</v>
       </c>
       <c r="G241" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="242" spans="1:7">
       <c r="A242" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="B242">
-        <v>3150</v>
+        <v>2100</v>
       </c>
       <c r="C242">
-        <v>0</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D242" t="s">
         <v>124</v>
@@ -5706,18 +5706,18 @@
         <v>144</v>
       </c>
       <c r="G242" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="243" spans="1:7">
       <c r="A243" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="B243">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C243">
-        <v>0</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D243" t="s">
         <v>124</v>
@@ -5731,13 +5731,13 @@
     </row>
     <row r="244" spans="1:7">
       <c r="A244" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="B244">
         <v>2750</v>
       </c>
       <c r="C244">
-        <v>0</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D244" t="s">
         <v>124</v>
@@ -5751,13 +5751,13 @@
     </row>
     <row r="245" spans="1:7">
       <c r="A245" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="B245">
-        <v>2250</v>
+        <v>3250</v>
       </c>
       <c r="C245">
-        <v>0</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D245" t="s">
         <v>124</v>
@@ -5766,18 +5766,18 @@
         <v>144</v>
       </c>
       <c r="G245" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="246" spans="1:7">
       <c r="A246" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="B246">
-        <v>3150</v>
+        <v>1800</v>
       </c>
       <c r="C246">
-        <v>10228.71383241515</v>
+        <v>0</v>
       </c>
       <c r="D246" t="s">
         <v>124</v>
@@ -5786,18 +5786,18 @@
         <v>144</v>
       </c>
       <c r="G246" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="247" spans="1:7">
       <c r="A247" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="B247">
-        <v>2900</v>
+        <v>3150</v>
       </c>
       <c r="C247">
-        <v>10228.71383241515</v>
+        <v>0</v>
       </c>
       <c r="D247" t="s">
         <v>124</v>
@@ -5806,18 +5806,18 @@
         <v>144</v>
       </c>
       <c r="G247" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="248" spans="1:7">
       <c r="A248" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="B248">
-        <v>2900</v>
+        <v>1800</v>
       </c>
       <c r="C248">
-        <v>10228.71383241515</v>
+        <v>0</v>
       </c>
       <c r="D248" t="s">
         <v>124</v>
@@ -5826,18 +5826,18 @@
         <v>144</v>
       </c>
       <c r="G248" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="249" spans="1:7">
       <c r="A249" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="B249">
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="C249">
-        <v>10228.71383241515</v>
+        <v>0</v>
       </c>
       <c r="D249" t="s">
         <v>124</v>
@@ -5846,15 +5846,15 @@
         <v>144</v>
       </c>
       <c r="G249" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="250" spans="1:7">
       <c r="A250" t="s">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="B250">
-        <v>2250</v>
+        <v>2900</v>
       </c>
       <c r="C250">
         <v>0</v>
@@ -5863,118 +5863,118 @@
         <v>124</v>
       </c>
       <c r="E250" t="s">
-        <v>143</v>
-      </c>
-      <c r="F250" t="s">
-        <v>148</v>
+        <v>144</v>
+      </c>
+      <c r="G250" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="251" spans="1:7">
       <c r="A251" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="B251">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C251">
-        <v>0</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D251" t="s">
         <v>124</v>
       </c>
       <c r="E251" t="s">
-        <v>143</v>
-      </c>
-      <c r="F251" t="s">
-        <v>148</v>
+        <v>144</v>
+      </c>
+      <c r="G251" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="252" spans="1:7">
       <c r="A252" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="B252">
-        <v>2250</v>
+        <v>3500</v>
       </c>
       <c r="C252">
-        <v>0</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D252" t="s">
         <v>124</v>
       </c>
       <c r="E252" t="s">
-        <v>143</v>
-      </c>
-      <c r="F252" t="s">
-        <v>148</v>
+        <v>144</v>
+      </c>
+      <c r="G252" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="253" spans="1:7">
       <c r="A253" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="B253">
-        <v>2250</v>
+        <v>2150</v>
       </c>
       <c r="C253">
-        <v>0</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D253" t="s">
         <v>124</v>
       </c>
       <c r="E253" t="s">
-        <v>143</v>
-      </c>
-      <c r="F253" t="s">
-        <v>148</v>
+        <v>144</v>
+      </c>
+      <c r="G253" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="254" spans="1:7">
       <c r="A254" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="B254">
         <v>2250</v>
       </c>
       <c r="C254">
-        <v>0</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D254" t="s">
         <v>124</v>
       </c>
       <c r="E254" t="s">
-        <v>143</v>
-      </c>
-      <c r="F254" t="s">
-        <v>150</v>
+        <v>144</v>
+      </c>
+      <c r="G254" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="255" spans="1:7">
       <c r="A255" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="B255">
-        <v>2750</v>
+        <v>2250</v>
       </c>
       <c r="C255">
-        <v>0</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D255" t="s">
         <v>124</v>
       </c>
       <c r="E255" t="s">
-        <v>143</v>
-      </c>
-      <c r="F255" t="s">
-        <v>150</v>
+        <v>144</v>
+      </c>
+      <c r="G255" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="256" spans="1:7">
       <c r="A256" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="B256">
-        <v>3250</v>
+        <v>3150</v>
       </c>
       <c r="C256">
         <v>0</v>
@@ -5986,15 +5986,15 @@
         <v>143</v>
       </c>
       <c r="F256" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
       <c r="A257" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="B257">
-        <v>3150</v>
+        <v>1500</v>
       </c>
       <c r="C257">
         <v>0</v>
@@ -6006,15 +6006,15 @@
         <v>143</v>
       </c>
       <c r="F257" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
       <c r="A258" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B258">
-        <v>2250</v>
+        <v>2100</v>
       </c>
       <c r="C258">
         <v>0</v>
@@ -6026,15 +6026,15 @@
         <v>143</v>
       </c>
       <c r="F258" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
       <c r="A259" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="B259">
-        <v>2250</v>
+        <v>3300</v>
       </c>
       <c r="C259">
         <v>0</v>
@@ -6046,15 +6046,15 @@
         <v>143</v>
       </c>
       <c r="F259" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
       <c r="A260" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="B260">
-        <v>2700</v>
+        <v>3100</v>
       </c>
       <c r="C260">
         <v>0</v>
@@ -6066,15 +6066,15 @@
         <v>143</v>
       </c>
       <c r="F260" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
       <c r="A261" t="s">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="B261">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="C261">
         <v>0</v>
@@ -6086,15 +6086,15 @@
         <v>143</v>
       </c>
       <c r="F261" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
       <c r="A262" t="s">
         <v>89</v>
       </c>
       <c r="B262">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C262">
         <v>0</v>
@@ -6106,15 +6106,15 @@
         <v>143</v>
       </c>
       <c r="F262" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
       <c r="A263" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="B263">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="C263">
         <v>0</v>
@@ -6126,15 +6126,15 @@
         <v>143</v>
       </c>
       <c r="F263" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
       <c r="A264" t="s">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="B264">
-        <v>2250</v>
+        <v>2900</v>
       </c>
       <c r="C264">
         <v>0</v>
@@ -6149,12 +6149,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="265" spans="1:7">
+    <row r="265" spans="1:6">
       <c r="A265" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B265">
-        <v>1450</v>
+        <v>2500</v>
       </c>
       <c r="C265">
         <v>0</v>
@@ -6166,15 +6166,15 @@
         <v>143</v>
       </c>
       <c r="F265" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
       <c r="A266" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="B266">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C266">
         <v>0</v>
@@ -6186,15 +6186,15 @@
         <v>143</v>
       </c>
       <c r="F266" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
       <c r="A267" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B267">
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="C267">
         <v>0</v>
@@ -6206,15 +6206,15 @@
         <v>143</v>
       </c>
       <c r="F267" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
       <c r="A268" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="B268">
-        <v>2750</v>
+        <v>2250</v>
       </c>
       <c r="C268">
         <v>0</v>
@@ -6226,15 +6226,15 @@
         <v>143</v>
       </c>
       <c r="F268" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
       <c r="A269" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="B269">
-        <v>3150</v>
+        <v>2200</v>
       </c>
       <c r="C269">
         <v>0</v>
@@ -6246,135 +6246,135 @@
         <v>143</v>
       </c>
       <c r="F269" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
       <c r="A270" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="B270">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C270">
         <v>0</v>
       </c>
       <c r="D270" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E270" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F270" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
       <c r="A271" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="B271">
-        <v>850</v>
+        <v>2500</v>
       </c>
       <c r="C271">
-        <v>10228.98246237894</v>
+        <v>0</v>
       </c>
       <c r="D271" t="s">
         <v>124</v>
       </c>
       <c r="E271" t="s">
-        <v>144</v>
-      </c>
-      <c r="G271" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7">
+        <v>143</v>
+      </c>
+      <c r="F271" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
       <c r="A272" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="B272">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="C272">
-        <v>10228.98246237894</v>
+        <v>0</v>
       </c>
       <c r="D272" t="s">
         <v>124</v>
       </c>
       <c r="E272" t="s">
-        <v>144</v>
-      </c>
-      <c r="G272" t="s">
-        <v>159</v>
+        <v>143</v>
+      </c>
+      <c r="F272" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="273" spans="1:7">
       <c r="A273" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="B273">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C273">
-        <v>10228.98246237894</v>
+        <v>0</v>
       </c>
       <c r="D273" t="s">
         <v>124</v>
       </c>
       <c r="E273" t="s">
-        <v>144</v>
-      </c>
-      <c r="G273" t="s">
-        <v>159</v>
+        <v>143</v>
+      </c>
+      <c r="F273" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="274" spans="1:7">
       <c r="A274" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B274">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C274">
-        <v>10228.98246237894</v>
+        <v>0</v>
       </c>
       <c r="D274" t="s">
         <v>124</v>
       </c>
       <c r="E274" t="s">
-        <v>144</v>
-      </c>
-      <c r="G274" t="s">
-        <v>162</v>
+        <v>143</v>
+      </c>
+      <c r="F274" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="275" spans="1:7">
       <c r="A275" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="B275">
-        <v>2250</v>
+        <v>2900</v>
       </c>
       <c r="C275">
-        <v>10228.98246237894</v>
+        <v>0</v>
       </c>
       <c r="D275" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E275" t="s">
-        <v>144</v>
-      </c>
-      <c r="G275" t="s">
-        <v>162</v>
+        <v>145</v>
+      </c>
+      <c r="F275" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="276" spans="1:7">
       <c r="A276" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="B276">
-        <v>2100</v>
+        <v>3150</v>
       </c>
       <c r="C276">
         <v>10228.98246237894</v>
@@ -6386,15 +6386,15 @@
         <v>144</v>
       </c>
       <c r="G276" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="277" spans="1:7">
       <c r="A277" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="B277">
-        <v>2600</v>
+        <v>3150</v>
       </c>
       <c r="C277">
         <v>10228.98246237894</v>
@@ -6406,15 +6406,15 @@
         <v>144</v>
       </c>
       <c r="G277" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="278" spans="1:7">
       <c r="A278" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B278">
-        <v>1800</v>
+        <v>2600</v>
       </c>
       <c r="C278">
         <v>10228.98246237894</v>
@@ -6426,15 +6426,15 @@
         <v>144</v>
       </c>
       <c r="G278" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="279" spans="1:7">
       <c r="A279" t="s">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="B279">
-        <v>2250</v>
+        <v>2100</v>
       </c>
       <c r="C279">
         <v>10228.98246237894</v>
@@ -6451,10 +6451,10 @@
     </row>
     <row r="280" spans="1:7">
       <c r="A280" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="B280">
-        <v>3300</v>
+        <v>3150</v>
       </c>
       <c r="C280">
         <v>10228.98246237894</v>
@@ -6466,15 +6466,15 @@
         <v>144</v>
       </c>
       <c r="G280" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="281" spans="1:7">
       <c r="A281" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B281">
-        <v>3250</v>
+        <v>2250</v>
       </c>
       <c r="C281">
         <v>10228.98246237894</v>
@@ -6486,18 +6486,18 @@
         <v>144</v>
       </c>
       <c r="G281" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="282" spans="1:7">
       <c r="A282" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B282">
-        <v>3000</v>
+        <v>3150</v>
       </c>
       <c r="C282">
-        <v>10228.71383241515</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D282" t="s">
         <v>124</v>
@@ -6511,13 +6511,13 @@
     </row>
     <row r="283" spans="1:7">
       <c r="A283" t="s">
-        <v>106</v>
+        <v>29</v>
       </c>
       <c r="B283">
-        <v>2100</v>
+        <v>2900</v>
       </c>
       <c r="C283">
-        <v>10228.71383241515</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D283" t="s">
         <v>124</v>
@@ -6531,10 +6531,10 @@
     </row>
     <row r="284" spans="1:7">
       <c r="A284" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B284">
-        <v>2250</v>
+        <v>3250</v>
       </c>
       <c r="C284">
         <v>10228.98246237894</v>
@@ -6546,15 +6546,15 @@
         <v>144</v>
       </c>
       <c r="G284" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="285" spans="1:7">
       <c r="A285" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="B285">
-        <v>2500</v>
+        <v>350</v>
       </c>
       <c r="C285">
         <v>10228.98246237894</v>
@@ -6566,18 +6566,18 @@
         <v>144</v>
       </c>
       <c r="G285" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="286" spans="1:7">
       <c r="A286" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="B286">
-        <v>4750</v>
+        <v>2750</v>
       </c>
       <c r="C286">
-        <v>10228.98246237894</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D286" t="s">
         <v>124</v>
@@ -6586,18 +6586,18 @@
         <v>144</v>
       </c>
       <c r="G286" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="287" spans="1:7">
       <c r="A287" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B287">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="C287">
-        <v>10228.98246237894</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D287" t="s">
         <v>124</v>
@@ -6606,18 +6606,18 @@
         <v>144</v>
       </c>
       <c r="G287" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="288" spans="1:7">
       <c r="A288" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="B288">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="C288">
-        <v>10228.98246237894</v>
+        <v>10228.71383241515</v>
       </c>
       <c r="D288" t="s">
         <v>124</v>
@@ -6626,15 +6626,15 @@
         <v>144</v>
       </c>
       <c r="G288" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="289" spans="1:7">
       <c r="A289" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="B289">
-        <v>3150</v>
+        <v>2100</v>
       </c>
       <c r="C289">
         <v>10228.98246237894</v>
@@ -6646,95 +6646,95 @@
         <v>144</v>
       </c>
       <c r="G289" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="290" spans="1:7">
       <c r="A290" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="B290">
-        <v>2900</v>
+        <v>2300</v>
       </c>
       <c r="C290">
-        <v>0</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D290" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E290" t="s">
-        <v>145</v>
-      </c>
-      <c r="F290" t="s">
-        <v>154</v>
+        <v>144</v>
+      </c>
+      <c r="G290" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="291" spans="1:7">
       <c r="A291" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="B291">
-        <v>3150</v>
+        <v>2500</v>
       </c>
       <c r="C291">
-        <v>0</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D291" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E291" t="s">
-        <v>145</v>
-      </c>
-      <c r="F291" t="s">
-        <v>154</v>
+        <v>144</v>
+      </c>
+      <c r="G291" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="292" spans="1:7">
       <c r="A292" t="s">
-        <v>103</v>
+        <v>42</v>
       </c>
       <c r="B292">
-        <v>2100</v>
+        <v>3500</v>
       </c>
       <c r="C292">
-        <v>0</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D292" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E292" t="s">
-        <v>145</v>
-      </c>
-      <c r="F292" t="s">
-        <v>154</v>
+        <v>144</v>
+      </c>
+      <c r="G292" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="293" spans="1:7">
       <c r="A293" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="B293">
-        <v>3100</v>
+        <v>3150</v>
       </c>
       <c r="C293">
-        <v>0</v>
+        <v>10228.98246237894</v>
       </c>
       <c r="D293" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E293" t="s">
-        <v>145</v>
-      </c>
-      <c r="F293" t="s">
-        <v>154</v>
+        <v>144</v>
+      </c>
+      <c r="G293" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="294" spans="1:7">
       <c r="A294" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B294">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="C294">
         <v>0</v>
@@ -6746,15 +6746,15 @@
         <v>145</v>
       </c>
       <c r="F294" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="295" spans="1:7">
       <c r="A295" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="B295">
-        <v>2250</v>
+        <v>2100</v>
       </c>
       <c r="C295">
         <v>0</v>
@@ -6766,12 +6766,12 @@
         <v>145</v>
       </c>
       <c r="F295" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="296" spans="1:7">
       <c r="A296" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="B296">
         <v>3150</v>
@@ -6786,15 +6786,15 @@
         <v>145</v>
       </c>
       <c r="F296" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="297" spans="1:7">
       <c r="A297" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B297">
-        <v>2250</v>
+        <v>2100</v>
       </c>
       <c r="C297">
         <v>0</v>
@@ -6806,12 +6806,12 @@
         <v>145</v>
       </c>
       <c r="F297" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="298" spans="1:7">
       <c r="A298" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B298">
         <v>2900</v>
@@ -6826,15 +6826,15 @@
         <v>145</v>
       </c>
       <c r="F298" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="299" spans="1:7">
       <c r="A299" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="B299">
-        <v>3150</v>
+        <v>2150</v>
       </c>
       <c r="C299">
         <v>0</v>
@@ -6846,15 +6846,15 @@
         <v>145</v>
       </c>
       <c r="F299" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="300" spans="1:7">
       <c r="A300" t="s">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="B300">
-        <v>2100</v>
+        <v>3150</v>
       </c>
       <c r="C300">
         <v>0</v>
@@ -6866,12 +6866,12 @@
         <v>145</v>
       </c>
       <c r="F300" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="301" spans="1:7">
       <c r="A301" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="B301">
         <v>2500</v>
@@ -6886,15 +6886,15 @@
         <v>145</v>
       </c>
       <c r="F301" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="302" spans="1:7">
       <c r="A302" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="B302">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="C302">
         <v>0</v>
@@ -6906,15 +6906,15 @@
         <v>145</v>
       </c>
       <c r="F302" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="303" spans="1:7">
       <c r="A303" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="B303">
-        <v>2600</v>
+        <v>2750</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -6926,15 +6926,15 @@
         <v>145</v>
       </c>
       <c r="F303" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="304" spans="1:7">
       <c r="A304" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B304">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="C304">
         <v>0</v>
@@ -6946,12 +6946,12 @@
         <v>145</v>
       </c>
       <c r="F304" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="305" spans="1:6">
       <c r="A305" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="B305">
         <v>3150</v>
@@ -6966,15 +6966,15 @@
         <v>145</v>
       </c>
       <c r="F305" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="306" spans="1:6">
       <c r="A306" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="B306">
-        <v>1800</v>
+        <v>2250</v>
       </c>
       <c r="C306">
         <v>0</v>
@@ -6986,15 +6986,15 @@
         <v>145</v>
       </c>
       <c r="F306" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="307" spans="1:6">
       <c r="A307" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="B307">
-        <v>2250</v>
+        <v>3500</v>
       </c>
       <c r="C307">
         <v>0</v>
@@ -7006,15 +7006,15 @@
         <v>145</v>
       </c>
       <c r="F307" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="308" spans="1:6">
       <c r="A308" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="B308">
-        <v>2900</v>
+        <v>3250</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -7026,12 +7026,12 @@
         <v>145</v>
       </c>
       <c r="F308" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="309" spans="1:6">
       <c r="A309" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B309">
         <v>2500</v>
@@ -7046,15 +7046,15 @@
         <v>145</v>
       </c>
       <c r="F309" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="310" spans="1:6">
       <c r="A310" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B310">
-        <v>3250</v>
+        <v>2500</v>
       </c>
       <c r="C310">
         <v>0</v>
@@ -7066,15 +7066,15 @@
         <v>145</v>
       </c>
       <c r="F310" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="311" spans="1:6">
       <c r="A311" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B311">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C311">
         <v>0</v>
@@ -7086,15 +7086,15 @@
         <v>145</v>
       </c>
       <c r="F311" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="312" spans="1:6">
       <c r="A312" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="B312">
-        <v>3500</v>
+        <v>1800</v>
       </c>
       <c r="C312">
         <v>0</v>
@@ -7106,18 +7106,18 @@
         <v>145</v>
       </c>
       <c r="F312" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="313" spans="1:6">
       <c r="A313" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="B313">
-        <v>3150</v>
+        <v>2600</v>
       </c>
       <c r="C313">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D313" t="s">
         <v>125</v>
@@ -7126,18 +7126,18 @@
         <v>145</v>
       </c>
       <c r="F313" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="314" spans="1:6">
       <c r="A314" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B314">
-        <v>2250</v>
+        <v>2600</v>
       </c>
       <c r="C314">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D314" t="s">
         <v>125</v>
@@ -7146,18 +7146,18 @@
         <v>145</v>
       </c>
       <c r="F314" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="315" spans="1:6">
       <c r="A315" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="B315">
         <v>2250</v>
       </c>
       <c r="C315">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D315" t="s">
         <v>125</v>
@@ -7166,18 +7166,18 @@
         <v>145</v>
       </c>
       <c r="F315" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="316" spans="1:6">
       <c r="A316" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="B316">
-        <v>1800</v>
+        <v>3500</v>
       </c>
       <c r="C316">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D316" t="s">
         <v>125</v>
@@ -7186,18 +7186,18 @@
         <v>145</v>
       </c>
       <c r="F316" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="317" spans="1:6">
       <c r="A317" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B317">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="C317">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D317" t="s">
         <v>125</v>
@@ -7206,18 +7206,18 @@
         <v>145</v>
       </c>
       <c r="F317" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="318" spans="1:6">
       <c r="A318" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B318">
-        <v>3150</v>
+        <v>2500</v>
       </c>
       <c r="C318">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D318" t="s">
         <v>125</v>
@@ -7226,18 +7226,18 @@
         <v>145</v>
       </c>
       <c r="F318" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="319" spans="1:6">
       <c r="A319" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B319">
-        <v>2900</v>
+        <v>2250</v>
       </c>
       <c r="C319">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D319" t="s">
         <v>125</v>
@@ -7246,18 +7246,18 @@
         <v>145</v>
       </c>
       <c r="F319" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="320" spans="1:6">
       <c r="A320" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="B320">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="C320">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D320" t="s">
         <v>125</v>
@@ -7266,15 +7266,15 @@
         <v>145</v>
       </c>
       <c r="F320" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="321" spans="1:6">
       <c r="A321" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B321">
-        <v>2750</v>
+        <v>2900</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -7286,18 +7286,18 @@
         <v>145</v>
       </c>
       <c r="F321" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="322" spans="1:6">
       <c r="A322" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="B322">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C322">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D322" t="s">
         <v>125</v>
@@ -7306,18 +7306,18 @@
         <v>145</v>
       </c>
       <c r="F322" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="323" spans="1:6">
       <c r="A323" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="B323">
-        <v>1800</v>
+        <v>2750</v>
       </c>
       <c r="C323">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D323" t="s">
         <v>125</v>
@@ -7326,18 +7326,18 @@
         <v>145</v>
       </c>
       <c r="F323" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="324" spans="1:6">
       <c r="A324" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="B324">
-        <v>2250</v>
+        <v>2300</v>
       </c>
       <c r="C324">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D324" t="s">
         <v>125</v>
@@ -7346,18 +7346,18 @@
         <v>145</v>
       </c>
       <c r="F324" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="325" spans="1:6">
       <c r="A325" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="B325">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="C325">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D325" t="s">
         <v>125</v>
@@ -7366,18 +7366,18 @@
         <v>145</v>
       </c>
       <c r="F325" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="326" spans="1:6">
       <c r="A326" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="B326">
-        <v>2600</v>
+        <v>3150</v>
       </c>
       <c r="C326">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D326" t="s">
         <v>125</v>
@@ -7386,18 +7386,18 @@
         <v>145</v>
       </c>
       <c r="F326" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="327" spans="1:6">
       <c r="A327" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="B327">
-        <v>3500</v>
+        <v>3150</v>
       </c>
       <c r="C327">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D327" t="s">
         <v>125</v>
@@ -7406,18 +7406,18 @@
         <v>145</v>
       </c>
       <c r="F327" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="328" spans="1:6">
       <c r="A328" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="B328">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C328">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D328" t="s">
         <v>125</v>
@@ -7426,18 +7426,18 @@
         <v>145</v>
       </c>
       <c r="F328" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="329" spans="1:6">
       <c r="A329" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B329">
-        <v>2250</v>
+        <v>2750</v>
       </c>
       <c r="C329">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D329" t="s">
         <v>125</v>
@@ -7446,18 +7446,18 @@
         <v>145</v>
       </c>
       <c r="F329" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="330" spans="1:6">
       <c r="A330" t="s">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="B330">
-        <v>2600</v>
+        <v>2100</v>
       </c>
       <c r="C330">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D330" t="s">
         <v>125</v>
@@ -7466,18 +7466,18 @@
         <v>145</v>
       </c>
       <c r="F330" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="331" spans="1:6">
       <c r="A331" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="B331">
-        <v>2300</v>
+        <v>2750</v>
       </c>
       <c r="C331">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D331" t="s">
         <v>125</v>
@@ -7486,18 +7486,18 @@
         <v>145</v>
       </c>
       <c r="F331" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="332" spans="1:6">
       <c r="A332" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B332">
-        <v>3250</v>
+        <v>2900</v>
       </c>
       <c r="C332">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D332" t="s">
         <v>125</v>
@@ -7506,15 +7506,15 @@
         <v>145</v>
       </c>
       <c r="F332" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="333" spans="1:6">
       <c r="A333" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B333">
-        <v>2500</v>
+        <v>3250</v>
       </c>
       <c r="C333">
         <v>50.30315431564902</v>
@@ -7526,15 +7526,15 @@
         <v>145</v>
       </c>
       <c r="F333" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="334" spans="1:6">
       <c r="A334" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="B334">
-        <v>3150</v>
+        <v>2500</v>
       </c>
       <c r="C334">
         <v>50.30315431564902</v>
@@ -7546,15 +7546,15 @@
         <v>145</v>
       </c>
       <c r="F334" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="335" spans="1:6">
       <c r="A335" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="B335">
-        <v>2900</v>
+        <v>2600</v>
       </c>
       <c r="C335">
         <v>50.30315431564902</v>
@@ -7566,15 +7566,15 @@
         <v>145</v>
       </c>
       <c r="F335" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="336" spans="1:6">
       <c r="A336" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B336">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C336">
         <v>50.30315431564902</v>
@@ -7586,18 +7586,18 @@
         <v>145</v>
       </c>
       <c r="F336" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="337" spans="1:6">
       <c r="A337" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B337">
-        <v>3150</v>
+        <v>2500</v>
       </c>
       <c r="C337">
-        <v>56.09574693011376</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D337" t="s">
         <v>125</v>
@@ -7606,18 +7606,18 @@
         <v>145</v>
       </c>
       <c r="F337" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="338" spans="1:6">
       <c r="A338" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B338">
-        <v>2100</v>
+        <v>3150</v>
       </c>
       <c r="C338">
-        <v>56.09574693011376</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D338" t="s">
         <v>125</v>
@@ -7626,15 +7626,15 @@
         <v>145</v>
       </c>
       <c r="F338" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="339" spans="1:6">
       <c r="A339" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="B339">
-        <v>2250</v>
+        <v>1800</v>
       </c>
       <c r="C339">
         <v>50.30315431564902</v>
@@ -7646,15 +7646,15 @@
         <v>145</v>
       </c>
       <c r="F339" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="340" spans="1:6">
       <c r="A340" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B340">
-        <v>2900</v>
+        <v>4750</v>
       </c>
       <c r="C340">
         <v>50.30315431564902</v>
@@ -7671,13 +7671,13 @@
     </row>
     <row r="341" spans="1:6">
       <c r="A341" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B341">
-        <v>2750</v>
+        <v>3150</v>
       </c>
       <c r="C341">
-        <v>50.30315431564902</v>
+        <v>0</v>
       </c>
       <c r="D341" t="s">
         <v>125</v>
@@ -7686,18 +7686,18 @@
         <v>145</v>
       </c>
       <c r="F341" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="342" spans="1:6">
       <c r="A342" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="B342">
-        <v>2200</v>
+        <v>3250</v>
       </c>
       <c r="C342">
-        <v>10331.50326630582</v>
+        <v>0</v>
       </c>
       <c r="D342" t="s">
         <v>125</v>
@@ -7706,18 +7706,18 @@
         <v>145</v>
       </c>
       <c r="F342" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="343" spans="1:6">
       <c r="A343" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="B343">
-        <v>2150</v>
+        <v>2500</v>
       </c>
       <c r="C343">
-        <v>10331.50326630582</v>
+        <v>0</v>
       </c>
       <c r="D343" t="s">
         <v>125</v>
@@ -7726,18 +7726,18 @@
         <v>145</v>
       </c>
       <c r="F343" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="344" spans="1:6">
       <c r="A344" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B344">
-        <v>2900</v>
+        <v>2250</v>
       </c>
       <c r="C344">
-        <v>10331.50326630582</v>
+        <v>0</v>
       </c>
       <c r="D344" t="s">
         <v>125</v>
@@ -7746,18 +7746,18 @@
         <v>145</v>
       </c>
       <c r="F344" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="345" spans="1:6">
       <c r="A345" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="B345">
-        <v>3150</v>
+        <v>2500</v>
       </c>
       <c r="C345">
-        <v>10331.50326630582</v>
+        <v>0</v>
       </c>
       <c r="D345" t="s">
         <v>125</v>
@@ -7766,18 +7766,18 @@
         <v>145</v>
       </c>
       <c r="F345" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="346" spans="1:6">
       <c r="A346" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="B346">
-        <v>2250</v>
+        <v>2900</v>
       </c>
       <c r="C346">
-        <v>56.09574693011376</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D346" t="s">
         <v>125</v>
@@ -7786,18 +7786,18 @@
         <v>145</v>
       </c>
       <c r="F346" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="347" spans="1:6">
       <c r="A347" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B347">
-        <v>2750</v>
+        <v>2250</v>
       </c>
       <c r="C347">
-        <v>10331.50326630582</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D347" t="s">
         <v>125</v>
@@ -7806,18 +7806,18 @@
         <v>145</v>
       </c>
       <c r="F347" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="348" spans="1:6">
       <c r="A348" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="B348">
-        <v>2250</v>
+        <v>2100</v>
       </c>
       <c r="C348">
-        <v>114.8097329106024</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D348" t="s">
         <v>125</v>
@@ -7826,18 +7826,18 @@
         <v>145</v>
       </c>
       <c r="F348" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="349" spans="1:6">
       <c r="A349" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="B349">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="C349">
-        <v>114.8097329106024</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D349" t="s">
         <v>125</v>
@@ -7846,18 +7846,18 @@
         <v>145</v>
       </c>
       <c r="F349" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="350" spans="1:6">
       <c r="A350" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="B350">
-        <v>1800</v>
+        <v>2250</v>
       </c>
       <c r="C350">
-        <v>114.8097329106024</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D350" t="s">
         <v>125</v>
@@ -7866,18 +7866,18 @@
         <v>145</v>
       </c>
       <c r="F350" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="351" spans="1:6">
       <c r="A351" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="B351">
-        <v>2500</v>
+        <v>2750</v>
       </c>
       <c r="C351">
-        <v>114.8097329106024</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D351" t="s">
         <v>125</v>
@@ -7886,18 +7886,18 @@
         <v>145</v>
       </c>
       <c r="F351" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="352" spans="1:6">
       <c r="A352" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B352">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="C352">
-        <v>114.8097329106024</v>
+        <v>10331.50326630582</v>
       </c>
       <c r="D352" t="s">
         <v>125</v>
@@ -7906,18 +7906,18 @@
         <v>145</v>
       </c>
       <c r="F352" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="353" spans="1:6">
       <c r="A353" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="B353">
-        <v>2100</v>
+        <v>3150</v>
       </c>
       <c r="C353">
-        <v>114.8097329106024</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D353" t="s">
         <v>125</v>
@@ -7926,18 +7926,18 @@
         <v>145</v>
       </c>
       <c r="F353" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="354" spans="1:6">
       <c r="A354" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="B354">
-        <v>2250</v>
+        <v>2200</v>
       </c>
       <c r="C354">
-        <v>114.8097329106024</v>
+        <v>56.09574693011376</v>
       </c>
       <c r="D354" t="s">
         <v>125</v>
@@ -7946,18 +7946,18 @@
         <v>145</v>
       </c>
       <c r="F354" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="355" spans="1:6">
       <c r="A355" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="B355">
-        <v>2900</v>
+        <v>3150</v>
       </c>
       <c r="C355">
-        <v>114.8097329106024</v>
+        <v>10331.50326630582</v>
       </c>
       <c r="D355" t="s">
         <v>125</v>
@@ -7966,18 +7966,18 @@
         <v>145</v>
       </c>
       <c r="F355" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="356" spans="1:6">
       <c r="A356" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="B356">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="C356">
-        <v>114.8097329106024</v>
+        <v>10331.50326630582</v>
       </c>
       <c r="D356" t="s">
         <v>125</v>
@@ -7986,18 +7986,18 @@
         <v>145</v>
       </c>
       <c r="F356" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="357" spans="1:6">
       <c r="A357" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B357">
-        <v>3150</v>
+        <v>2100</v>
       </c>
       <c r="C357">
-        <v>114.8097329106024</v>
+        <v>10331.50326630582</v>
       </c>
       <c r="D357" t="s">
         <v>125</v>
@@ -8006,18 +8006,18 @@
         <v>145</v>
       </c>
       <c r="F357" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="358" spans="1:6">
       <c r="A358" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="B358">
-        <v>3150</v>
+        <v>2600</v>
       </c>
       <c r="C358">
-        <v>114.8097329106024</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D358" t="s">
         <v>125</v>
@@ -8026,18 +8026,18 @@
         <v>145</v>
       </c>
       <c r="F358" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="359" spans="1:6">
       <c r="A359" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="B359">
-        <v>2850</v>
+        <v>3150</v>
       </c>
       <c r="C359">
-        <v>114.8097329106024</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D359" t="s">
         <v>125</v>
@@ -8046,18 +8046,18 @@
         <v>145</v>
       </c>
       <c r="F359" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="360" spans="1:6">
       <c r="A360" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B360">
-        <v>2500</v>
+        <v>2750</v>
       </c>
       <c r="C360">
-        <v>114.8097329106024</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D360" t="s">
         <v>125</v>
@@ -8066,18 +8066,18 @@
         <v>145</v>
       </c>
       <c r="F360" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="361" spans="1:6">
       <c r="A361" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="B361">
-        <v>3100</v>
+        <v>2100</v>
       </c>
       <c r="C361">
-        <v>114.8097329106024</v>
+        <v>10331.50326630582</v>
       </c>
       <c r="D361" t="s">
         <v>125</v>
@@ -8091,13 +8091,13 @@
     </row>
     <row r="362" spans="1:6">
       <c r="A362" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B362">
         <v>2900</v>
       </c>
       <c r="C362">
-        <v>114.8097329106024</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D362" t="s">
         <v>125</v>
@@ -8106,18 +8106,18 @@
         <v>145</v>
       </c>
       <c r="F362" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="363" spans="1:6">
       <c r="A363" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="B363">
         <v>2250</v>
       </c>
       <c r="C363">
-        <v>114.8097329106024</v>
+        <v>50.30315431564902</v>
       </c>
       <c r="D363" t="s">
         <v>125</v>
@@ -8126,18 +8126,18 @@
         <v>145</v>
       </c>
       <c r="F363" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="364" spans="1:6">
       <c r="A364" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="B364">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="C364">
-        <v>114.8097329106024</v>
+        <v>10331.50326630582</v>
       </c>
       <c r="D364" t="s">
         <v>125</v>
@@ -8146,7 +8146,87 @@
         <v>145</v>
       </c>
       <c r="F364" t="s">
-        <v>146</v>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6">
+      <c r="A365" t="s">
+        <v>81</v>
+      </c>
+      <c r="B365">
+        <v>3300</v>
+      </c>
+      <c r="C365">
+        <v>50.30315431564902</v>
+      </c>
+      <c r="D365" t="s">
+        <v>125</v>
+      </c>
+      <c r="E365" t="s">
+        <v>145</v>
+      </c>
+      <c r="F365" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6">
+      <c r="A366" t="s">
+        <v>51</v>
+      </c>
+      <c r="B366">
+        <v>2250</v>
+      </c>
+      <c r="C366">
+        <v>50.30315431564902</v>
+      </c>
+      <c r="D366" t="s">
+        <v>125</v>
+      </c>
+      <c r="E366" t="s">
+        <v>145</v>
+      </c>
+      <c r="F366" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6">
+      <c r="A367" t="s">
+        <v>45</v>
+      </c>
+      <c r="B367">
+        <v>3150</v>
+      </c>
+      <c r="C367">
+        <v>50.30315431564902</v>
+      </c>
+      <c r="D367" t="s">
+        <v>125</v>
+      </c>
+      <c r="E367" t="s">
+        <v>145</v>
+      </c>
+      <c r="F367" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6">
+      <c r="A368" t="s">
+        <v>17</v>
+      </c>
+      <c r="B368">
+        <v>2250</v>
+      </c>
+      <c r="C368">
+        <v>50.30315431564902</v>
+      </c>
+      <c r="D368" t="s">
+        <v>125</v>
+      </c>
+      <c r="E368" t="s">
+        <v>145</v>
+      </c>
+      <c r="F368" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
